--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,43 +425,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G917"/>
+  <dimension ref="A1:H918"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>文章編號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>標題</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>作者</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>爬取時間</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>關鍵詞</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>內文</t>
         </is>
       </c>
     </row>
@@ -487,6 +504,7 @@
           <t>撤銷徵收、廢止徵收</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -522,6 +540,7 @@
           <t>界址爭議</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -557,6 +576,7 @@
           <t>地價稅、土地增值稅、遺產稅、贈與稅、公共設施保留地、公共設施用地</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -592,6 +612,7 @@
           <t>登記不實、損害賠償</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -627,6 +648,7 @@
           <t>公共設施保留地、公共設施用地</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -662,6 +684,7 @@
           <t>分管契約、判決分割</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -697,6 +720,7 @@
           <t>建物拆除補償</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -732,6 +756,7 @@
           <t>拋棄繼承、順位繼承人</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -767,6 +792,7 @@
           <t>絕對估值、相對估值、勘估標的</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -802,6 +828,7 @@
           <t>借名登記契約</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -837,6 +864,7 @@
           <t>申請興建農舍</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -872,6 +900,7 @@
           <t>農業用地變更使用</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -907,6 +936,7 @@
           <t>時效取得地上權登記、主觀意思之證明文件</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -942,6 +972,7 @@
           <t>空地限建、平均地權、限制建築</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -977,6 +1008,7 @@
           <t>區域計畫、環境保護</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1012,6 +1044,7 @@
           <t>公地放領、農地農用、自耕農</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1047,6 +1080,7 @@
           <t>土地徵收、一般徵收、區段徵收</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1082,6 +1116,7 @@
           <t>國土保育費、影響費</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1117,6 +1152,7 @@
           <t>有償撥用、無償撥用、土地徵收、土地徵用</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1152,6 +1188,7 @@
           <t>特別犧牲、財產權</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1187,6 +1224,7 @@
           <t>私人土地或其改良物、土地徵收、土地徵用</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1222,6 +1260,7 @@
           <t>自辦市地重劃、重劃會</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1257,6 +1296,7 @@
           <t>都市更新、基地權利價值</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1292,6 +1332,7 @@
           <t>國土計畫公告、國土計畫變更、都市計畫</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1327,6 +1368,7 @@
           <t>公寓大廈約定專用、系爭房地、公寓大廈管理條例、系爭買賣契約</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1362,6 +1404,7 @@
           <t>基地優先購買權、物權效力</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1397,6 +1440,7 @@
           <t>土地開發分析法</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1432,6 +1476,7 @@
           <t>折現現金流量分析法</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1467,6 +1512,7 @@
           <t>土地增值稅、免徵、不課徵、記存、不計徵、租稅</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1502,6 +1548,7 @@
           <t>消費者保護法、企業經營者、消費者、無過失責任</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1537,6 +1584,7 @@
           <t>空地、素地、袋地、裡地、估價</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1572,6 +1620,7 @@
           <t>優先購買權、土地所有權、基地</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1607,6 +1656,7 @@
           <t>民法物權編施行法第8條之5、土地法第104條、優先承買權、基地</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1642,6 +1692,7 @@
           <t>美濃大峽谷、土石採取法、廢棄物清理法、區域計畫法、非都市土地</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1677,6 +1728,7 @@
           <t>土地法第34條之1、公同共有、優先購買</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1712,6 +1764,7 @@
           <t>不動產經紀業、聯合行為</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1747,6 +1800,7 @@
           <t>差別稅率、地價稅、土地增值稅、房地合一所得稅、房屋稅</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1782,6 +1836,7 @@
           <t>回頭殺、差價、不動產經紀業管理條例</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1817,6 +1872,7 @@
           <t>生態足跡、碳足跡、土地面積、碳排放</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1852,6 +1908,7 @@
           <t>租賃、租客、租金、欠租、租霸下車</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1887,6 +1944,7 @@
           <t>WTP、WTA、不動產、依戀不捨情感</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1922,6 +1980,7 @@
           <t>消保法、保證書、消費者</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1957,6 +2016,7 @@
           <t>產權型態、分別共有、公同共有、公寓大廈</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1992,6 +2052,7 @@
           <t>聯合行為、不動產經紀業者、共同約束</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2027,6 +2088,7 @@
           <t>離差計算、比較標、調整率</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2062,6 +2124,7 @@
           <t>起造人、建造執照、所有權人、公寓大廈</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2097,6 +2160,7 @@
           <t>離差、不動產估價、勘估標、比較標</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2132,6 +2196,7 @@
           <t>市地重劃、地價、共同負擔</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2167,6 +2232,7 @@
           <t>土地分割、土地合併、建物分割、建物合併</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2202,6 +2268,7 @@
           <t>公平交易法、結合、全聯公司、大潤發</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2237,6 +2304,7 @@
           <t>營業用、自住、房屋稅、稅率、稅基</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2272,6 +2340,7 @@
           <t>非市場價值、旅遊成本法、特徵價格法、條件評價法</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2307,6 +2376,7 @@
           <t>不動產市場、市場失靈、財貨市場、供需機制</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2342,6 +2412,7 @@
           <t>鄉村地區整體規劃、鄉村地區計畫、國土計畫法</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2377,6 +2448,7 @@
           <t>不動產市場、具體市場、集中市場、效率市場</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2412,6 +2484,7 @@
           <t>土地政策、國土計畫法、農業、農地、農一用地</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2447,6 +2520,7 @@
           <t>土地增值稅、租稅、地價</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2482,6 +2556,7 @@
           <t>容積獎勵、公共設施、都市發展</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2517,6 +2592,7 @@
           <t>ESG、環境保護、社會責任、公司治理</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2552,6 +2628,7 @@
           <t>重購、先賣後買、先買後賣</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2587,6 +2664,7 @@
           <t>機會成本、犠牲、自有資金</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2622,6 +2700,7 @@
           <t>房地合一稅、繼承、受贈</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2657,6 +2736,7 @@
           <t>先行區段徵收、區段徵收、都市計畫</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2692,6 +2772,7 @@
           <t>移轉現值、土地現值、土地增值稅</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2727,6 +2808,7 @@
           <t>公同共有人、優先購買權、權利行使</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2762,6 +2844,7 @@
           <t>國土計畫法、農業發展區、國土保育區</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2797,6 +2880,7 @@
           <t>土地增值稅、租稅、地上權</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2832,6 +2916,7 @@
           <t>農業用地、農業發展、農業生產</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2867,6 +2952,7 @@
           <t>購屋預約單、預售屋買賣契約</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2902,6 +2988,7 @@
           <t>優先購買權、地籍清理</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2937,6 +3024,7 @@
           <t>實價登錄、車位、車位總價、車位總面積</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2972,6 +3060,7 @@
           <t>配偶、贈與、土地增值稅</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3007,6 +3096,7 @@
           <t>地號、建號</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3042,6 +3132,7 @@
           <t>地政士</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3077,6 +3168,7 @@
           <t>平均地權條例、預售屋、新建成屋</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3112,6 +3204,7 @@
           <t>所得稅、土地增值稅、繼承</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3147,6 +3240,7 @@
           <t>租稅、平等原則、土地稅法、土地增值稅</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3182,6 +3276,7 @@
           <t>所得稅、免納(徵)、非課稅範圍、無所得、房地合一</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3217,6 +3312,7 @@
           <t>土地增值稅、土地徵收、公共設施保留地、非都市土地</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3252,6 +3348,7 @@
           <t>信託、受益人、信託財產、受託人、委託人</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3287,6 +3384,7 @@
           <t>房地合一、房地交換</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3322,6 +3420,7 @@
           <t>預售屋、房屋預售、公寓大廈、房價飆漲</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3357,6 +3456,7 @@
           <t>應繼遺產、繼承人、遺產稅</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3392,6 +3492,7 @@
           <t>預售屋、成屋、購屋貸款、選擇權</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3427,6 +3528,7 @@
           <t>信託契約、自由處分、委託人、信託法</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3462,6 +3564,7 @@
           <t>預售屋、自備款、房價、定金、簽約金</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3497,6 +3600,7 @@
           <t>遺產、剩餘財產、差額分配、受贈配偶</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3532,6 +3636,7 @@
           <t>信託、受益權、受託人、受益人</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3567,6 +3672,7 @@
           <t>建設公司、先售後建、預售屋</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3602,6 +3708,7 @@
           <t>共有人、繼承人、繼承登記、默示分管</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3637,6 +3744,7 @@
           <t>選擇權、買權選擇權、賣權選擇權、權利金、標的物</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3672,6 +3780,7 @@
           <t>個人墓地、土地法第34條之1、個人墓園、共有人、優先承買</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3707,6 +3816,7 @@
           <t>新青安、購屋、房價、貸款</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3742,6 +3852,7 @@
           <t>房地合一所得稅、受贈、土地現值、所得稅</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3777,6 +3888,7 @@
           <t>友善農地、慣行農業</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3812,6 +3924,7 @@
           <t>共有人、地上權、共有物</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3847,6 +3960,7 @@
           <t>優先購買權、土地法第34條之1、租賃權、地上權、典權</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3882,6 +3996,7 @@
           <t>地上權、時效取得、占有人</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3917,6 +4032,7 @@
           <t>地上權、使用權、分割移轉</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3952,6 +4068,7 @@
           <t>信託、委託人、抵押、投資</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3987,6 +4104,7 @@
           <t>農業權、農地、容積、容積移轉</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4022,6 +4140,7 @@
           <t>基地、優先購買權、所有權人</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4057,6 +4176,7 @@
           <t>環境永續、碳中和、循環利用、溫室氣體</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -4092,6 +4212,7 @@
           <t>都市計畫、行政訴訟、道路</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4127,6 +4248,7 @@
           <t>國土計畫法、區域計畫法、農地</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -4162,6 +4284,7 @@
           <t>都市計畫、計畫裁量、利益衡量</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4197,6 +4320,7 @@
           <t>借名契約、借名登記、所有權</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -4232,6 +4356,7 @@
           <t>承攬人、抵押權</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -4267,6 +4392,7 @@
           <t>公路法、私有公路、自然人、土地增值稅</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -4302,6 +4428,7 @@
           <t>市地重劃、土地所有權人</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -4337,6 +4464,7 @@
           <t>財產權、不動產、112年憲判字第20號、所有權人</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -4372,6 +4500,7 @@
           <t>贈與稅、免稅額、土地現值</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -4407,6 +4536,7 @@
           <t>內部估價、外部估價、不動產估價師</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -4442,6 +4572,7 @@
           <t>遺產稅、繼承人、免稅額、扣除額</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4477,6 +4608,7 @@
           <t>住宅租約、租賃住宅、承租人、出租人</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -4512,6 +4644,7 @@
           <t>共有物分割、抵押權、共有人</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -4547,6 +4680,7 @@
           <t>透天房屋、真透天、假透天、產權</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4582,6 +4716,7 @@
           <t>基地權利種類、所有權</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -4617,6 +4752,7 @@
           <t>地價稅、房屋稅、信託歸戶、信託利益、受益人</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -4652,6 +4788,7 @@
           <t>林業用地</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -4687,6 +4824,7 @@
           <t>區段徵收、都市土地、都市計畫</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -4722,6 +4860,7 @@
           <t>土地法、私有土地、照價收買</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -4757,6 +4896,7 @@
           <t>都市計畫、土地權利、地主</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -4792,6 +4932,7 @@
           <t>遺贈、死因贈與、遺囑、贈與說</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -4827,6 +4968,7 @@
           <t>土地法第34條之1、公同共有、優先購買權、共有人</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -4862,6 +5004,7 @@
           <t>公平交易法、共同約束、加盟、聯合行為</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -4897,6 +5040,7 @@
           <t>地價區段、區段地價</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -4932,6 +5076,7 @@
           <t>併同出賣、優先購買權</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -4967,6 +5112,7 @@
           <t>企業經營者、消費者</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -5002,6 +5148,7 @@
           <t>規約、公寓大廈、所有權人</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -5037,6 +5184,7 @@
           <t>定型化契約、誠信原則、平等互惠、消費者</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -5072,6 +5220,7 @@
           <t>私有土地、累進稅、地價稅</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -5107,6 +5256,7 @@
           <t>空地限建、地價、空地稅、照價收買</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -5142,6 +5292,7 @@
           <t>土地法、共有人、優先購買權、地上權、典權</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -5177,6 +5328,7 @@
           <t>房屋稅、囤房稅</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -5212,6 +5364,7 @@
           <t>建築物違規、所有權人、行為人、建築法</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -5247,6 +5400,7 @@
           <t>優先購買權、土地登記、土地權利移轉</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -5282,6 +5436,7 @@
           <t>優先購買權、共有人</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -5317,6 +5472,7 @@
           <t>土地徵收、公共設施保留地、毗鄰</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -5352,6 +5508,7 @@
           <t>公共設施保留地、公共設施用地</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -5387,6 +5544,7 @@
           <t>地面師、偽造遺囑、土地登記、繼承登記</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -5422,6 +5580,7 @@
           <t>發給補償完竣、補償人、土地徵收</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -5457,6 +5616,7 @@
           <t>名勝古蹟、古蹟保存</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -5492,6 +5652,7 @@
           <t>區段徵收、土地所有權人、抵價地</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -5527,6 +5688,7 @@
           <t>定型化契約</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -5562,6 +5724,7 @@
           <t>市地重劃、區段徵收、地價、土地所有權人</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -5597,6 +5760,7 @@
           <t>更正登記、登記錯誤、土地登記</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -5632,6 +5796,7 @@
           <t>遺囑信託、遺囑執行人、繼承人、繼承登記、遺產管理人</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -5667,6 +5832,7 @@
           <t>定型化契約、消費者保護法、誠信原則、個別磋商、審閱權利</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -5702,6 +5868,7 @@
           <t>土地重劃、區段徵收、抵費地、配餘地</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -5737,6 +5904,7 @@
           <t>移轉登記、優先購買權、共有人</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -5772,6 +5940,7 @@
           <t>設籍、房地合一所得稅、地價稅、房屋稅</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -5807,6 +5976,7 @@
           <t>納稅、滯納金、強制執行、行政執行</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -5842,6 +6012,7 @@
           <t>非都市土地、區域計畫法</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -5877,6 +6048,7 @@
           <t>房地合一所得稅、稅基、房地交易所得</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -5912,6 +6084,7 @@
           <t>土地參考資訊檔、建物、土地</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -5947,6 +6120,7 @@
           <t>預售屋、履約擔保、信託、專戶管理、價金返還、連帶擔保</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -5982,6 +6156,7 @@
           <t>預告登記、土地權利、請求權、登記名義人</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -6017,6 +6192,7 @@
           <t>登記、權利人、義務人、優先購買權</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -6052,6 +6228,7 @@
           <t>地價稅、農業用地</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -6087,6 +6264,7 @@
           <t>耕地、農業發展</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -6122,6 +6300,7 @@
           <t>優先購買權、土地法、耕地</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -6157,6 +6336,7 @@
           <t>仕紳化、租隙</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -6192,6 +6372,7 @@
           <t>受託人、信託財產、信託法</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -6227,6 +6408,7 @@
           <t>公地標售、地價、房價</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -6262,6 +6444,7 @@
           <t>居住、居住正義</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -6297,6 +6480,7 @@
           <t>綠能智慧建築、節能減碳、碳足跡</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -6332,6 +6516,7 @@
           <t>信託財產、受益人、受託人</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -6367,6 +6552,7 @@
           <t>土地登記規則、更正登記、登記錯誤、登記遺漏</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -6402,6 +6588,7 @@
           <t>區段徵收、都市計畫</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -6437,6 +6624,7 @@
           <t>土地登記、登記錯誤、更正登記、塗銷登記</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -6472,6 +6660,7 @@
           <t>私權爭執、登記權利人、登記義務人</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -6507,6 +6696,7 @@
           <t>法定空地、地價稅、公眾通行、所有權人</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -6542,6 +6732,7 @@
           <t>公眾通行、無償、土地稅、土地所有權人</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -6577,6 +6768,7 @@
           <t>都市計畫、行政處分、行政訴訟</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -6612,6 +6804,7 @@
           <t>贈與稅、受贈人、贈與人</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -6647,6 +6840,7 @@
           <t>自住、房屋稅</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -6682,6 +6876,7 @@
           <t>公共設施保留地、遺產稅、贈與稅、納稅義務人</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -6717,6 +6912,7 @@
           <t>農業用地、土地增值稅</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -6752,6 +6948,7 @@
           <t>土地增值稅、契稅、贈與稅</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -6787,6 +6984,7 @@
           <t>既成道路、公共設施、地價稅</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -6822,6 +7020,7 @@
           <t>土地增值稅、土地、所有權人</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -6857,6 +7056,7 @@
           <t>土地增值稅、配偶、贈與</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -6892,6 +7092,7 @@
           <t>重大災害、房屋稅、納稅義務人、地價稅</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -6927,6 +7128,7 @@
           <t>土地登記、登記錯誤、登記遺漏、登記虛偽</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -6962,6 +7164,7 @@
           <t>淨零排放、溫室氣體、碳匯</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -6997,6 +7200,7 @@
           <t>重購、土地徵收、免稅、退稅</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -7032,6 +7236,7 @@
           <t>公共設施、都市計畫、遺產稅、繼承人</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -7067,6 +7272,7 @@
           <t>自住、房屋所有權人、房地所有權人、房地合一、重購房地</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -7102,6 +7308,7 @@
           <t>信託、委託、委任、委託人、委任人、受任人</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -7137,6 +7344,7 @@
           <t>韌性城市、災害</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -7172,6 +7380,7 @@
           <t>共有物、所有權、共有關係、變動關係</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -7207,6 +7416,7 @@
           <t>空地稅、空屋稅、囤房稅、空地、空屋</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -7242,6 +7452,7 @@
           <t>農地、農業用地、區域計畫法、土地</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -7277,6 +7488,7 @@
           <t>房屋稅</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -7312,6 +7524,7 @@
           <t>損失補償、財產權、特別犧牲</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -7347,6 +7560,7 @@
           <t>土地稅、地價稅、建築物</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -7382,6 +7596,7 @@
           <t>地價稅、稅基、稅率、稅額</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -7417,6 +7632,7 @@
           <t>地籍圖、土地所有權、指界</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -7452,6 +7668,7 @@
           <t>登記、調解、權利變更</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -7487,6 +7704,7 @@
           <t>日治時期、土地登記、土地所有權、請求權</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -7522,6 +7740,7 @@
           <t>鄉村地區、非都市土地</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -7557,6 +7776,7 @@
           <t>登記、上訴人、土地權利</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -7592,6 +7812,7 @@
           <t>太陽光電、太陽能光電、非都市土地</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -7627,6 +7848,7 @@
           <t>地主、佃農、農地</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -7662,6 +7884,7 @@
           <t>囤房稅</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -7697,6 +7920,7 @@
           <t>農場規模、農業</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -7732,6 +7956,7 @@
           <t>信託財產</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -7767,6 +7992,7 @@
           <t>債權效力、物權效力、優先購買權</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -7802,6 +8028,7 @@
           <t>地價、區段地價、公告地價</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -7837,6 +8064,7 @@
           <t>工業用地、農業用地、農業產量、工業產量</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -7872,6 +8100,7 @@
           <t>違章建築、信託、不動產、登記</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -7907,6 +8136,7 @@
           <t>地價、勞資、土地集約度</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -7942,6 +8172,7 @@
           <t>住宅用地、稅率、土地持分、房屋持分、地價稅</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -7977,6 +8208,7 @@
           <t>地盡其利、有效使用、土地利用</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -8012,6 +8244,7 @@
           <t>土地所有權、權利</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -8047,6 +8280,7 @@
           <t>土地利用、低度利用、過度利用、不當利用</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -8082,6 +8316,7 @@
           <t>信託利益、受益權</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -8117,6 +8352,7 @@
           <t>通貨膨脹、不動產價格、經濟不景氣、利率上漲、炒房</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -8152,6 +8388,7 @@
           <t>土地面積、稅率、地價稅</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -8187,6 +8424,7 @@
           <t>生態足跡、碳足跡</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -8222,6 +8460,7 @@
           <t>登記錯誤、損害賠償、地政事務所、重複登錄</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -8257,6 +8496,7 @@
           <t>地上權、典權、優先購買權、土地法第34條、土地法第104條</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -8292,6 +8532,7 @@
           <t>損害賠償、登記錯誤、登記面積</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -8327,6 +8568,7 @@
           <t>有償讓與、共有人、受讓人、用益物權</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -8362,6 +8604,7 @@
           <t>繼承人、連續繼承、遺贈</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -8397,6 +8640,7 @@
           <t>溫室氣體、排放量、排放源、碳費、碳權</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -8432,6 +8676,7 @@
           <t>所有權、不動產登記</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -8467,6 +8712,7 @@
           <t>房價上漲、土地貢獻、聯合貢獻、土地、建物</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -8502,6 +8748,7 @@
           <t>預售屋、定型化契約、信託</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -8537,6 +8784,7 @@
           <t>建物、折舊、增值</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -8572,6 +8820,7 @@
           <t>農業用地租賃、租賃契約、農業用地</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -8607,6 +8856,7 @@
           <t>漲價完全歸公、市場完全閉鎖、市場地價</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -8642,6 +8892,7 @@
           <t>部分共有人、優先購買權</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -8677,6 +8928,7 @@
           <t>土地稅、地價稅、土地增值稅、公共建設</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -8712,6 +8964,7 @@
           <t>多數決、共有人、優先購買、地上權、典權</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -8747,6 +9000,7 @@
           <t>所有權、共有</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -8782,6 +9036,7 @@
           <t>不動產移轉稅、土地增值稅、房地合一所得稅</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -8817,6 +9072,7 @@
           <t>共有人、優先購買權、出賣人</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -8852,6 +9108,7 @@
           <t>不動產、地價稅、房屋稅、持有稅</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -8887,6 +9144,7 @@
           <t>共有人、多數決</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -8922,6 +9180,7 @@
           <t>公共設施、資本化、土地所有權人、重新規定地價</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -8957,6 +9216,7 @@
           <t>多數決、共有人、優先購買權</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -8992,6 +9252,7 @@
           <t>平均地權、規定地價、照價徵稅、照價收買、漲價歸公</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -9027,6 +9288,7 @@
           <t>多數決、有償讓與、優先購買、共有人</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -9062,6 +9324,7 @@
           <t>重劃區、土地所有權人、公共設施</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -9097,6 +9360,7 @@
           <t>土地所有權、登記、申請</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -9132,6 +9396,7 @@
           <t>移轉、不動產所有權</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -9167,6 +9432,7 @@
           <t>土地總登記、土地所有權、第一次登記</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -9202,6 +9468,7 @@
           <t>地租國有、地利共享、稅去地主、天然地租、社會地租</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -9237,6 +9504,7 @@
           <t>用腳投票、公共設施、財產稅</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -9272,6 +9540,7 @@
           <t>碳權、二氧化碳、排放量</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -9307,6 +9576,7 @@
           <t>訴訟外紛爭解決機制、調處、調解、仲裁、訴訟、ADR</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -9342,6 +9612,7 @@
           <t>屠能、辛克萊、都市發展、經濟作物、農地</t>
         </is>
       </c>
+      <c r="H255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -9377,6 +9648,7 @@
           <t>登記錯誤、土地登記、損害賠償</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -9412,6 +9684,7 @@
           <t>指界、土地所有權人</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -9447,6 +9720,7 @@
           <t>租約、租賃、契約、不定期限</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -9482,6 +9756,7 @@
           <t>財產權、土地</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -9517,6 +9792,7 @@
           <t>房地合一稅、營利事業</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -9552,6 +9828,7 @@
           <t>所有權人、繼承人、回復原狀、核准回復說、自動回復說</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -9587,6 +9864,7 @@
           <t>預售屋、新建成屋、買賣契約、轉售、買受人</t>
         </is>
       </c>
+      <c r="H262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -9622,6 +9900,7 @@
           <t>登記</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -9657,6 +9936,7 @@
           <t>氣候變遷、調適能力</t>
         </is>
       </c>
+      <c r="H264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -9692,6 +9972,7 @@
           <t>私法人、住宅</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -9727,6 +10008,7 @@
           <t>土地、所有權、請求權</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -9762,6 +10044,7 @@
           <t>平均地權、土地現值</t>
         </is>
       </c>
+      <c r="H267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -9797,6 +10080,7 @@
           <t>耕地租佃、裁判費、耕地、租約</t>
         </is>
       </c>
+      <c r="H268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -9832,6 +10116,7 @@
           <t>土地登記、損害賠償、過失</t>
         </is>
       </c>
+      <c r="H269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -9867,6 +10152,7 @@
           <t>土地登記</t>
         </is>
       </c>
+      <c r="H270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -9902,6 +10188,7 @@
           <t>農業用地、非都市土地、農業使用</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -9937,6 +10224,7 @@
           <t>損害賠償、過失、登記錯誤</t>
         </is>
       </c>
+      <c r="H272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -9972,6 +10260,7 @@
           <t>重購、退稅、自住房屋</t>
         </is>
       </c>
+      <c r="H273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -10007,6 +10296,7 @@
           <t>侵權行為、所有權移轉、共有人</t>
         </is>
       </c>
+      <c r="H274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -10042,6 +10332,7 @@
           <t>繼承登記、共有人、優先購買權、不動產</t>
         </is>
       </c>
+      <c r="H275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -10077,6 +10368,7 @@
           <t>地籍、測量錯誤</t>
         </is>
       </c>
+      <c r="H276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -10112,6 +10404,7 @@
           <t>遺產、配偶、剩餘財產、繼承人、贈與</t>
         </is>
       </c>
+      <c r="H277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -10147,6 +10440,7 @@
           <t>成長極、平衡發展理論</t>
         </is>
       </c>
+      <c r="H278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -10182,6 +10476,7 @@
           <t>剩餘財產、配偶、遺產稅、土地增值稅</t>
         </is>
       </c>
+      <c r="H279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -10217,6 +10512,7 @@
           <t>共有人、優先購買權</t>
         </is>
       </c>
+      <c r="H280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -10252,6 +10548,7 @@
           <t>遺產稅、繼承登記、納稅義務人</t>
         </is>
       </c>
+      <c r="H281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -10287,6 +10584,7 @@
           <t>地價評議</t>
         </is>
       </c>
+      <c r="H282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -10322,6 +10620,7 @@
           <t>繳代金、容積移轉、都市計畫</t>
         </is>
       </c>
+      <c r="H283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -10357,6 +10656,7 @@
           <t>繼承登記、優先購買、共有人、土地</t>
         </is>
       </c>
+      <c r="H284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -10392,6 +10692,7 @@
           <t>制度、資源配置、分區管制、實價登錄</t>
         </is>
       </c>
+      <c r="H285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -10427,6 +10728,7 @@
           <t>交易成本、Transaction Cos、不動產交易、財貨交易</t>
         </is>
       </c>
+      <c r="H286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -10462,6 +10764,7 @@
           <t>巴瑞圖經濟效率、馬歇爾經濟效率、土地徵收</t>
         </is>
       </c>
+      <c r="H287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -10497,6 +10800,7 @@
           <t>共有人、優先購買權、優先承買權、公同共有物、肯定說</t>
         </is>
       </c>
+      <c r="H288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -10532,6 +10836,7 @@
           <t>容積獎勵、容積移轉、容積代金、發展權國有</t>
         </is>
       </c>
+      <c r="H289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -10567,6 +10872,7 @@
           <t>遺產、共有人、繼承人、債權人</t>
         </is>
       </c>
+      <c r="H290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -10602,6 +10908,7 @@
           <t>外部利益、外部成本、社會成本、社會利益、土地開發</t>
         </is>
       </c>
+      <c r="H291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -10637,6 +10944,7 @@
           <t>公同共有、共有物、分割</t>
         </is>
       </c>
+      <c r="H292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -10672,6 +10980,7 @@
           <t>共用地悲劇、反共用地悲劇、財產權</t>
         </is>
       </c>
+      <c r="H293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -10707,6 +11016,7 @@
           <t>繼承登記、優先購買權、繼承人、合法使用人、其他共有人</t>
         </is>
       </c>
+      <c r="H294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -10742,6 +11052,7 @@
           <t>市場失靈、政府失靈</t>
         </is>
       </c>
+      <c r="H295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -10777,6 +11088,7 @@
           <t>房地合一稅、所得稅法、農業發展條例、土地增值稅</t>
         </is>
       </c>
+      <c r="H296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -10812,6 +11124,7 @@
           <t>多次繼承、房地合一、繼承</t>
         </is>
       </c>
+      <c r="H297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -10847,6 +11160,7 @@
           <t>土地法、優先購買權</t>
         </is>
       </c>
+      <c r="H298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -10882,6 +11196,7 @@
           <t>都市計畫、通盤檢討</t>
         </is>
       </c>
+      <c r="H299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -10917,6 +11232,7 @@
           <t>登載不實、土地登記、逃漏稅捐、土地增值稅</t>
         </is>
       </c>
+      <c r="H300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -10952,6 +11268,7 @@
           <t>借名登記、地所有權</t>
         </is>
       </c>
+      <c r="H301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -10987,6 +11304,7 @@
           <t>土地登記、虛偽登記、登記錯誤</t>
         </is>
       </c>
+      <c r="H302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -11022,6 +11340,7 @@
           <t>土地國有、土地私有、絕對地租、市場機制、價格機能</t>
         </is>
       </c>
+      <c r="H303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -11057,6 +11376,7 @@
           <t>建造執照、換約、紅單、公寓大廈、預售屋</t>
         </is>
       </c>
+      <c r="H304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -11092,6 +11412,7 @@
           <t>地籍測量、土地複丈、建物測量</t>
         </is>
       </c>
+      <c r="H305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -11127,6 +11448,7 @@
           <t>房屋稅、平民住宅、社會住宅、臨時工廠、特定工廠</t>
         </is>
       </c>
+      <c r="H306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -11162,6 +11484,7 @@
           <t>違章建築、時效取得、合法建物、建物所有權</t>
         </is>
       </c>
+      <c r="H307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -11197,6 +11520,7 @@
           <t>特別犧牲、徵收補償、既成道路、徵收地上權</t>
         </is>
       </c>
+      <c r="H308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -11232,6 +11556,7 @@
           <t>土地徵收、現金補償、抵價地補償、債券補償、區段徵收、一般徵收</t>
         </is>
       </c>
+      <c r="H309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -11267,6 +11592,7 @@
           <t>國土計畫、區域計畫、土地使用、管制</t>
         </is>
       </c>
+      <c r="H310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -11302,6 +11628,7 @@
           <t>一般因素、區域因素、個別因素</t>
         </is>
       </c>
+      <c r="H311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -11337,6 +11664,7 @@
           <t>預先拋棄、優先承買權</t>
         </is>
       </c>
+      <c r="H312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -11372,6 +11700,7 @@
           <t>土地增值稅、免徵、房地合一所得稅、農業用地</t>
         </is>
       </c>
+      <c r="H313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -11407,6 +11736,7 @@
           <t>土地增值稅、農牧用地、交通用地、農路、公路</t>
         </is>
       </c>
+      <c r="H314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -11442,6 +11772,7 @@
           <t>土地增值稅、房地合一所得稅、自用住宅、課徵、課稅</t>
         </is>
       </c>
+      <c r="H315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -11477,6 +11808,7 @@
           <t>自用住宅、直系親屬</t>
         </is>
       </c>
+      <c r="H316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -11512,6 +11844,7 @@
           <t>原地價偏高、原地價偏低、土地增值稅、公告土地現值</t>
         </is>
       </c>
+      <c r="H317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -11547,6 +11880,7 @@
           <t>騎樓、地價稅</t>
         </is>
       </c>
+      <c r="H318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -11582,6 +11916,7 @@
           <t>土地增值稅、契稅、課徵對象、課稅基礎</t>
         </is>
       </c>
+      <c r="H319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -11617,6 +11952,7 @@
           <t>土地增值稅、無移轉、土地所有權</t>
         </is>
       </c>
+      <c r="H320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -11652,6 +11988,7 @@
           <t>非都市土地編定、交通用地、土地稅法、農業用地、土地增值稅</t>
         </is>
       </c>
+      <c r="H321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -11687,6 +12024,7 @@
           <t>審議、國土計畫、審議機關</t>
         </is>
       </c>
+      <c r="H322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -11722,6 +12060,7 @@
           <t>土地增值稅、信託、不課徵、契稅、租稅效果</t>
         </is>
       </c>
+      <c r="H323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -11757,6 +12096,7 @@
           <t>房地合一稅、重購、退稅、自住房屋</t>
         </is>
       </c>
+      <c r="H324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -11792,6 +12132,7 @@
           <t>農業用地、土地增值稅、房地合一所得稅、興建農舍</t>
         </is>
       </c>
+      <c r="H325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -11827,6 +12168,7 @@
           <t>贈與現金、土地增值稅、稅負</t>
         </is>
       </c>
+      <c r="H326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -11862,6 +12204,7 @@
           <t>錯誤登記、登記錯誤、更正登記、塗銷登記</t>
         </is>
       </c>
+      <c r="H327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -11897,6 +12240,7 @@
           <t>房地合一、所得稅、共有房地</t>
         </is>
       </c>
+      <c r="H328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -11932,6 +12276,7 @@
           <t>公寓大廈、鐵鋁窗、防墜設施</t>
         </is>
       </c>
+      <c r="H329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -11967,6 +12312,7 @@
           <t>國土計畫、建築用地</t>
         </is>
       </c>
+      <c r="H330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -12002,6 +12348,7 @@
           <t>優先購買權、物權效力、債權效力、公共利益、社會福利</t>
         </is>
       </c>
+      <c r="H331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -12037,6 +12384,7 @@
           <t>定型化契約、不構成契約</t>
         </is>
       </c>
+      <c r="H332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -12072,6 +12420,7 @@
           <t>優先購買權、土地法第73條之1、繼承人、合法使用人、其他共有人</t>
         </is>
       </c>
+      <c r="H333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -12107,6 +12456,7 @@
           <t>土地增值稅、房屋合一稅、重購、退稅</t>
         </is>
       </c>
+      <c r="H334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -12142,6 +12492,7 @@
           <t>興建農舍、農業用地</t>
         </is>
       </c>
+      <c r="H335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -12177,6 +12528,7 @@
           <t>預售屋、房地合一</t>
         </is>
       </c>
+      <c r="H336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -12212,6 +12564,7 @@
           <t>優先購買權、競合</t>
         </is>
       </c>
+      <c r="H337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -12247,6 +12600,7 @@
           <t>廣告、經紀業、事實不符</t>
         </is>
       </c>
+      <c r="H338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -12282,6 +12636,7 @@
           <t>復權請求權、公法上請求權</t>
         </is>
       </c>
+      <c r="H339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -12317,6 +12672,7 @@
           <t>借名人、出名人、借名登記、請求權</t>
         </is>
       </c>
+      <c r="H340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -12352,6 +12708,7 @@
           <t>優先購買權、共有人</t>
         </is>
       </c>
+      <c r="H341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -12387,6 +12744,7 @@
           <t>共有土地、土地多數決、共有人、書面通知</t>
         </is>
       </c>
+      <c r="H342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -12422,6 +12780,7 @@
           <t>共有人、土地法第34條之1、買賣契約</t>
         </is>
       </c>
+      <c r="H343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -12457,6 +12816,7 @@
           <t>共有土地、共有人、優先購買權</t>
         </is>
       </c>
+      <c r="H344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -12492,6 +12852,7 @@
           <t>繼承登記、優先購買權、土地所有權、使用權分離</t>
         </is>
       </c>
+      <c r="H345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -12527,6 +12888,7 @@
           <t>耕地、優先購買權</t>
         </is>
       </c>
+      <c r="H346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -12562,6 +12924,7 @@
           <t>特別犧牲、一般犧牲</t>
         </is>
       </c>
+      <c r="H347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -12597,6 +12960,7 @@
           <t>假贈與、優先承買權、移轉登記</t>
         </is>
       </c>
+      <c r="H348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -12632,6 +12996,7 @@
           <t>土地徵收、補償地價</t>
         </is>
       </c>
+      <c r="H349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -12667,6 +13032,7 @@
           <t>照舊使用、農田水利、徵收補償、農田水利會</t>
         </is>
       </c>
+      <c r="H350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -12702,6 +13068,7 @@
           <t>共有人、原物分配</t>
         </is>
       </c>
+      <c r="H351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -12737,6 +13104,7 @@
           <t>免徵、不課徵、記存、累進稅、增值稅</t>
         </is>
       </c>
+      <c r="H352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -12772,6 +13140,7 @@
           <t>土地徵收、稟賦價值</t>
         </is>
       </c>
+      <c r="H353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -12807,6 +13176,7 @@
           <t>宗教團體、自然人名義、暫行條例</t>
         </is>
       </c>
+      <c r="H354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -12842,6 +13212,7 @@
           <t>炒房、預售屋、平均地權條例</t>
         </is>
       </c>
+      <c r="H355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -12877,6 +13248,7 @@
           <t>土地登記、損害賠償、請求權</t>
         </is>
       </c>
+      <c r="H356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -12912,6 +13284,7 @@
           <t>實價登錄、不動產價格</t>
         </is>
       </c>
+      <c r="H357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -12947,6 +13320,7 @@
           <t>借名登記契約、借名登記、借名人、出名人</t>
         </is>
       </c>
+      <c r="H358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -12982,6 +13356,7 @@
           <t>土地法第34條之1、地上權、農育權、不動產役權、典權</t>
         </is>
       </c>
+      <c r="H359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -13017,6 +13392,7 @@
           <t>登記錯誤、盜賣、東區名人巷</t>
         </is>
       </c>
+      <c r="H360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -13052,6 +13428,7 @@
           <t>成長管理</t>
         </is>
       </c>
+      <c r="H361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -13087,6 +13464,7 @@
           <t>停滯性通貨膨脹、通貨膨脹</t>
         </is>
       </c>
+      <c r="H362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -13122,6 +13500,7 @@
           <t>線上聲明、聲明</t>
         </is>
       </c>
+      <c r="H363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -13157,6 +13536,7 @@
           <t>袋地、裡地</t>
         </is>
       </c>
+      <c r="H364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -13192,6 +13572,7 @@
           <t>土地或建築改良物、標售</t>
         </is>
       </c>
+      <c r="H365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -13227,6 +13608,7 @@
           <t>面積短少、損害賠償、損失補償</t>
         </is>
       </c>
+      <c r="H366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -13262,6 +13644,7 @@
           <t>農地、保護農地、農地變更、全球性糧荒</t>
         </is>
       </c>
+      <c r="H367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -13297,6 +13680,7 @@
           <t>特別犧牲、歷史建築</t>
         </is>
       </c>
+      <c r="H368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -13332,6 +13716,7 @@
           <t>平民住宅、平價配售</t>
         </is>
       </c>
+      <c r="H369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -13367,6 +13752,7 @@
           <t>稅捐稽徵法、滯納金</t>
         </is>
       </c>
+      <c r="H370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -13402,6 +13788,7 @@
           <t>稅捐、核課期間</t>
         </is>
       </c>
+      <c r="H371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -13437,6 +13824,7 @@
           <t>重複課稅、工程受益費、土地增值稅、房地合一所得稅</t>
         </is>
       </c>
+      <c r="H372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -13472,6 +13860,7 @@
           <t>國土計畫、特定區域計畫</t>
         </is>
       </c>
+      <c r="H373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -13507,6 +13896,7 @@
           <t>退稅、重購退稅、稅捐稽徵法、土地增值稅、房地合一所得稅</t>
         </is>
       </c>
+      <c r="H374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -13542,6 +13932,7 @@
           <t>土地登記、登記錯誤</t>
         </is>
       </c>
+      <c r="H375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -13577,6 +13968,7 @@
           <t>地價評議委員會、不動產評價委員會</t>
         </is>
       </c>
+      <c r="H376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -13612,6 +14004,7 @@
           <t>土地增值稅、不課徵土地增值稅</t>
         </is>
       </c>
+      <c r="H377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -13647,6 +14040,7 @@
           <t>地上權、不動產役權、農育權</t>
         </is>
       </c>
+      <c r="H378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -13682,6 +14076,7 @@
           <t>土地增值稅、免徵性質、不課徵性質</t>
         </is>
       </c>
+      <c r="H379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -13717,6 +14112,7 @@
           <t>耕地租用、耕地租佃、農業用地租賃</t>
         </is>
       </c>
+      <c r="H380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -13752,6 +14148,7 @@
           <t>信託行為、信託契約、信託登記</t>
         </is>
       </c>
+      <c r="H381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -13787,6 +14184,7 @@
           <t>土地權利契約、信託登記</t>
         </is>
       </c>
+      <c r="H382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -13822,6 +14220,7 @@
           <t>典權、原始取得、繼受取得</t>
         </is>
       </c>
+      <c r="H383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -13857,6 +14256,7 @@
           <t>地上權、地上權登記</t>
         </is>
       </c>
+      <c r="H384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -13892,6 +14292,7 @@
           <t>遺產、繼承人、遺產分割、公同共有</t>
         </is>
       </c>
+      <c r="H385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -13927,6 +14328,7 @@
           <t>地價、地價動態</t>
         </is>
       </c>
+      <c r="H386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -13962,6 +14364,7 @@
           <t>區段徵收、都市計畫</t>
         </is>
       </c>
+      <c r="H387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -13997,6 +14400,7 @@
           <t>質權、出質人</t>
         </is>
       </c>
+      <c r="H388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -14032,6 +14436,7 @@
           <t>市地重劃、都市計畫</t>
         </is>
       </c>
+      <c r="H389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -14067,6 +14472,7 @@
           <t>優先購買權、土地法、共有物、民法</t>
         </is>
       </c>
+      <c r="H390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -14102,6 +14508,7 @@
           <t>建物所有權、土地登記規則</t>
         </is>
       </c>
+      <c r="H391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -14137,6 +14544,7 @@
           <t>分割合併、合併分割、不動產、合併登記、分割登記</t>
         </is>
       </c>
+      <c r="H392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -14172,6 +14580,7 @@
           <t>土地合併、抵押權、典權、複丈</t>
         </is>
       </c>
+      <c r="H393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -14207,6 +14616,7 @@
           <t>土地法、處分、債權行為、負擔行為、物權行為</t>
         </is>
       </c>
+      <c r="H394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -14242,6 +14652,7 @@
           <t>共有不動產、使用管理登記</t>
         </is>
       </c>
+      <c r="H395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -14277,6 +14688,7 @@
           <t>土地法、法律上之處分、事實上之處分、債權行為、物權行為</t>
         </is>
       </c>
+      <c r="H396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -14312,6 +14724,7 @@
           <t>撥用、公有不動產、不動產計畫書</t>
         </is>
       </c>
+      <c r="H397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -14347,6 +14760,7 @@
           <t>更正登記、私契、公契</t>
         </is>
       </c>
+      <c r="H398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -14382,6 +14796,7 @@
           <t>土地登記</t>
         </is>
       </c>
+      <c r="H399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -14417,6 +14832,7 @@
           <t>耕地分割、農業發展條例</t>
         </is>
       </c>
+      <c r="H400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -14452,6 +14868,7 @@
           <t>課予義務訴訟、補償處分、補償請求權、徵收土地</t>
         </is>
       </c>
+      <c r="H401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -14487,6 +14904,7 @@
           <t>標示分割、權利分割</t>
         </is>
       </c>
+      <c r="H402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -14522,6 +14940,7 @@
           <t>收回權、徵收補償</t>
         </is>
       </c>
+      <c r="H403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -14557,6 +14976,7 @@
           <t>重購退稅、土地增值稅、房地合一所得稅</t>
         </is>
       </c>
+      <c r="H404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -14592,6 +15012,7 @@
           <t>合併分割</t>
         </is>
       </c>
+      <c r="H405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -14627,6 +15048,7 @@
           <t>反共用地、共用地、土地利用、土地產權、財產權、土地私有制、土地國有制</t>
         </is>
       </c>
+      <c r="H406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -14662,6 +15084,7 @@
           <t>憲法法庭、憲法訴訟法、憲法審查、違憲、判決</t>
         </is>
       </c>
+      <c r="H407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -14697,6 +15120,7 @@
           <t>共用地悲劇、土地資源</t>
         </is>
       </c>
+      <c r="H408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -14732,6 +15156,7 @@
           <t>打炒房、不動產炒作、預售屋</t>
         </is>
       </c>
+      <c r="H409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -14767,6 +15192,7 @@
           <t>大陸地區繼承人、繼承權、不動產</t>
         </is>
       </c>
+      <c r="H410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -14802,6 +15228,7 @@
           <t>發展權、分區管制、國土計畫、都市計畫</t>
         </is>
       </c>
+      <c r="H411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -14837,6 +15264,7 @@
           <t>都市計畫變更、發展權、租利</t>
         </is>
       </c>
+      <c r="H412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -14872,6 +15300,7 @@
           <t>分管契約、共有物分割</t>
         </is>
       </c>
+      <c r="H413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -14907,6 +15336,7 @@
           <t>房價高漲、市場失靈、市場機制</t>
         </is>
       </c>
+      <c r="H414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -14942,6 +15372,7 @@
           <t>不動產役權、需役不動產、供役不動產、不動產登記簿</t>
         </is>
       </c>
+      <c r="H415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -14977,6 +15408,7 @@
           <t>通貨膨脹、疫情</t>
         </is>
       </c>
+      <c r="H416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -15012,6 +15444,7 @@
           <t>重建、都市計畫、老舊建築物、危險建築物</t>
         </is>
       </c>
+      <c r="H417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -15047,6 +15480,7 @@
           <t>土地法、徵收補償、土地徵收條例</t>
         </is>
       </c>
+      <c r="H418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -15082,6 +15516,7 @@
           <t>土地法、共有物分割、信託、所有權移轉</t>
         </is>
       </c>
+      <c r="H419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -15117,6 +15552,7 @@
           <t>囤房稅</t>
         </is>
       </c>
+      <c r="H420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -15152,6 +15588,7 @@
           <t>停滯性通貨膨脹、痛苦指數、菲力浦曲線、物價上漲率、失業率</t>
         </is>
       </c>
+      <c r="H421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -15187,6 +15624,7 @@
           <t>鄉村地區整體規劃、土地使用規劃原則</t>
         </is>
       </c>
+      <c r="H422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -15222,6 +15660,7 @@
           <t>通貨膨脹、不動產市場、不動產保值性</t>
         </is>
       </c>
+      <c r="H423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -15257,6 +15696,7 @@
           <t>農電共生、農地</t>
         </is>
       </c>
+      <c r="H424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -15292,6 +15732,7 @@
           <t>都市更新、重建、合法建築物、建築法</t>
         </is>
       </c>
+      <c r="H425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -15327,6 +15768,7 @@
           <t>地籍測量錯誤、登記錯誤、土地法、肯定說、否定說</t>
         </is>
       </c>
+      <c r="H426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -15362,6 +15804,7 @@
           <t>規劃利得、規劃損失</t>
         </is>
       </c>
+      <c r="H427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -15397,6 +15840,7 @@
           <t>自用住宅用地、土地稅法施行細則</t>
         </is>
       </c>
+      <c r="H428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -15432,6 +15876,7 @@
           <t>回復原狀請求權、回復請求權、民法第767條、土地法第12條</t>
         </is>
       </c>
+      <c r="H429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -15467,6 +15912,7 @@
           <t>土地分割、分割限制、土地登記</t>
         </is>
       </c>
+      <c r="H430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -15502,6 +15948,7 @@
           <t>不動產估價師</t>
         </is>
       </c>
+      <c r="H431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -15537,6 +15984,7 @@
           <t>共有不動產、共有不動產多數決、土地法第34條之1</t>
         </is>
       </c>
+      <c r="H432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -15572,6 +16020,7 @@
           <t>註記登記、行政處分、事實行為</t>
         </is>
       </c>
+      <c r="H433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -15607,6 +16056,7 @@
           <t>不動產經紀人、不實廣告、不動產經紀業管理條例、公平交易法、消費者保護法</t>
         </is>
       </c>
+      <c r="H434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -15642,6 +16092,7 @@
           <t>土地法、物權、耕地三七五減租條例、農地重劃條例、地籍清理條例</t>
         </is>
       </c>
+      <c r="H435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -15677,6 +16128,7 @@
           <t>註記登記、土地徵收、主登記、附記登記</t>
         </is>
       </c>
+      <c r="H436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -15712,6 +16164,7 @@
           <t>土地法、優先購買權、債權</t>
         </is>
       </c>
+      <c r="H437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -15747,6 +16200,7 @@
           <t>區段徵收、先行區段徵收、都市計畫</t>
         </is>
       </c>
+      <c r="H438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -15782,6 +16236,7 @@
           <t>住宅階梯</t>
         </is>
       </c>
+      <c r="H439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -15813,6 +16268,7 @@
         </is>
       </c>
       <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -15848,6 +16304,7 @@
           <t>更正登記</t>
         </is>
       </c>
+      <c r="H441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -15883,6 +16340,7 @@
           <t>融通物、不融通物</t>
         </is>
       </c>
+      <c r="H442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -15918,6 +16376,7 @@
           <t>成屋申報、預售屋申報、實價登錄</t>
         </is>
       </c>
+      <c r="H443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -15953,6 +16412,7 @@
           <t>土地登記、與登記有關第三人</t>
         </is>
       </c>
+      <c r="H444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -15988,6 +16448,7 @@
           <t>市地重劃、區段徵收</t>
         </is>
       </c>
+      <c r="H445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -16023,6 +16484,7 @@
           <t>土地法第34條</t>
         </is>
       </c>
+      <c r="H446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -16058,6 +16520,7 @@
           <t>房地合一</t>
         </is>
       </c>
+      <c r="H447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -16089,6 +16552,7 @@
         </is>
       </c>
       <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -16124,6 +16588,7 @@
           <t>房地合一稅、土地增值稅</t>
         </is>
       </c>
+      <c r="H449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -16159,6 +16624,7 @@
           <t>父母移轉不動產土地增值稅、契稅、所得稅</t>
         </is>
       </c>
+      <c r="H450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -16194,6 +16660,7 @@
           <t>永續發展目標、SDGs</t>
         </is>
       </c>
+      <c r="H451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -16229,6 +16696,7 @@
           <t>土地稅課徵、區域計畫法</t>
         </is>
       </c>
+      <c r="H452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -16264,6 +16732,7 @@
           <t>債權效力、優先購買權</t>
         </is>
       </c>
+      <c r="H453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -16299,6 +16768,7 @@
           <t>登記絕對效力、登記損害賠償</t>
         </is>
       </c>
+      <c r="H454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -16334,6 +16804,7 @@
           <t>地方創生</t>
         </is>
       </c>
+      <c r="H455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -16369,6 +16840,7 @@
           <t>登記絕對效力</t>
         </is>
       </c>
+      <c r="H456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -16404,6 +16876,7 @@
           <t>土地利用法規、開發許可</t>
         </is>
       </c>
+      <c r="H457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -16435,6 +16908,7 @@
         </is>
       </c>
       <c r="G458" t="inlineStr"/>
+      <c r="H458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -16470,6 +16944,7 @@
           <t>協議價購土地增值稅、土地增值稅</t>
         </is>
       </c>
+      <c r="H459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -16505,6 +16980,7 @@
           <t>公共設施保留地</t>
         </is>
       </c>
+      <c r="H460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -16540,6 +17016,7 @@
           <t>更生登記</t>
         </is>
       </c>
+      <c r="H461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -16575,6 +17052,7 @@
           <t>收回權</t>
         </is>
       </c>
+      <c r="H462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -16610,6 +17088,7 @@
           <t>土地登記</t>
         </is>
       </c>
+      <c r="H463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -16645,6 +17124,7 @@
           <t>房價高漲、房市泡沫</t>
         </is>
       </c>
+      <c r="H464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -16680,6 +17160,7 @@
           <t>登記錯誤</t>
         </is>
       </c>
+      <c r="H465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -16715,6 +17196,7 @@
           <t>房價高漲、房市泡沫</t>
         </is>
       </c>
+      <c r="H466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -16750,6 +17232,7 @@
           <t>更正登記、不妨礙原登記之同一性</t>
         </is>
       </c>
+      <c r="H467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -16785,6 +17268,7 @@
           <t>房價高漲、房市泡沫</t>
         </is>
       </c>
+      <c r="H468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -16820,6 +17304,7 @@
           <t>土地徵收</t>
         </is>
       </c>
+      <c r="H469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -16851,6 +17336,7 @@
         </is>
       </c>
       <c r="G470" t="inlineStr"/>
+      <c r="H470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -16886,6 +17372,7 @@
           <t>土地合併</t>
         </is>
       </c>
+      <c r="H471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -16917,6 +17404,7 @@
         </is>
       </c>
       <c r="G472" t="inlineStr"/>
+      <c r="H472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -16952,6 +17440,7 @@
           <t>實價登錄2.0</t>
         </is>
       </c>
+      <c r="H473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -16983,6 +17472,7 @@
         </is>
       </c>
       <c r="G474" t="inlineStr"/>
+      <c r="H474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -17018,6 +17508,7 @@
           <t>地籍圖重測、土地複丈</t>
         </is>
       </c>
+      <c r="H475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -17049,6 +17540,7 @@
         </is>
       </c>
       <c r="G476" t="inlineStr"/>
+      <c r="H476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -17084,6 +17576,7 @@
           <t>代理權說、處分權說</t>
         </is>
       </c>
+      <c r="H477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -17115,6 +17608,7 @@
         </is>
       </c>
       <c r="G478" t="inlineStr"/>
+      <c r="H478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -17150,6 +17644,7 @@
           <t>房地合一稅、預售屋</t>
         </is>
       </c>
+      <c r="H479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -17185,6 +17680,7 @@
           <t>負擔行為、處分行為</t>
         </is>
       </c>
+      <c r="H480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -17220,6 +17716,7 @@
           <t>遺產及贈與稅法、信託利益、遺產稅</t>
         </is>
       </c>
+      <c r="H481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -17255,6 +17752,7 @@
           <t>興建農舍</t>
         </is>
       </c>
+      <c r="H482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -17290,6 +17788,7 @@
           <t>稅捐稽徵法</t>
         </is>
       </c>
+      <c r="H483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -17325,6 +17824,7 @@
           <t>土地增值稅、納稅義務人、代繳義務人、代繳人</t>
         </is>
       </c>
+      <c r="H484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -17360,6 +17860,7 @@
           <t>遺產稅</t>
         </is>
       </c>
+      <c r="H485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -17395,6 +17896,7 @@
           <t>原地價、土地增值稅</t>
         </is>
       </c>
+      <c r="H486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -17430,6 +17932,7 @@
           <t>買賣不破租賃</t>
         </is>
       </c>
+      <c r="H487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -17465,6 +17968,7 @@
           <t>公共設施保留地、不動產估價</t>
         </is>
       </c>
+      <c r="H488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -17500,6 +18004,7 @@
           <t>地價稅</t>
         </is>
       </c>
+      <c r="H489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -17535,6 +18040,7 @@
           <t>適當利潤率、不動產估價</t>
         </is>
       </c>
+      <c r="H490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -17570,6 +18076,7 @@
           <t>老農、新農、農業用地興建農舍辦法、興建農舍</t>
         </is>
       </c>
+      <c r="H491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -17605,6 +18112,7 @@
           <t>權利變換</t>
         </is>
       </c>
+      <c r="H492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -17640,6 +18148,7 @@
           <t>優先購買權</t>
         </is>
       </c>
+      <c r="H493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -17671,6 +18180,7 @@
         </is>
       </c>
       <c r="G494" t="inlineStr"/>
+      <c r="H494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -17706,6 +18216,7 @@
           <t>時效取得地上權</t>
         </is>
       </c>
+      <c r="H495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -17737,6 +18248,7 @@
         </is>
       </c>
       <c r="G496" t="inlineStr"/>
+      <c r="H496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -17772,6 +18284,7 @@
           <t>以房養老、不動產逆向抵押貸款</t>
         </is>
       </c>
+      <c r="H497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -17803,6 +18316,7 @@
         </is>
       </c>
       <c r="G498" t="inlineStr"/>
+      <c r="H498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -17838,6 +18352,7 @@
           <t>多數決、優先購買、土地法34條之1</t>
         </is>
       </c>
+      <c r="H499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -17869,6 +18384,7 @@
         </is>
       </c>
       <c r="G500" t="inlineStr"/>
+      <c r="H500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -17904,6 +18420,7 @@
           <t>照價收買、原始取得、繼受取得</t>
         </is>
       </c>
+      <c r="H501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -17935,6 +18452,7 @@
         </is>
       </c>
       <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -17970,6 +18488,7 @@
           <t>房地合一稅</t>
         </is>
       </c>
+      <c r="H503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -18005,6 +18524,7 @@
           <t>發展權</t>
         </is>
       </c>
+      <c r="H504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -18040,6 +18560,7 @@
           <t>土地徵收補償、相當補償、完全補償</t>
         </is>
       </c>
+      <c r="H505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -18075,6 +18596,7 @@
           <t>共有土地分割、共有土地合併、土地法第34條之1</t>
         </is>
       </c>
+      <c r="H506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -18110,6 +18632,7 @@
           <t>雙地政士</t>
         </is>
       </c>
+      <c r="H507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -18145,6 +18668,7 @@
           <t>共有土地分割、共有土地合併、土地增值稅</t>
         </is>
       </c>
+      <c r="H508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -18180,6 +18704,7 @@
           <t>土地總登記、土地登記</t>
         </is>
       </c>
+      <c r="H509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -18215,6 +18740,7 @@
           <t>共有土地分割、共有土地合併、土地登記</t>
         </is>
       </c>
+      <c r="H510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -18250,6 +18776,7 @@
           <t>預售屋買賣定型化契約</t>
         </is>
       </c>
+      <c r="H511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -18285,6 +18812,7 @@
           <t>優先購買權、意定優先購買權、法定優先購買權</t>
         </is>
       </c>
+      <c r="H512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -18320,6 +18848,7 @@
           <t>土地徵收</t>
         </is>
       </c>
+      <c r="H513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -18355,6 +18884,7 @@
           <t>土地買賣未辦竣移轉登記</t>
         </is>
       </c>
+      <c r="H514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -18390,6 +18920,7 @@
           <t>三類謄本、土地登記</t>
         </is>
       </c>
+      <c r="H515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -18425,6 +18956,7 @@
           <t>預售屋轉售</t>
         </is>
       </c>
+      <c r="H516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -18460,6 +18992,7 @@
           <t>登記對抗</t>
         </is>
       </c>
+      <c r="H517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -18495,6 +19028,7 @@
           <t>土地登記損害賠償</t>
         </is>
       </c>
+      <c r="H518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -18530,6 +19064,7 @@
           <t>策略性更新地區、都市更新</t>
         </is>
       </c>
+      <c r="H519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -18561,6 +19096,7 @@
         </is>
       </c>
       <c r="G520" t="inlineStr"/>
+      <c r="H520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -18596,6 +19132,7 @@
           <t>土地登記</t>
         </is>
       </c>
+      <c r="H521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -18631,6 +19168,7 @@
           <t>不動產合併、不動產分割、權利合併、標示合併</t>
         </is>
       </c>
+      <c r="H522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -18666,6 +19204,7 @@
           <t>土地經濟學、需求曲線後彎</t>
         </is>
       </c>
+      <c r="H523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -18701,6 +19240,7 @@
           <t>紅單交易</t>
         </is>
       </c>
+      <c r="H524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -18736,6 +19276,7 @@
           <t>多數決、土地交換</t>
         </is>
       </c>
+      <c r="H525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -18767,6 +19308,7 @@
         </is>
       </c>
       <c r="G526" t="inlineStr"/>
+      <c r="H526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -18802,6 +19344,7 @@
           <t>區域計畫法、國土計畫法、開發影響費、國土保育費、影響費</t>
         </is>
       </c>
+      <c r="H527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -18833,6 +19376,7 @@
         </is>
       </c>
       <c r="G528" t="inlineStr"/>
+      <c r="H528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -18868,6 +19412,7 @@
           <t>出售農地、房地合一所得稅</t>
         </is>
       </c>
+      <c r="H529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -18903,6 +19448,7 @@
           <t>地價稅、房屋稅</t>
         </is>
       </c>
+      <c r="H530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -18938,6 +19484,7 @@
           <t>土地買賣、土地買賣未辦竣權利移轉登記</t>
         </is>
       </c>
+      <c r="H531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -18969,6 +19516,7 @@
         </is>
       </c>
       <c r="G532" t="inlineStr"/>
+      <c r="H532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -19004,6 +19552,7 @@
           <t>註記登記、訴訟繫屬事實註記</t>
         </is>
       </c>
+      <c r="H533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -19035,6 +19584,7 @@
         </is>
       </c>
       <c r="G534" t="inlineStr"/>
+      <c r="H534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -19070,6 +19620,7 @@
           <t>市地重劃、區段徵收、土地增值稅</t>
         </is>
       </c>
+      <c r="H535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -19105,6 +19656,7 @@
           <t>預告登記</t>
         </is>
       </c>
+      <c r="H536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -19140,6 +19692,7 @@
           <t>登記錯誤、錯誤登記</t>
         </is>
       </c>
+      <c r="H537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -19171,6 +19724,7 @@
         </is>
       </c>
       <c r="G538" t="inlineStr"/>
+      <c r="H538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -19206,6 +19760,7 @@
           <t>租賃住宅市場發展及管理條例、租賃關係消滅</t>
         </is>
       </c>
+      <c r="H539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -19241,6 +19796,7 @@
           <t>不動產</t>
         </is>
       </c>
+      <c r="H540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -19276,6 +19832,7 @@
           <t>預告登記</t>
         </is>
       </c>
+      <c r="H541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -19311,6 +19868,7 @@
           <t>地號、建號</t>
         </is>
       </c>
+      <c r="H542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -19342,6 +19900,7 @@
         </is>
       </c>
       <c r="G543" t="inlineStr"/>
+      <c r="H543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -19377,6 +19936,7 @@
           <t>申報移轉現值</t>
         </is>
       </c>
+      <c r="H544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -19412,6 +19972,7 @@
           <t>公寓大廈管理條例</t>
         </is>
       </c>
+      <c r="H545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -19447,6 +20008,7 @@
           <t>申報地價</t>
         </is>
       </c>
+      <c r="H546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -19482,6 +20044,7 @@
           <t>土地登記、分管契約</t>
         </is>
       </c>
+      <c r="H547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -19517,6 +20080,7 @@
           <t>剩餘財產差額</t>
         </is>
       </c>
+      <c r="H548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -19552,6 +20116,7 @@
           <t>斡旋金、要約書</t>
         </is>
       </c>
+      <c r="H549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -19587,6 +20152,7 @@
           <t>遺贈</t>
         </is>
       </c>
+      <c r="H550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -19622,6 +20188,7 @@
           <t>處分、信託行為、多數決</t>
         </is>
       </c>
+      <c r="H551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -19657,6 +20224,7 @@
           <t>債權物權化、三七五租約、租賃權、物權</t>
         </is>
       </c>
+      <c r="H552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -19692,6 +20260,7 @@
           <t>處分、共有物權利分割</t>
         </is>
       </c>
+      <c r="H553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -19727,6 +20296,7 @@
           <t>公告地價、公告土地現值、兩價</t>
         </is>
       </c>
+      <c r="H554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -19762,6 +20332,7 @@
           <t>再轉繼承、代位繼承</t>
         </is>
       </c>
+      <c r="H555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -19797,6 +20368,7 @@
           <t>實價登錄、房地合一所得稅、個人綜合所得稅</t>
         </is>
       </c>
+      <c r="H556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -19832,6 +20404,7 @@
           <t>土地登記、私權爭執</t>
         </is>
       </c>
+      <c r="H557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -19867,6 +20440,7 @@
           <t>工程受益費、土地增值稅</t>
         </is>
       </c>
+      <c r="H558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -19902,6 +20476,7 @@
           <t>繼承登記、拋棄繼承、土地登記規則</t>
         </is>
       </c>
+      <c r="H559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -19937,6 +20512,7 @@
           <t>新冠肺炎、不動產市場</t>
         </is>
       </c>
+      <c r="H560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -19972,6 +20548,7 @@
           <t>都市更新條例、都市更新事業計畫同意比率</t>
         </is>
       </c>
+      <c r="H561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -20007,6 +20584,7 @@
           <t>實價登錄</t>
         </is>
       </c>
+      <c r="H562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -20042,6 +20620,7 @@
           <t>都市更新條例、都市更新權利變換代拆機制、權利變換計畫</t>
         </is>
       </c>
+      <c r="H563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -20077,6 +20656,7 @@
           <t>房地合一所得稅</t>
         </is>
       </c>
+      <c r="H564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -20112,6 +20692,7 @@
           <t>容積、容積獎勵、容積移轉、增額容積、容積折繳代金、容積銀行制度</t>
         </is>
       </c>
+      <c r="H565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -20143,6 +20724,7 @@
         </is>
       </c>
       <c r="G566" t="inlineStr"/>
+      <c r="H566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -20178,6 +20760,7 @@
           <t>都市計畫</t>
         </is>
       </c>
+      <c r="H567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -20213,6 +20796,7 @@
           <t>累進稅、倍數累進、金額累進、土地增值稅</t>
         </is>
       </c>
+      <c r="H568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -20244,6 +20828,7 @@
         </is>
       </c>
       <c r="G569" t="inlineStr"/>
+      <c r="H569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -20279,6 +20864,7 @@
           <t>累進稅、比例稅、土地增值稅</t>
         </is>
       </c>
+      <c r="H570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -20310,6 +20896,7 @@
         </is>
       </c>
       <c r="G571" t="inlineStr"/>
+      <c r="H571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -20345,6 +20932,7 @@
           <t>信託法</t>
         </is>
       </c>
+      <c r="H572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -20380,6 +20968,7 @@
           <t>公益信託</t>
         </is>
       </c>
+      <c r="H573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -20415,6 +21004,7 @@
           <t>土地分割</t>
         </is>
       </c>
+      <c r="H574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -20450,6 +21040,7 @@
           <t>開發許可</t>
         </is>
       </c>
+      <c r="H575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -20481,6 +21072,7 @@
         </is>
       </c>
       <c r="G576" t="inlineStr"/>
+      <c r="H576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -20516,6 +21108,7 @@
           <t>住宅市場</t>
         </is>
       </c>
+      <c r="H577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -20547,6 +21140,7 @@
         </is>
       </c>
       <c r="G578" t="inlineStr"/>
+      <c r="H578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -20582,6 +21176,7 @@
           <t>與登記有關之第三人</t>
         </is>
       </c>
+      <c r="H579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -20613,6 +21208,7 @@
         </is>
       </c>
       <c r="G580" t="inlineStr"/>
+      <c r="H580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -20648,6 +21244,7 @@
           <t>信託登記、公示性</t>
         </is>
       </c>
+      <c r="H581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -20679,6 +21276,7 @@
         </is>
       </c>
       <c r="G582" t="inlineStr"/>
+      <c r="H582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -20714,6 +21312,7 @@
           <t>國土計畫法修法、國土計畫</t>
         </is>
       </c>
+      <c r="H583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -20745,6 +21344,7 @@
         </is>
       </c>
       <c r="G584" t="inlineStr"/>
+      <c r="H584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -20780,6 +21380,7 @@
           <t>線上聲明、土地登記</t>
         </is>
       </c>
+      <c r="H585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -20815,6 +21416,7 @@
           <t>占有契稅</t>
         </is>
       </c>
+      <c r="H586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -20850,6 +21452,7 @@
           <t>區段地價、公告地價、公告現值、申報地價、申報移轉現值、徵收補償市價、市場正常交易價格</t>
         </is>
       </c>
+      <c r="H587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -20881,6 +21484,7 @@
         </is>
       </c>
       <c r="G588" t="inlineStr"/>
+      <c r="H588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -20916,6 +21520,7 @@
           <t>共有優先購買權</t>
         </is>
       </c>
+      <c r="H589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -20947,6 +21552,7 @@
         </is>
       </c>
       <c r="G590" t="inlineStr"/>
+      <c r="H590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -20982,6 +21588,7 @@
           <t>共有優先購買權</t>
         </is>
       </c>
+      <c r="H591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -21017,6 +21624,7 @@
           <t>優先購買權、債權性質優先購買權、物權性質優先購買權</t>
         </is>
       </c>
+      <c r="H592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -21052,6 +21660,7 @@
           <t>共有優先購買權</t>
         </is>
       </c>
+      <c r="H593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -21083,6 +21692,7 @@
         </is>
       </c>
       <c r="G594" t="inlineStr"/>
+      <c r="H594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -21118,6 +21728,7 @@
           <t>共有優先購買權</t>
         </is>
       </c>
+      <c r="H595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -21149,6 +21760,7 @@
         </is>
       </c>
       <c r="G596" t="inlineStr"/>
+      <c r="H596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -21184,6 +21796,7 @@
           <t>土地法第34條</t>
         </is>
       </c>
+      <c r="H597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -21215,6 +21828,7 @@
         </is>
       </c>
       <c r="G598" t="inlineStr"/>
+      <c r="H598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -21250,6 +21864,7 @@
           <t>信託、委任</t>
         </is>
       </c>
+      <c r="H599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -21285,6 +21900,7 @@
           <t>跨縣市土地登記、土地登記</t>
         </is>
       </c>
+      <c r="H600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -21316,6 +21932,7 @@
         </is>
       </c>
       <c r="G601" t="inlineStr"/>
+      <c r="H601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -21351,6 +21968,7 @@
           <t>山坡地保育區、山坡地、原住民保留地</t>
         </is>
       </c>
+      <c r="H602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -21386,6 +22004,7 @@
           <t>公有土地、市地重劃、土地法第25條</t>
         </is>
       </c>
+      <c r="H603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -21417,6 +22036,7 @@
         </is>
       </c>
       <c r="G604" t="inlineStr"/>
+      <c r="H604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -21452,6 +22072,7 @@
           <t>土地登記、強制登記</t>
         </is>
       </c>
+      <c r="H605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -21483,6 +22104,7 @@
         </is>
       </c>
       <c r="G606" t="inlineStr"/>
+      <c r="H606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -21518,6 +22140,7 @@
           <t>土地登記</t>
         </is>
       </c>
+      <c r="H607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -21553,6 +22176,7 @@
           <t>典權、典權期限、典權人</t>
         </is>
       </c>
+      <c r="H608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -21584,6 +22208,7 @@
         </is>
       </c>
       <c r="G609" t="inlineStr"/>
+      <c r="H609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -21619,6 +22244,7 @@
           <t>實質審查、形式審查</t>
         </is>
       </c>
+      <c r="H610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -21650,6 +22276,7 @@
         </is>
       </c>
       <c r="G611" t="inlineStr"/>
+      <c r="H611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -21685,6 +22312,7 @@
           <t>程序正義</t>
         </is>
       </c>
+      <c r="H612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -21716,6 +22344,7 @@
         </is>
       </c>
       <c r="G613" t="inlineStr"/>
+      <c r="H613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -21751,6 +22380,7 @@
           <t>比例原則、禁止過度原則、行政程序法、土地法規</t>
         </is>
       </c>
+      <c r="H614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -21782,6 +22412,7 @@
         </is>
       </c>
       <c r="G615" t="inlineStr"/>
+      <c r="H615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -21817,6 +22448,7 @@
           <t>市場失靈、市場價格</t>
         </is>
       </c>
+      <c r="H616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -21852,6 +22484,7 @@
           <t>土地增值稅</t>
         </is>
       </c>
+      <c r="H617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -21887,6 +22520,7 @@
           <t>贈與不動產、土地增值稅</t>
         </is>
       </c>
+      <c r="H618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -21922,6 +22556,7 @@
           <t>耕作權</t>
         </is>
       </c>
+      <c r="H619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -21953,6 +22588,7 @@
         </is>
       </c>
       <c r="G620" t="inlineStr"/>
+      <c r="H620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -21988,6 +22624,7 @@
           <t>浮覆地</t>
         </is>
       </c>
+      <c r="H621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -22023,6 +22660,7 @@
           <t>使用基地之證明文件、建物所有權</t>
         </is>
       </c>
+      <c r="H622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -22054,6 +22692,7 @@
         </is>
       </c>
       <c r="G623" t="inlineStr"/>
+      <c r="H623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -22089,6 +22728,7 @@
           <t>土地登記規則、補正、駁回</t>
         </is>
       </c>
+      <c r="H624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -22120,6 +22760,7 @@
         </is>
       </c>
       <c r="G625" t="inlineStr"/>
+      <c r="H625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -22155,6 +22796,7 @@
           <t>土地登記</t>
         </is>
       </c>
+      <c r="H626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -22186,6 +22828,7 @@
         </is>
       </c>
       <c r="G627" t="inlineStr"/>
+      <c r="H627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -22221,6 +22864,7 @@
           <t>土地徵收要件</t>
         </is>
       </c>
+      <c r="H628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -22252,6 +22896,7 @@
         </is>
       </c>
       <c r="G629" t="inlineStr"/>
+      <c r="H629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -22287,6 +22932,7 @@
           <t>不動產相關定型化契約</t>
         </is>
       </c>
+      <c r="H630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -22318,6 +22964,7 @@
         </is>
       </c>
       <c r="G631" t="inlineStr"/>
+      <c r="H631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -22353,6 +23000,7 @@
           <t>土地法第12條、土地浮覆</t>
         </is>
       </c>
+      <c r="H632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -22384,6 +23032,7 @@
         </is>
       </c>
       <c r="G633" t="inlineStr"/>
+      <c r="H633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -22419,6 +23068,7 @@
           <t>釋字774、釋字156</t>
         </is>
       </c>
+      <c r="H634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -22454,6 +23104,7 @@
           <t>工業用地、工業區</t>
         </is>
       </c>
+      <c r="H635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -22489,6 +23140,7 @@
           <t>囤房、囤房稅、房屋稅</t>
         </is>
       </c>
+      <c r="H636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -22520,6 +23172,7 @@
         </is>
       </c>
       <c r="G637" t="inlineStr"/>
+      <c r="H637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -22555,6 +23208,7 @@
           <t>不動產市場、不完全競爭市場、非自由競爭市場</t>
         </is>
       </c>
+      <c r="H638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -22590,6 +23244,7 @@
           <t>自耕農、地主</t>
         </is>
       </c>
+      <c r="H639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -22625,6 +23280,7 @@
           <t>房地合一稅</t>
         </is>
       </c>
+      <c r="H640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -22656,6 +23312,7 @@
         </is>
       </c>
       <c r="G641" t="inlineStr"/>
+      <c r="H641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -22691,6 +23348,7 @@
           <t>規約</t>
         </is>
       </c>
+      <c r="H642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -22722,6 +23380,7 @@
         </is>
       </c>
       <c r="G643" t="inlineStr"/>
+      <c r="H643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -22757,6 +23416,7 @@
           <t>照價收買、繼受取得、原始取得</t>
         </is>
       </c>
+      <c r="H644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -22788,6 +23448,7 @@
         </is>
       </c>
       <c r="G645" t="inlineStr"/>
+      <c r="H645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -22823,6 +23484,7 @@
           <t>土地增值稅</t>
         </is>
       </c>
+      <c r="H646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -22854,6 +23516,7 @@
         </is>
       </c>
       <c r="G647" t="inlineStr"/>
+      <c r="H647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -22889,6 +23552,7 @@
           <t>釋字第779號</t>
         </is>
       </c>
+      <c r="H648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -22920,6 +23584,7 @@
         </is>
       </c>
       <c r="G649" t="inlineStr"/>
+      <c r="H649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -22955,6 +23620,7 @@
           <t>實價登錄、平均地權條例</t>
         </is>
       </c>
+      <c r="H650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -22986,6 +23652,7 @@
         </is>
       </c>
       <c r="G651" t="inlineStr"/>
+      <c r="H651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="n">
@@ -23021,6 +23688,7 @@
           <t>土地法第104條、優先購買權</t>
         </is>
       </c>
+      <c r="H652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -23052,6 +23720,7 @@
         </is>
       </c>
       <c r="G653" t="inlineStr"/>
+      <c r="H653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -23087,6 +23756,7 @@
           <t>土地重測、土地重劃</t>
         </is>
       </c>
+      <c r="H654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="n">
@@ -23118,6 +23788,7 @@
         </is>
       </c>
       <c r="G655" t="inlineStr"/>
+      <c r="H655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="n">
@@ -23153,6 +23824,7 @@
           <t>危老條例</t>
         </is>
       </c>
+      <c r="H656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -23184,6 +23856,7 @@
         </is>
       </c>
       <c r="G657" t="inlineStr"/>
+      <c r="H657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -23219,6 +23892,7 @@
           <t>多數決、優先購買、土地法第34條之1</t>
         </is>
       </c>
+      <c r="H658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="n">
@@ -23250,6 +23924,7 @@
         </is>
       </c>
       <c r="G659" t="inlineStr"/>
+      <c r="H659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="n">
@@ -23285,6 +23960,7 @@
           <t>原始取得、繼受取得、市地重劃</t>
         </is>
       </c>
+      <c r="H660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="n">
@@ -23316,6 +23992,7 @@
         </is>
       </c>
       <c r="G661" t="inlineStr"/>
+      <c r="H661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" t="n">
@@ -23351,6 +24028,7 @@
           <t>房地合一稅</t>
         </is>
       </c>
+      <c r="H662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="n">
@@ -23386,6 +24064,7 @@
           <t>流抵約定、絕賣條款</t>
         </is>
       </c>
+      <c r="H663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="n">
@@ -23421,6 +24100,7 @@
           <t>釋字732</t>
         </is>
       </c>
+      <c r="H664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" t="n">
@@ -23452,6 +24132,7 @@
         </is>
       </c>
       <c r="G665" t="inlineStr"/>
+      <c r="H665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="n">
@@ -23487,6 +24168,7 @@
           <t>人口數量、人口結構、人口流動</t>
         </is>
       </c>
+      <c r="H666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="n">
@@ -23518,6 +24200,7 @@
         </is>
       </c>
       <c r="G667" t="inlineStr"/>
+      <c r="H667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="n">
@@ -23553,6 +24236,7 @@
           <t>土地法</t>
         </is>
       </c>
+      <c r="H668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" t="n">
@@ -23584,6 +24268,7 @@
         </is>
       </c>
       <c r="G669" t="inlineStr"/>
+      <c r="H669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="n">
@@ -23619,6 +24304,7 @@
           <t>土地正義</t>
         </is>
       </c>
+      <c r="H670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="n">
@@ -23650,6 +24336,7 @@
         </is>
       </c>
       <c r="G671" t="inlineStr"/>
+      <c r="H671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" t="n">
@@ -23685,6 +24372,7 @@
           <t>耕地收回補償、耕地三七五減租</t>
         </is>
       </c>
+      <c r="H672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="n">
@@ -23720,6 +24408,7 @@
           <t>土地法第107條</t>
         </is>
       </c>
+      <c r="H673" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" t="n">
@@ -23755,6 +24444,7 @@
           <t>全國國土計畫、輔導合法化之原則</t>
         </is>
       </c>
+      <c r="H674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" t="n">
@@ -23786,6 +24476,7 @@
         </is>
       </c>
       <c r="G675" t="inlineStr"/>
+      <c r="H675" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" t="n">
@@ -23821,6 +24512,7 @@
           <t>形式審查、實質審查、虛偽登記</t>
         </is>
       </c>
+      <c r="H676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" t="n">
@@ -23856,6 +24548,7 @@
           <t>土地參考資訊檔</t>
         </is>
       </c>
+      <c r="H677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="n">
@@ -23891,6 +24584,7 @@
           <t>信託法概要、信託關係、信託關係消滅、信託目的</t>
         </is>
       </c>
+      <c r="H678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" t="n">
@@ -23922,6 +24616,7 @@
         </is>
       </c>
       <c r="G679" t="inlineStr"/>
+      <c r="H679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" t="n">
@@ -23957,6 +24652,7 @@
           <t>原地價、減徵、土地增值稅</t>
         </is>
       </c>
+      <c r="H680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" t="n">
@@ -23988,6 +24684,7 @@
         </is>
       </c>
       <c r="G681" t="inlineStr"/>
+      <c r="H681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="n">
@@ -24023,6 +24720,7 @@
           <t>地方創生、土地政策與利用</t>
         </is>
       </c>
+      <c r="H682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="n">
@@ -24058,6 +24756,7 @@
           <t>公共設施保留地、公共設施保留地 地價</t>
         </is>
       </c>
+      <c r="H683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="n">
@@ -24093,6 +24792,7 @@
           <t>容積移轉、公共設施保留地</t>
         </is>
       </c>
+      <c r="H684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="n">
@@ -24128,6 +24828,7 @@
           <t>地號、建號</t>
         </is>
       </c>
+      <c r="H685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="n">
@@ -24163,6 +24864,7 @@
           <t>土地增值稅、重劃後移轉減徵</t>
         </is>
       </c>
+      <c r="H686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" t="n">
@@ -24198,6 +24900,7 @@
           <t>地上權</t>
         </is>
       </c>
+      <c r="H687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="n">
@@ -24233,6 +24936,7 @@
           <t>土地增值稅、房地合一稅、土地稅重購退稅</t>
         </is>
       </c>
+      <c r="H688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" t="n">
@@ -24264,6 +24968,7 @@
         </is>
       </c>
       <c r="G689" t="inlineStr"/>
+      <c r="H689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="n">
@@ -24299,6 +25004,7 @@
           <t>抵價地、抵費地</t>
         </is>
       </c>
+      <c r="H690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" t="n">
@@ -24334,6 +25040,7 @@
           <t>民法第759條</t>
         </is>
       </c>
+      <c r="H691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="n">
@@ -24369,6 +25076,7 @@
           <t>區段徵收、租賃權</t>
         </is>
       </c>
+      <c r="H692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="n">
@@ -24400,6 +25108,7 @@
         </is>
       </c>
       <c r="G693" t="inlineStr"/>
+      <c r="H693" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" t="n">
@@ -24435,6 +25144,7 @@
           <t>徵收補償、相當補償、完全補償</t>
         </is>
       </c>
+      <c r="H694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" t="n">
@@ -24466,6 +25176,7 @@
         </is>
       </c>
       <c r="G695" t="inlineStr"/>
+      <c r="H695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" t="n">
@@ -24501,6 +25212,7 @@
           <t>信託財產、信託財產獨立性、信託法</t>
         </is>
       </c>
+      <c r="H696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="n">
@@ -24536,6 +25248,7 @@
           <t>更正登記、不妨礙原登記之同一性</t>
         </is>
       </c>
+      <c r="H697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="n">
@@ -24571,6 +25284,7 @@
           <t>聽證、土地徵收、土地重劃、都市更新</t>
         </is>
       </c>
+      <c r="H698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="n">
@@ -24606,6 +25320,7 @@
           <t>都市更新事業、都市更新條例</t>
         </is>
       </c>
+      <c r="H699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" t="n">
@@ -24641,6 +25356,7 @@
           <t>區段徵收</t>
         </is>
       </c>
+      <c r="H700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="n">
@@ -24676,6 +25392,7 @@
           <t>更新單元、都市更新條例</t>
         </is>
       </c>
+      <c r="H701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="n">
@@ -24707,6 +25424,7 @@
         </is>
       </c>
       <c r="G702" t="inlineStr"/>
+      <c r="H702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="n">
@@ -24742,6 +25460,7 @@
           <t>都市更新、重建區段、協議合建、權利變換</t>
         </is>
       </c>
+      <c r="H703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="n">
@@ -24773,6 +25492,7 @@
         </is>
       </c>
       <c r="G704" t="inlineStr"/>
+      <c r="H704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="n">
@@ -24808,6 +25528,7 @@
           <t>信託財產、信託財產獨立性</t>
         </is>
       </c>
+      <c r="H705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="n">
@@ -24839,6 +25560,7 @@
         </is>
       </c>
       <c r="G706" t="inlineStr"/>
+      <c r="H706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="n">
@@ -24874,6 +25596,7 @@
           <t>地價、區段地價、申報地價</t>
         </is>
       </c>
+      <c r="H707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="n">
@@ -24909,6 +25632,7 @@
           <t>更正登記</t>
         </is>
       </c>
+      <c r="H708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="n">
@@ -24940,6 +25664,7 @@
         </is>
       </c>
       <c r="G709" t="inlineStr"/>
+      <c r="H709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="n">
@@ -24971,6 +25696,7 @@
         </is>
       </c>
       <c r="G710" t="inlineStr"/>
+      <c r="H710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="n">
@@ -25006,6 +25732,7 @@
           <t>信賴保護原則</t>
         </is>
       </c>
+      <c r="H711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="n">
@@ -25041,6 +25768,7 @@
           <t>優先購買權</t>
         </is>
       </c>
+      <c r="H712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="n">
@@ -25076,6 +25804,7 @@
           <t>釋字774</t>
         </is>
       </c>
+      <c r="H713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="n">
@@ -25111,6 +25840,7 @@
           <t>優先購買權</t>
         </is>
       </c>
+      <c r="H714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="n">
@@ -25146,6 +25876,7 @@
           <t>租賃住宅市場發展及管理條例、土地法</t>
         </is>
       </c>
+      <c r="H715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="n">
@@ -25181,6 +25912,7 @@
           <t>抵押權</t>
         </is>
       </c>
+      <c r="H716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="n">
@@ -25216,6 +25948,7 @@
           <t>全國國土計畫、違章工廠</t>
         </is>
       </c>
+      <c r="H717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="n">
@@ -25247,6 +25980,7 @@
         </is>
       </c>
       <c r="G718" t="inlineStr"/>
+      <c r="H718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="n">
@@ -25282,6 +26016,7 @@
           <t>土地參考資訊檔、土地登記</t>
         </is>
       </c>
+      <c r="H719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="n">
@@ -25317,6 +26052,7 @@
           <t>地上權、所有權分離</t>
         </is>
       </c>
+      <c r="H720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="n">
@@ -25352,6 +26088,7 @@
           <t>釋字765、土地徵收條例</t>
         </is>
       </c>
+      <c r="H721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="n">
@@ -25383,6 +26120,7 @@
         </is>
       </c>
       <c r="G722" t="inlineStr"/>
+      <c r="H722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="n">
@@ -25418,6 +26156,7 @@
           <t>地上權、土地登記</t>
         </is>
       </c>
+      <c r="H723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="n">
@@ -25449,6 +26188,7 @@
         </is>
       </c>
       <c r="G724" t="inlineStr"/>
+      <c r="H724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="n">
@@ -25484,6 +26224,7 @@
           <t>財產權保障、存續保障、價值保障</t>
         </is>
       </c>
+      <c r="H725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="n">
@@ -25515,6 +26256,7 @@
         </is>
       </c>
       <c r="G726" t="inlineStr"/>
+      <c r="H726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" t="n">
@@ -25546,6 +26288,7 @@
         </is>
       </c>
       <c r="G727" t="inlineStr"/>
+      <c r="H727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="n">
@@ -25577,6 +26320,7 @@
         </is>
       </c>
       <c r="G728" t="inlineStr"/>
+      <c r="H728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" t="n">
@@ -25612,6 +26356,7 @@
           <t>登記錯誤、錯誤登記</t>
         </is>
       </c>
+      <c r="H729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="n">
@@ -25643,6 +26388,7 @@
         </is>
       </c>
       <c r="G730" t="inlineStr"/>
+      <c r="H730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" t="n">
@@ -25674,6 +26420,7 @@
         </is>
       </c>
       <c r="G731" t="inlineStr"/>
+      <c r="H731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" t="n">
@@ -25705,6 +26452,7 @@
         </is>
       </c>
       <c r="G732" t="inlineStr"/>
+      <c r="H732" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" t="n">
@@ -25740,6 +26488,7 @@
           <t>市地重劃</t>
         </is>
       </c>
+      <c r="H733" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" t="n">
@@ -25775,6 +26524,7 @@
           <t>繼承登記</t>
         </is>
       </c>
+      <c r="H734" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" t="n">
@@ -25806,6 +26556,7 @@
         </is>
       </c>
       <c r="G735" t="inlineStr"/>
+      <c r="H735" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" t="n">
@@ -25841,6 +26592,7 @@
           <t>土地增值稅</t>
         </is>
       </c>
+      <c r="H736" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" t="n">
@@ -25876,6 +26628,7 @@
           <t>市地重劃</t>
         </is>
       </c>
+      <c r="H737" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" t="n">
@@ -25911,6 +26664,7 @@
           <t>不動產經紀人、房屋租賃、住宅租賃</t>
         </is>
       </c>
+      <c r="H738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" t="n">
@@ -25942,6 +26696,7 @@
         </is>
       </c>
       <c r="G739" t="inlineStr"/>
+      <c r="H739" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" t="n">
@@ -25977,6 +26732,7 @@
           <t>預告登記</t>
         </is>
       </c>
+      <c r="H740" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" t="n">
@@ -26012,6 +26768,7 @@
           <t>區段徵收、市地重劃、抵價地、抵費地</t>
         </is>
       </c>
+      <c r="H741" t="inlineStr"/>
     </row>
     <row r="742">
       <c r="A742" t="n">
@@ -26043,6 +26800,7 @@
         </is>
       </c>
       <c r="G742" t="inlineStr"/>
+      <c r="H742" t="inlineStr"/>
     </row>
     <row r="743">
       <c r="A743" t="n">
@@ -26074,6 +26832,7 @@
         </is>
       </c>
       <c r="G743" t="inlineStr"/>
+      <c r="H743" t="inlineStr"/>
     </row>
     <row r="744">
       <c r="A744" t="n">
@@ -26109,6 +26868,7 @@
           <t>房屋租賃、住宅租賃契約、成屋買賣、預售屋買賣</t>
         </is>
       </c>
+      <c r="H744" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" t="n">
@@ -26140,6 +26900,7 @@
         </is>
       </c>
       <c r="G745" t="inlineStr"/>
+      <c r="H745" t="inlineStr"/>
     </row>
     <row r="746">
       <c r="A746" t="n">
@@ -26175,6 +26936,7 @@
           <t>危老條例</t>
         </is>
       </c>
+      <c r="H746" t="inlineStr"/>
     </row>
     <row r="747">
       <c r="A747" t="n">
@@ -26210,6 +26972,7 @@
           <t>共有物所有權</t>
         </is>
       </c>
+      <c r="H747" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" t="n">
@@ -26245,6 +27008,7 @@
           <t>夫妻間贈與、土地增值稅、契稅</t>
         </is>
       </c>
+      <c r="H748" t="inlineStr"/>
     </row>
     <row r="749">
       <c r="A749" t="n">
@@ -26280,6 +27044,7 @@
           <t>共有物所有權</t>
         </is>
       </c>
+      <c r="H749" t="inlineStr"/>
     </row>
     <row r="750">
       <c r="A750" t="n">
@@ -26315,6 +27080,7 @@
           <t>土地稅減免、地價稅減徵</t>
         </is>
       </c>
+      <c r="H750" t="inlineStr"/>
     </row>
     <row r="751">
       <c r="A751" t="n">
@@ -26350,6 +27116,7 @@
           <t>土地法第104條、優先購買權、擴大解釋、類推適用</t>
         </is>
       </c>
+      <c r="H751" t="inlineStr"/>
     </row>
     <row r="752">
       <c r="A752" t="n">
@@ -26385,6 +27152,7 @@
           <t>土地法第12條、浮覆地、土地所有權、視為消滅</t>
         </is>
       </c>
+      <c r="H752" t="inlineStr"/>
     </row>
     <row r="753">
       <c r="A753" t="n">
@@ -26420,6 +27188,7 @@
           <t>地上權、優先購買權</t>
         </is>
       </c>
+      <c r="H753" t="inlineStr"/>
     </row>
     <row r="754">
       <c r="A754" t="n">
@@ -26455,6 +27224,7 @@
           <t>贈與稅、遺產、地上權、永佃權、典權</t>
         </is>
       </c>
+      <c r="H754" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" t="n">
@@ -26490,6 +27260,7 @@
           <t>不動產信託、不動產管理信託、不動產處分信託、不動產開發信託</t>
         </is>
       </c>
+      <c r="H755" t="inlineStr"/>
     </row>
     <row r="756">
       <c r="A756" t="n">
@@ -26525,6 +27296,7 @@
           <t>地上權、典權、租賃權</t>
         </is>
       </c>
+      <c r="H756" t="inlineStr"/>
     </row>
     <row r="757">
       <c r="A757" t="n">
@@ -26560,6 +27332,7 @@
           <t>繼承登記、土地所有權、地上權</t>
         </is>
       </c>
+      <c r="H757" t="inlineStr"/>
     </row>
     <row r="758">
       <c r="A758" t="n">
@@ -26595,6 +27368,7 @@
           <t>測量錯誤、登記錯誤</t>
         </is>
       </c>
+      <c r="H758" t="inlineStr"/>
     </row>
     <row r="759">
       <c r="A759" t="n">
@@ -26630,6 +27404,7 @@
           <t>土地登記漏誤、更正登記、塗銷登記、登記損害賠償</t>
         </is>
       </c>
+      <c r="H759" t="inlineStr"/>
     </row>
     <row r="760">
       <c r="A760" t="n">
@@ -26665,6 +27440,7 @@
           <t>定型化契約不得記載事項、不得記載事項、定型化契約</t>
         </is>
       </c>
+      <c r="H760" t="inlineStr"/>
     </row>
     <row r="761">
       <c r="A761" t="n">
@@ -26700,6 +27476,7 @@
           <t>更正登記、土地登記、登記錯誤、登記遺漏</t>
         </is>
       </c>
+      <c r="H761" t="inlineStr"/>
     </row>
     <row r="762">
       <c r="A762" t="n">
@@ -26735,6 +27512,7 @@
           <t>危老條例</t>
         </is>
       </c>
+      <c r="H762" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" t="n">
@@ -26770,6 +27548,7 @@
           <t>更正登記、同一性</t>
         </is>
       </c>
+      <c r="H763" t="inlineStr"/>
     </row>
     <row r="764">
       <c r="A764" t="n">
@@ -26805,6 +27584,7 @@
           <t>租賃住宅服務業、租賃住宅</t>
         </is>
       </c>
+      <c r="H764" t="inlineStr"/>
     </row>
     <row r="765">
       <c r="A765" t="n">
@@ -26840,6 +27620,7 @@
           <t>非都市土地、再生能源相關設施</t>
         </is>
       </c>
+      <c r="H765" t="inlineStr"/>
     </row>
     <row r="766">
       <c r="A766" t="n">
@@ -26875,6 +27656,7 @@
           <t>房屋稅</t>
         </is>
       </c>
+      <c r="H766" t="inlineStr"/>
     </row>
     <row r="767">
       <c r="A767" t="n">
@@ -26910,6 +27692,7 @@
           <t>新古典經濟學、新制度經濟學</t>
         </is>
       </c>
+      <c r="H767" t="inlineStr"/>
     </row>
     <row r="768">
       <c r="A768" t="n">
@@ -26945,6 +27728,7 @@
           <t>土地增值稅、土地稅法</t>
         </is>
       </c>
+      <c r="H768" t="inlineStr"/>
     </row>
     <row r="769">
       <c r="A769" t="n">
@@ -26980,6 +27764,7 @@
           <t>全國國土計畫、土地利用與土地政策</t>
         </is>
       </c>
+      <c r="H769" t="inlineStr"/>
     </row>
     <row r="770">
       <c r="A770" t="n">
@@ -27015,6 +27800,7 @@
           <t>閒置土地、強制拍賣</t>
         </is>
       </c>
+      <c r="H770" t="inlineStr"/>
     </row>
     <row r="771">
       <c r="A771" t="n">
@@ -27050,6 +27836,7 @@
           <t>不動產估價、不動產估價報告書</t>
         </is>
       </c>
+      <c r="H771" t="inlineStr"/>
     </row>
     <row r="772">
       <c r="A772" t="n">
@@ -27085,6 +27872,7 @@
           <t>租賃契約、租賃住宅、不動產經紀人</t>
         </is>
       </c>
+      <c r="H772" t="inlineStr"/>
     </row>
     <row r="773">
       <c r="A773" t="n">
@@ -27120,6 +27908,7 @@
           <t>全國國土計畫、土地利用與土地政策、土地使用議題</t>
         </is>
       </c>
+      <c r="H773" t="inlineStr"/>
     </row>
     <row r="774">
       <c r="A774" t="n">
@@ -27155,6 +27944,7 @@
           <t>公司法人、土地登記</t>
         </is>
       </c>
+      <c r="H774" t="inlineStr"/>
     </row>
     <row r="775">
       <c r="A775" t="n">
@@ -27190,6 +27980,7 @@
           <t>全國國土計畫、土地利用與土地政策</t>
         </is>
       </c>
+      <c r="H775" t="inlineStr"/>
     </row>
     <row r="776">
       <c r="A776" t="n">
@@ -27225,6 +28016,7 @@
           <t>土地法規、土地增值稅、記存</t>
         </is>
       </c>
+      <c r="H776" t="inlineStr"/>
     </row>
     <row r="777">
       <c r="A777" t="n">
@@ -27260,6 +28052,7 @@
           <t>全國國土計畫、土地利用與土地政策</t>
         </is>
       </c>
+      <c r="H777" t="inlineStr"/>
     </row>
     <row r="778">
       <c r="A778" t="n">
@@ -27295,6 +28088,7 @@
           <t>全國國土計畫、土地利用與土地政策</t>
         </is>
       </c>
+      <c r="H778" t="inlineStr"/>
     </row>
     <row r="779">
       <c r="A779" t="n">
@@ -27330,6 +28124,7 @@
           <t>租賃住宅、土地法、土地政策</t>
         </is>
       </c>
+      <c r="H779" t="inlineStr"/>
     </row>
     <row r="780">
       <c r="A780" t="n">
@@ -27365,6 +28160,7 @@
           <t>全國國土計畫、土地利用與土地政策</t>
         </is>
       </c>
+      <c r="H780" t="inlineStr"/>
     </row>
     <row r="781">
       <c r="A781" t="n">
@@ -27400,6 +28196,7 @@
           <t>土地徵收</t>
         </is>
       </c>
+      <c r="H781" t="inlineStr"/>
     </row>
     <row r="782">
       <c r="A782" t="n">
@@ -27435,6 +28232,7 @@
           <t>全國國土計畫、土地利用與土地政策</t>
         </is>
       </c>
+      <c r="H782" t="inlineStr"/>
     </row>
     <row r="783">
       <c r="A783" t="n">
@@ -27470,6 +28268,7 @@
           <t>實價登錄</t>
         </is>
       </c>
+      <c r="H783" t="inlineStr"/>
     </row>
     <row r="784">
       <c r="A784" t="n">
@@ -27505,6 +28304,7 @@
           <t>全國國土計畫、土地利用與土地政策</t>
         </is>
       </c>
+      <c r="H784" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" t="n">
@@ -27540,6 +28340,7 @@
           <t>公信力、地政士、土地法規、民事庭決議</t>
         </is>
       </c>
+      <c r="H785" t="inlineStr"/>
     </row>
     <row r="786">
       <c r="A786" t="n">
@@ -27575,6 +28376,7 @@
           <t>地政士考試、土地稅法規、遺贈稅</t>
         </is>
       </c>
+      <c r="H786" t="inlineStr"/>
     </row>
     <row r="787">
       <c r="A787" t="n">
@@ -27610,6 +28412,7 @@
           <t>地政士考試、地政士考試重點</t>
         </is>
       </c>
+      <c r="H787" t="inlineStr"/>
     </row>
     <row r="788">
       <c r="A788" t="n">
@@ -27645,6 +28448,7 @@
           <t>地政士考試、土地法規</t>
         </is>
       </c>
+      <c r="H788" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" t="n">
@@ -27680,6 +28484,7 @@
           <t>實價登錄</t>
         </is>
       </c>
+      <c r="H789" t="inlineStr"/>
     </row>
     <row r="790">
       <c r="A790" t="n">
@@ -27715,6 +28520,7 @@
           <t>存續保障、價值保障</t>
         </is>
       </c>
+      <c r="H790" t="inlineStr"/>
     </row>
     <row r="791">
       <c r="A791" t="n">
@@ -27750,6 +28556,7 @@
           <t>防災型都市更新、防災都更、都市計畫內防災建築再生自治條例</t>
         </is>
       </c>
+      <c r="H791" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" t="n">
@@ -27785,6 +28592,7 @@
           <t>農舍單獨移轉、土地法第104條、農業用地</t>
         </is>
       </c>
+      <c r="H792" t="inlineStr"/>
     </row>
     <row r="793">
       <c r="A793" t="n">
@@ -27820,6 +28628,7 @@
           <t>收回權、土地法、土地徵收條例、徵收補償</t>
         </is>
       </c>
+      <c r="H793" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" t="n">
@@ -27855,6 +28664,7 @@
           <t>釋字第763號、土地徵收</t>
         </is>
       </c>
+      <c r="H794" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" t="n">
@@ -27890,6 +28700,7 @@
           <t>釋字763、徵收收回權、程序正義</t>
         </is>
       </c>
+      <c r="H795" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" t="n">
@@ -27925,6 +28736,7 @@
           <t>土地法第三十四條之一、土地法第34條之1</t>
         </is>
       </c>
+      <c r="H796" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" t="n">
@@ -27960,6 +28772,7 @@
           <t>土登規則、土地登記規則</t>
         </is>
       </c>
+      <c r="H797" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" t="n">
@@ -27995,6 +28808,7 @@
           <t>土地法第三十四條之一、土地法第34條之1</t>
         </is>
       </c>
+      <c r="H798" t="inlineStr"/>
     </row>
     <row r="799">
       <c r="A799" t="n">
@@ -28030,6 +28844,7 @@
           <t>公共設施保留地、土地稅</t>
         </is>
       </c>
+      <c r="H799" t="inlineStr"/>
     </row>
     <row r="800">
       <c r="A800" t="n">
@@ -28065,6 +28880,7 @@
           <t>土地法第三十四條之一、土地法第34條之1</t>
         </is>
       </c>
+      <c r="H800" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" t="n">
@@ -28100,6 +28916,7 @@
           <t>自用住宅</t>
         </is>
       </c>
+      <c r="H801" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" t="n">
@@ -28135,6 +28952,7 @@
           <t>土地登記、所有權移轉登記、繼承登記、他項權利登記</t>
         </is>
       </c>
+      <c r="H802" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" t="n">
@@ -28170,6 +28988,7 @@
           <t>建物標示圖、建物所有權、土地登記</t>
         </is>
       </c>
+      <c r="H803" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" t="n">
@@ -28205,6 +29024,7 @@
           <t>市地重劃、籌備會、釋字第739號</t>
         </is>
       </c>
+      <c r="H804" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" t="n">
@@ -28240,6 +29060,7 @@
           <t>信託關係消滅、信託關係、信託行為、地政士</t>
         </is>
       </c>
+      <c r="H805" t="inlineStr"/>
     </row>
     <row r="806">
       <c r="A806" t="n">
@@ -28275,6 +29096,7 @@
           <t>土地法第25條、土地法第26條</t>
         </is>
       </c>
+      <c r="H806" t="inlineStr"/>
     </row>
     <row r="807">
       <c r="A807" t="n">
@@ -28310,6 +29132,7 @@
           <t>地政士、洗錢防制、不動產買賣</t>
         </is>
       </c>
+      <c r="H807" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" t="n">
@@ -28345,6 +29168,7 @@
           <t>政府徵收土地、釋字第743號、土地徵收條例</t>
         </is>
       </c>
+      <c r="H808" t="inlineStr"/>
     </row>
     <row r="809">
       <c r="A809" t="n">
@@ -28380,6 +29204,7 @@
           <t>土地法34-1、土地法104、優先購買權</t>
         </is>
       </c>
+      <c r="H809" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" t="n">
@@ -28415,6 +29240,7 @@
           <t>房地合一所得稅、遺產稅、贈與稅</t>
         </is>
       </c>
+      <c r="H810" t="inlineStr"/>
     </row>
     <row r="811">
       <c r="A811" t="n">
@@ -28450,6 +29276,7 @@
           <t>地政士、地政士法</t>
         </is>
       </c>
+      <c r="H811" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" t="n">
@@ -28485,6 +29312,7 @@
           <t>土地法第34條之1</t>
         </is>
       </c>
+      <c r="H812" t="inlineStr"/>
     </row>
     <row r="813">
       <c r="A813" t="n">
@@ -28520,6 +29348,7 @@
           <t>土地法34-1、事實上處分</t>
         </is>
       </c>
+      <c r="H813" t="inlineStr"/>
     </row>
     <row r="814">
       <c r="A814" t="n">
@@ -28555,6 +29384,7 @@
           <t>重複課稅、稅基、稅額、稅基扣除稅基、稅額扣抵稅額</t>
         </is>
       </c>
+      <c r="H814" t="inlineStr"/>
     </row>
     <row r="815">
       <c r="A815" t="n">
@@ -28590,6 +29420,7 @@
           <t>房屋自住、住家用房屋、房屋稅</t>
         </is>
       </c>
+      <c r="H815" t="inlineStr"/>
     </row>
     <row r="816">
       <c r="A816" t="n">
@@ -28625,6 +29456,7 @@
           <t>土地增值稅、地價稅</t>
         </is>
       </c>
+      <c r="H816" t="inlineStr"/>
     </row>
     <row r="817">
       <c r="A817" t="n">
@@ -28660,6 +29492,7 @@
           <t>消滅時效、土地浮覆、回復請求權、已登記不動產</t>
         </is>
       </c>
+      <c r="H817" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" t="n">
@@ -28695,6 +29528,7 @@
           <t>不課徵土地增值稅、租稅遞延性質、租稅免除性質</t>
         </is>
       </c>
+      <c r="H818" t="inlineStr"/>
     </row>
     <row r="819">
       <c r="A819" t="n">
@@ -28730,6 +29564,7 @@
           <t>行政法、信賴保護原則</t>
         </is>
       </c>
+      <c r="H819" t="inlineStr"/>
     </row>
     <row r="820">
       <c r="A820" t="n">
@@ -28765,6 +29600,7 @@
           <t>公保地檢討變更、公共設施用地解編</t>
         </is>
       </c>
+      <c r="H820" t="inlineStr"/>
     </row>
     <row r="821">
       <c r="A821" t="n">
@@ -28800,6 +29636,7 @@
           <t>土地法、釋字第758號、釋字第400號</t>
         </is>
       </c>
+      <c r="H821" t="inlineStr"/>
     </row>
     <row r="822">
       <c r="A822" t="n">
@@ -28835,6 +29672,7 @@
           <t>地政士法、地政士</t>
         </is>
       </c>
+      <c r="H822" t="inlineStr"/>
     </row>
     <row r="823">
       <c r="A823" t="n">
@@ -28870,6 +29708,7 @@
           <t>房屋產權登記面積、虛坪制、實坪制</t>
         </is>
       </c>
+      <c r="H823" t="inlineStr"/>
     </row>
     <row r="824">
       <c r="A824" t="n">
@@ -28905,6 +29744,7 @@
           <t>信託法、稅捐稽徵法、稅捐保全、信託行為</t>
         </is>
       </c>
+      <c r="H824" t="inlineStr"/>
     </row>
     <row r="825">
       <c r="A825" t="n">
@@ -28940,6 +29780,7 @@
           <t>重新規定地價、公告地價、土地現值</t>
         </is>
       </c>
+      <c r="H825" t="inlineStr"/>
     </row>
     <row r="826">
       <c r="A826" t="n">
@@ -28975,6 +29816,7 @@
           <t>市地重劃、繼受取得、原始取得</t>
         </is>
       </c>
+      <c r="H826" t="inlineStr"/>
     </row>
     <row r="827">
       <c r="A827" t="n">
@@ -29010,6 +29852,7 @@
           <t>規定地價、照價徵稅、照價收買、漲價歸公、重新規定地價</t>
         </is>
       </c>
+      <c r="H827" t="inlineStr"/>
     </row>
     <row r="828">
       <c r="A828" t="n">
@@ -29045,6 +29888,7 @@
           <t>建物平面圖測繪、雨遮不登記、屋簷</t>
         </is>
       </c>
+      <c r="H828" t="inlineStr"/>
     </row>
     <row r="829">
       <c r="A829" t="n">
@@ -29080,6 +29924,7 @@
           <t>優先購買權、放棄優先購買權、視為放棄優先購買權</t>
         </is>
       </c>
+      <c r="H829" t="inlineStr"/>
     </row>
     <row r="830">
       <c r="A830" t="n">
@@ -29115,6 +29960,7 @@
           <t>優先購買權、土地法第34之1</t>
         </is>
       </c>
+      <c r="H830" t="inlineStr"/>
     </row>
     <row r="831">
       <c r="A831" t="n">
@@ -29150,6 +29996,7 @@
           <t>土地法、優先購買權、回復期限</t>
         </is>
       </c>
+      <c r="H831" t="inlineStr"/>
     </row>
     <row r="832">
       <c r="A832" t="n">
@@ -29185,6 +30032,7 @@
           <t>土地法第104條</t>
         </is>
       </c>
+      <c r="H832" t="inlineStr"/>
     </row>
     <row r="833">
       <c r="A833" t="n">
@@ -29220,6 +30068,7 @@
           <t>土地經濟學、地方特考</t>
         </is>
       </c>
+      <c r="H833" t="inlineStr"/>
     </row>
     <row r="834">
       <c r="A834" t="n">
@@ -29255,6 +30104,7 @@
           <t>國土計畫</t>
         </is>
       </c>
+      <c r="H834" t="inlineStr"/>
     </row>
     <row r="835">
       <c r="A835" t="n">
@@ -29290,6 +30140,7 @@
           <t>土地法第34條之1</t>
         </is>
       </c>
+      <c r="H835" t="inlineStr"/>
     </row>
     <row r="836">
       <c r="A836" t="n">
@@ -29325,6 +30176,7 @@
           <t>土地增值稅、房地合一所得稅、重購退稅額度</t>
         </is>
       </c>
+      <c r="H836" t="inlineStr"/>
     </row>
     <row r="837">
       <c r="A837" t="n">
@@ -29360,6 +30212,7 @@
           <t>國土計畫法</t>
         </is>
       </c>
+      <c r="H837" t="inlineStr"/>
     </row>
     <row r="838">
       <c r="A838" t="n">
@@ -29395,6 +30248,7 @@
           <t>市地重劃、區段徵收</t>
         </is>
       </c>
+      <c r="H838" t="inlineStr"/>
     </row>
     <row r="839">
       <c r="A839" t="n">
@@ -29430,6 +30284,7 @@
           <t>全國國土計畫</t>
         </is>
       </c>
+      <c r="H839" t="inlineStr"/>
     </row>
     <row r="840">
       <c r="A840" t="n">
@@ -29465,6 +30320,7 @@
           <t>不動產經紀人、房屋租賃定型化契約</t>
         </is>
       </c>
+      <c r="H840" t="inlineStr"/>
     </row>
     <row r="841">
       <c r="A841" t="n">
@@ -29500,6 +30356,7 @@
           <t>地價稅、土地稅法、信託土地、自益信託、他益信託</t>
         </is>
       </c>
+      <c r="H841" t="inlineStr"/>
     </row>
     <row r="842">
       <c r="A842" t="n">
@@ -29535,6 +30392,7 @@
           <t>合建分配比、合建權益分配</t>
         </is>
       </c>
+      <c r="H842" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" t="n">
@@ -29570,6 +30428,7 @@
           <t>土地法第13條、岸地優先取得權、優先購買權</t>
         </is>
       </c>
+      <c r="H843" t="inlineStr"/>
     </row>
     <row r="844">
       <c r="A844" t="n">
@@ -29605,6 +30464,7 @@
           <t>農業用地、耕地、土地增值稅</t>
         </is>
       </c>
+      <c r="H844" t="inlineStr"/>
     </row>
     <row r="845">
       <c r="A845" t="n">
@@ -29640,6 +30500,7 @@
           <t>土地移轉契約、土地增值稅、解除契約</t>
         </is>
       </c>
+      <c r="H845" t="inlineStr"/>
     </row>
     <row r="846">
       <c r="A846" t="n">
@@ -29675,6 +30536,7 @@
           <t>農業用地、耕地、土地增值稅</t>
         </is>
       </c>
+      <c r="H846" t="inlineStr"/>
     </row>
     <row r="847">
       <c r="A847" t="n">
@@ -29710,6 +30572,7 @@
           <t>土地法34-1</t>
         </is>
       </c>
+      <c r="H847" t="inlineStr"/>
     </row>
     <row r="848">
       <c r="A848" t="n">
@@ -29745,6 +30608,7 @@
           <t>容積移轉、文化資產法、都市計畫法、水利法</t>
         </is>
       </c>
+      <c r="H848" t="inlineStr"/>
     </row>
     <row r="849">
       <c r="A849" t="n">
@@ -29780,6 +30644,7 @@
           <t>農業用地、農舍、田賦或地價稅、房地合一所得稅、贈與稅、遺產稅、土地增值稅、房屋稅、契稅</t>
         </is>
       </c>
+      <c r="H849" t="inlineStr"/>
     </row>
     <row r="850">
       <c r="A850" t="n">
@@ -29815,6 +30680,7 @@
           <t>遺贈登記、民法、土地登記、土地增值稅、遺產及贈與稅法</t>
         </is>
       </c>
+      <c r="H850" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" t="n">
@@ -29850,6 +30716,7 @@
           <t>公共設施保留地、土地增值稅</t>
         </is>
       </c>
+      <c r="H851" t="inlineStr"/>
     </row>
     <row r="852">
       <c r="A852" t="n">
@@ -29885,6 +30752,7 @@
           <t>公有土地撥用</t>
         </is>
       </c>
+      <c r="H852" t="inlineStr"/>
     </row>
     <row r="853">
       <c r="A853" t="n">
@@ -29920,6 +30788,7 @@
           <t>信託法第五條、信託行為</t>
         </is>
       </c>
+      <c r="H853" t="inlineStr"/>
     </row>
     <row r="854">
       <c r="A854" t="n">
@@ -29955,6 +30824,7 @@
           <t>土地法第104條、優先購買權</t>
         </is>
       </c>
+      <c r="H854" t="inlineStr"/>
     </row>
     <row r="855">
       <c r="A855" t="n">
@@ -29990,6 +30860,7 @@
           <t>自辦市地重劃、市地重劃實施辦法、市地重劃</t>
         </is>
       </c>
+      <c r="H855" t="inlineStr"/>
     </row>
     <row r="856">
       <c r="A856" t="n">
@@ -30025,6 +30896,7 @@
           <t>容積移轉、發展權移轉、容積獎勵、民法物權編</t>
         </is>
       </c>
+      <c r="H856" t="inlineStr"/>
     </row>
     <row r="857">
       <c r="A857" t="n">
@@ -30060,6 +30932,7 @@
           <t>土地法第12條、土地法第14條、水道浮覆地</t>
         </is>
       </c>
+      <c r="H857" t="inlineStr"/>
     </row>
     <row r="858">
       <c r="A858" t="n">
@@ -30095,6 +30968,7 @@
           <t>三七五租約、平均地權條例、市地重劃、土地徵收、補償地價、土地增值稅</t>
         </is>
       </c>
+      <c r="H858" t="inlineStr"/>
     </row>
     <row r="859">
       <c r="A859" t="n">
@@ -30130,6 +31004,7 @@
           <t>地上權、土地法第104條、地上權登記、地上權實例</t>
         </is>
       </c>
+      <c r="H859" t="inlineStr"/>
     </row>
     <row r="860">
       <c r="A860" t="n">
@@ -30165,6 +31040,7 @@
           <t>土地利用與政策、開發許可、區域計畫</t>
         </is>
       </c>
+      <c r="H860" t="inlineStr"/>
     </row>
     <row r="861">
       <c r="A861" t="n">
@@ -30200,6 +31076,7 @@
           <t>界址爭議、地籍測量、土地法第46條之2</t>
         </is>
       </c>
+      <c r="H861" t="inlineStr"/>
     </row>
     <row r="862">
       <c r="A862" t="n">
@@ -30235,6 +31112,7 @@
           <t>耕地375、耕地三七五減租條例、三七五租約</t>
         </is>
       </c>
+      <c r="H862" t="inlineStr"/>
     </row>
     <row r="863">
       <c r="A863" t="n">
@@ -30270,6 +31148,7 @@
           <t>不動產估價師、土地利用法規、不動產經濟學、都市更新條例</t>
         </is>
       </c>
+      <c r="H863" t="inlineStr"/>
     </row>
     <row r="864">
       <c r="A864" t="n">
@@ -30305,6 +31184,7 @@
           <t>逆向抵押貸款、不動產投資分析、以房養老</t>
         </is>
       </c>
+      <c r="H864" t="inlineStr"/>
     </row>
     <row r="865">
       <c r="A865" t="n">
@@ -30340,6 +31220,7 @@
           <t>大陸地區人民在臺灣地區取得設定或移轉不動產物權許可辦法</t>
         </is>
       </c>
+      <c r="H865" t="inlineStr"/>
     </row>
     <row r="866">
       <c r="A866" t="n">
@@ -30375,6 +31256,7 @@
           <t>優先購買權、土地法第104條、書面通知</t>
         </is>
       </c>
+      <c r="H866" t="inlineStr"/>
     </row>
     <row r="867">
       <c r="A867" t="n">
@@ -30410,6 +31292,7 @@
           <t>影子銀行、不動產投資分析、資產證券化</t>
         </is>
       </c>
+      <c r="H867" t="inlineStr"/>
     </row>
     <row r="868">
       <c r="A868" t="n">
@@ -30445,6 +31328,7 @@
           <t>大陸地區人民在臺灣地區取得設定或移轉不動產物權許可辦法、543條款、大陸人民地權限制</t>
         </is>
       </c>
+      <c r="H868" t="inlineStr"/>
     </row>
     <row r="869">
       <c r="A869" t="n">
@@ -30480,6 +31364,7 @@
           <t>更正登記、登記錯誤、土地法第43條、土地登記</t>
         </is>
       </c>
+      <c r="H869" t="inlineStr"/>
     </row>
     <row r="870">
       <c r="A870" t="n">
@@ -30515,6 +31400,7 @@
           <t>土地法第43條</t>
         </is>
       </c>
+      <c r="H870" t="inlineStr"/>
     </row>
     <row r="871">
       <c r="A871" t="n">
@@ -30550,6 +31436,7 @@
           <t>撤銷徵收、廢止徵收、土地徵收條例</t>
         </is>
       </c>
+      <c r="H871" t="inlineStr"/>
     </row>
     <row r="872">
       <c r="A872" t="n">
@@ -30585,6 +31472,7 @@
           <t>實價登錄、平均地權條例、地政士法、不動產經紀業管理條例、修法</t>
         </is>
       </c>
+      <c r="H872" t="inlineStr"/>
     </row>
     <row r="873">
       <c r="A873" t="n">
@@ -30620,6 +31508,7 @@
           <t>土地法規</t>
         </is>
       </c>
+      <c r="H873" t="inlineStr"/>
     </row>
     <row r="874">
       <c r="A874" t="n">
@@ -30655,6 +31544,7 @@
           <t>都更條例、老屋條例</t>
         </is>
       </c>
+      <c r="H874" t="inlineStr"/>
     </row>
     <row r="875">
       <c r="A875" t="n">
@@ -30690,6 +31580,7 @@
           <t>實價登錄、土地登記</t>
         </is>
       </c>
+      <c r="H875" t="inlineStr"/>
     </row>
     <row r="876">
       <c r="A876" t="n">
@@ -30725,6 +31616,7 @@
           <t>徵收地上權、土地徵收條例、釋字747</t>
         </is>
       </c>
+      <c r="H876" t="inlineStr"/>
     </row>
     <row r="877">
       <c r="A877" t="n">
@@ -30760,6 +31652,7 @@
           <t>土地徵收、徵收補償發給</t>
         </is>
       </c>
+      <c r="H877" t="inlineStr"/>
     </row>
     <row r="878">
       <c r="A878" t="n">
@@ -30795,6 +31688,7 @@
           <t>農民、農舍、農舍移轉、農業用地、違規農舍</t>
         </is>
       </c>
+      <c r="H878" t="inlineStr"/>
     </row>
     <row r="879">
       <c r="A879" t="n">
@@ -30830,6 +31724,7 @@
           <t>農民、農舍、農業發展條例、農業用地興建農舍辦法</t>
         </is>
       </c>
+      <c r="H879" t="inlineStr"/>
     </row>
     <row r="880">
       <c r="A880" t="n">
@@ -30865,6 +31760,7 @@
           <t>地政士、土地法規、土地登記實務、土地稅法規、信託法概要</t>
         </is>
       </c>
+      <c r="H880" t="inlineStr"/>
     </row>
     <row r="881">
       <c r="A881" t="n">
@@ -30900,6 +31796,7 @@
           <t>地政士、稅捐稽徵法、平均地權條例</t>
         </is>
       </c>
+      <c r="H881" t="inlineStr"/>
     </row>
     <row r="882">
       <c r="A882" t="n">
@@ -30935,6 +31832,7 @@
           <t>國土計畫法、國土保育地區、海洋資源地區、農業發展地區、城鄉發展地區、住宅存量流量模型</t>
         </is>
       </c>
+      <c r="H882" t="inlineStr"/>
     </row>
     <row r="883">
       <c r="A883" t="n">
@@ -30970,6 +31868,7 @@
           <t>所有權住宅、地上權住宅、使用權住宅、地價稅、房屋稅、土地增值稅、房地合一所得稅</t>
         </is>
       </c>
+      <c r="H883" t="inlineStr"/>
     </row>
     <row r="884">
       <c r="A884" t="n">
@@ -31005,6 +31904,7 @@
           <t>所有權住宅、地上權住宅、使用權住宅</t>
         </is>
       </c>
+      <c r="H884" t="inlineStr"/>
     </row>
     <row r="885">
       <c r="A885" t="n">
@@ -31040,6 +31940,7 @@
           <t>土地登記、破產登記</t>
         </is>
       </c>
+      <c r="H885" t="inlineStr"/>
     </row>
     <row r="886">
       <c r="A886" t="n">
@@ -31075,6 +31976,7 @@
           <t>土地登記、建物所有權</t>
         </is>
       </c>
+      <c r="H886" t="inlineStr"/>
     </row>
     <row r="887">
       <c r="A887" t="n">
@@ -31110,6 +32012,7 @@
           <t>修法、平均地權條例、遺產及贈與稅法</t>
         </is>
       </c>
+      <c r="H887" t="inlineStr"/>
     </row>
     <row r="888">
       <c r="A888" t="n">
@@ -31145,6 +32048,7 @@
           <t>房地市場價格</t>
         </is>
       </c>
+      <c r="H888" t="inlineStr"/>
     </row>
     <row r="889">
       <c r="A889" t="n">
@@ -31180,6 +32084,7 @@
           <t>房地市場價格、土地貢獻價值、建物貢獻價值</t>
         </is>
       </c>
+      <c r="H889" t="inlineStr"/>
     </row>
     <row r="890">
       <c r="A890" t="n">
@@ -31215,6 +32120,7 @@
           <t>建物折舊、物理性折舊、功能性折舊、經濟性折舊、物理耐用年數、經濟耐用年數</t>
         </is>
       </c>
+      <c r="H890" t="inlineStr"/>
     </row>
     <row r="891">
       <c r="A891" t="n">
@@ -31250,6 +32156,7 @@
           <t>不動產契約書、公契、私契</t>
         </is>
       </c>
+      <c r="H891" t="inlineStr"/>
     </row>
     <row r="892">
       <c r="A892" t="n">
@@ -31285,6 +32192,7 @@
           <t>土地登記規則</t>
         </is>
       </c>
+      <c r="H892" t="inlineStr"/>
     </row>
     <row r="893">
       <c r="A893" t="n">
@@ -31316,6 +32224,7 @@
         </is>
       </c>
       <c r="G893" t="inlineStr"/>
+      <c r="H893" t="inlineStr"/>
     </row>
     <row r="894">
       <c r="A894" t="n">
@@ -31351,6 +32260,7 @@
           <t>停車位產權、獨立權狀車位、無獨立權狀車位</t>
         </is>
       </c>
+      <c r="H894" t="inlineStr"/>
     </row>
     <row r="895">
       <c r="A895" t="n">
@@ -31386,6 +32296,7 @@
           <t>停車位、法定車位、增設車位、獎勵車位、停車位產權</t>
         </is>
       </c>
+      <c r="H895" t="inlineStr"/>
     </row>
     <row r="896">
       <c r="A896" t="n">
@@ -31421,6 +32332,7 @@
           <t>都市發展、都市化、郊區化、仕紳化</t>
         </is>
       </c>
+      <c r="H896" t="inlineStr"/>
     </row>
     <row r="897">
       <c r="A897" t="n">
@@ -31456,6 +32368,7 @@
           <t>老舊建物、老舊建物拆除重建</t>
         </is>
       </c>
+      <c r="H897" t="inlineStr"/>
     </row>
     <row r="898">
       <c r="A898" t="n">
@@ -31491,6 +32404,7 @@
           <t>實價申報、平均地權條例、不動產估價、實價登錄</t>
         </is>
       </c>
+      <c r="H898" t="inlineStr"/>
     </row>
     <row r="899">
       <c r="A899" t="n">
@@ -31526,6 +32440,7 @@
           <t>建築執照面積、建物登記面積、地籍測量實施規則、雨遮、屋簷</t>
         </is>
       </c>
+      <c r="H899" t="inlineStr"/>
     </row>
     <row r="900">
       <c r="A900" t="n">
@@ -31561,6 +32476,7 @@
           <t>地籍測量實施規則、專有部分、共有部分、主建物面積、附屬建物面積</t>
         </is>
       </c>
+      <c r="H900" t="inlineStr"/>
     </row>
     <row r="901">
       <c r="A901" t="n">
@@ -31596,6 +32512,7 @@
           <t>區段徵收、現金補償、抵價地補償、土地徵收條例</t>
         </is>
       </c>
+      <c r="H901" t="inlineStr"/>
     </row>
     <row r="902">
       <c r="A902" t="n">
@@ -31631,6 +32548,7 @@
           <t>都市更新、都更案、積極型住戶、消極型住戶</t>
         </is>
       </c>
+      <c r="H902" t="inlineStr"/>
     </row>
     <row r="903">
       <c r="A903" t="n">
@@ -31666,6 +32584,7 @@
           <t>釋字156、釋字742、都市計畫</t>
         </is>
       </c>
+      <c r="H903" t="inlineStr"/>
     </row>
     <row r="904">
       <c r="A904" t="n">
@@ -31701,6 +32620,7 @@
           <t>地方特考、土地徵收、土地政策、土地法規</t>
         </is>
       </c>
+      <c r="H904" t="inlineStr"/>
     </row>
     <row r="905">
       <c r="A905" t="n">
@@ -31736,6 +32656,7 @@
           <t>地價稅、土地增值稅、公告地價、公告土地現值</t>
         </is>
       </c>
+      <c r="H905" t="inlineStr"/>
     </row>
     <row r="906">
       <c r="A906" t="n">
@@ -31771,6 +32692,7 @@
           <t>不動產經紀人、不動產估價概要、土地法與土地相關稅法概要、不動產經紀相關法規概要</t>
         </is>
       </c>
+      <c r="H906" t="inlineStr"/>
     </row>
     <row r="907">
       <c r="A907" t="n">
@@ -31806,6 +32728,7 @@
           <t>區段徵收、土地徵收</t>
         </is>
       </c>
+      <c r="H907" t="inlineStr"/>
     </row>
     <row r="908">
       <c r="A908" t="n">
@@ -31841,6 +32764,7 @@
           <t>精準地價、自動估價系統、AVM、不動產估價</t>
         </is>
       </c>
+      <c r="H908" t="inlineStr"/>
     </row>
     <row r="909">
       <c r="A909" t="n">
@@ -31876,6 +32800,7 @@
           <t>地價稅、房屋稅</t>
         </is>
       </c>
+      <c r="H909" t="inlineStr"/>
     </row>
     <row r="910">
       <c r="A910" t="n">
@@ -31911,6 +32836,7 @@
           <t>海域、海域區、海域用地</t>
         </is>
       </c>
+      <c r="H910" t="inlineStr"/>
     </row>
     <row r="911">
       <c r="A911" t="n">
@@ -31946,6 +32872,7 @@
           <t>不動產估價</t>
         </is>
       </c>
+      <c r="H911" t="inlineStr"/>
     </row>
     <row r="912">
       <c r="A912" t="n">
@@ -31981,6 +32908,7 @@
           <t>國土計畫法、高普考、土地政策</t>
         </is>
       </c>
+      <c r="H912" t="inlineStr"/>
     </row>
     <row r="913">
       <c r="A913" t="n">
@@ -32016,6 +32944,7 @@
           <t>不動產經紀人、房屋租賃定型化契約應記載及不得記載事項、不動產經紀相關法規概要</t>
         </is>
       </c>
+      <c r="H913" t="inlineStr"/>
     </row>
     <row r="914">
       <c r="A914" t="n">
@@ -32051,6 +32980,7 @@
           <t>不動產經紀人、土地法與土地相關稅法概要、房地合一稅、所得稅、土地增值稅</t>
         </is>
       </c>
+      <c r="H914" t="inlineStr"/>
     </row>
     <row r="915">
       <c r="A915" t="n">
@@ -32086,6 +33016,7 @@
           <t>不動產估價師、不動產投資分析、不動產估價理論</t>
         </is>
       </c>
+      <c r="H915" t="inlineStr"/>
     </row>
     <row r="916">
       <c r="A916" t="n">
@@ -32121,6 +33052,7 @@
           <t>土地登記、登記錯誤、登記遺漏、塗銷登記</t>
         </is>
       </c>
+      <c r="H916" t="inlineStr"/>
     </row>
     <row r="917">
       <c r="A917" t="n">
@@ -32154,6 +33086,49 @@
       <c r="G917" t="inlineStr">
         <is>
           <t>不動產估價師、不動產經濟學、不動產估價實務</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr"/>
+    </row>
+    <row r="918">
+      <c r="A918" t="n">
+        <v>915297</v>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>申報房屋稅籍有關事項及使用情形,曾榮耀老師</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>蘇偉強</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>2026/02/24</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915297</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>2026-02-24 12:39:13</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>房屋稅籍</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>依據房屋稅條例第7條規定，「納稅義務人應於房屋建造完成之日起算三十日內檢附有關文件，向當地主管稽徵機關申報房屋稅籍有關事項及使用情形；其有增建、改建或移轉、承典時，亦同。」
+因此，新、增、改建房屋應於建造完成之日起 30 日內送至所轄稅捐稽徵處申請設籍。應檢附附件： (一)建築物使用執照影本；未領使用執照者，請檢附建造執照影本。 (二)平面圖及立（側）面圖影本。 (三)地下室及共同使用部分協議書正本。 (四)未領建造執照或完工證明之房屋，請另附未辦保存登記 ( 所有權登記 ) 之房屋申請設立房屋稅籍承諾書正本及其他有關文件。 (五)若為鋼鐵造房屋，請檢附鋼鐵規格資料（如未檢附資料者，核實認定）。 (六)若裝設電梯，請附電梯工程合約書影本。 (七)若有三親等內親屬以外之他人設有戶籍，且無租賃關係，需填寫房屋所有人無租賃關係申明書或設籍人無租賃關係申明書。 (八)其他有關文件。
+參考資料：財政部，稅務線上申辦－申請房屋設籍。</t>
         </is>
       </c>
     </row>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H918"/>
+  <dimension ref="A1:H919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33132,6 +33132,60 @@
         </is>
       </c>
     </row>
+    <row r="919">
+      <c r="A919" t="n">
+        <v>915299</v>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>房價上漲拉動地價上漲，而非地價上漲推動房價上漲,許文昌老師</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915299</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>2026-02-26 12:38:31</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>土地開發分析法、房價、地價、預售屋價、新成屋價、中古屋價</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>• (一) 建設公司購地之最高價格 建設公司就建築基地在最有效使用下，預估銷售總金額，扣除建築成本、管銷費用及正常利潤，所得到之餘額，就是建設公司購買土地之最高支付價格。不動產估價技術規則第81條「土地開發分析法」之公式正是此一構想。
+• (二) 土地開發分析法之啟示 土地開發分析法之公式如下： V=S÷（1+R）÷（1+i）−（C+M）……①其中：
+1. V代表個別基地之地價：地價為因變數，S、C、M、i及R等為自變數。亦即，個別基地之地價（V）受到總銷售金額（S）、建築成本（C）、管銷費用（M）、綜合利率（i）、適當利潤率（R）等之影響。以函數關係表示如下： V=f(S, C, M, i, R)……②
+2. S代表總銷售金額：建設公司於建築基地之建蔽率、容積率等容積管制下，規劃建物之可銷售樓地板面積（即建坪）。再就各層可銷售單價（即房價），乘以各層可銷售樓地板面積，就得到總銷售金額（即建案之總收入）。亦即： S=Σ(P×Q)……③ 其中： S：預期總銷售金額。 P：各層之可銷售單價（即房價）。 Q：各層之可銷售樓地板面積（即建坪）。
+3. C代表建築成本：建築成本就是造價成本。不動產估價技術規則稱為「直接成本」。
+4. M代表管銷費用：管銷費用包括規劃設計費、廣告費及銷售費、管理費、稅捐等，但不包括資本利息。不動產估價技術規則稱為「間接成本」。
+5. i代表綜合利率：綜合利率為個案利率，而非年利率。亦即，建案興建一段期間所負擔之平均利率。
+6. R代表適當利潤率：適當利潤率就是經濟學之正常利潤率。適當利潤率為個案利潤率，而非年利潤率。亦即，建案興建一段期間所要求之正常利潤率。
+由③式可知，構成總銷售金額之因素為可銷售之房價（P）及可銷售之樓地板面積（Q）。又，可銷售之樓地板面積主要取決於容積率（以A代表），容積率代表土地使用強度。因此，②式可以改寫為：V=f(P, A, C, M, i, R)……④
+由①式可知，房價（P）與地價（V）成正比，容積率（A）與地價（V）成正比，造價（C）與地價（V）成反比，管銷費用（M）與地價（V）成反比，綜合利率（i）與地價（V）成反比，適當利潤率（R）與地價（V）成反比。
+• (三) 地價與房價之關係：
+1. 由④式可知，房價（P）為自變數，地價（V）為因變數。因此，房價影響地價，而非地價影響房價。
+2. 房價（P）與地價（V）成正比。亦即，房價上漲拉動地價上漲，而非地價上漲推動房價上漲。
+• (四) 預售屋價格為不動產價格之核心 建設公司所採用之房價（P）為預售屋價，而非新成屋價。因此，預售屋價上漲帶動新成屋價上漲，新成屋價上漲再帶動中古屋價上漲。
+綜上，預售屋價上漲帶動地價上漲，預售屋價上張又帶動新成屋價上漲及中古屋價上漲。要言之，預售屋價格為不動產價格上漲之領頭羊。 政府於不動產價格高漲時，採取抑制不動產價格高漲之措施，焦點應放在預售屋價格。只要預售屋價格受到抑制，其餘之新成屋價、中古屋價及地價等隨之熄火。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H919"/>
+  <dimension ref="A1:H920"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33186,6 +33186,47 @@
         </is>
       </c>
     </row>
+    <row r="920">
+      <c r="A920" t="n">
+        <v>915330</v>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>騎樓地價稅減免,曾榮耀老師</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>蘇偉強</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>2026/03/03</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915330</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:27:13</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>騎樓走廊地、地價稅</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>根據土地稅減免規則第10條，供公共通行之騎樓走廊地，無建築改良物者，應免徵地價稅，有建築改良物者，依下列規定減徵地價稅。 一、地上有建築改良物一層者，減徵二分之一。 二、地上有建築改良物二層者，減徵三分之一。 三、地上有建築改良物三層者，減徵四分之一。 四、地上有建築改良物四層以上者，減徵五分之一。
+範例：一棟總樓層10層樓之公寓大廈，基地面積為1,500平方公尺，每戶土地持分各1/10，而1樓供公共通行的騎樓走廊地面積為50平方公尺。 當任何一位土地所有權人向稅捐處申請減免地價稅，因本棟共10層樓，屬騎樓走廊地的上方有4層以上，故各樓層有持分基地的所有權人，皆可減徵騎樓走廊地面積的1/5，即50平方公尺×1/5＝10平方公尺。 因此，每一土地所有權人各可減徵10平方公尺的1/10（每戶持分），也就是1平方公尺的地價稅。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H920"/>
+  <dimension ref="A1:H921"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33227,6 +33227,53 @@
         </is>
       </c>
     </row>
+    <row r="921">
+      <c r="A921" t="n">
+        <v>915333</v>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>都市更新整合不易成功之原因,許文昌老師</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>2026/03/05</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915333</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:36:19</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>都市更新、釘子戶</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>都市更新為現行政府強化建物結構、改善居住環境及提升居住品質之重要手段。雖政府給予容積獎勵、稅捐減免等優惠措施，然最困難在於整合費時且不易成功。其原因如下：
+• (一) 愛比較心理：原住戶參加都市更新，不僅計算自己的利益，還會比較別人的利益；不僅計算本案的利益，還會比較別案的利益。比來比去，總覺得自己所獲得利益較別人少。
+• (二) 稟賦效果：原住戶對其所擁有之房地，失去的評價往往高於買入的評價。買入的評價有市場行情可供參考，但失去的評價涉及個人主觀感受，難以評估。
+• (三) 囚犯困境：都市更新之參與者，彼此間缺乏信任。因此，在集體行動中，個人所做出理性決策，卻造成集體不理性的結果。
+• (四) 資訊不對稱：實施者與原住戶間存在資訊不對稱。實施者對更新案之資訊較多，原住戶對更新案之資訊較少。換言之，實施者是資訊強勢者，原住戶是資訊弱勢者，造成雙方不信任。
+• (五) 競合關係：實施者與原住戶及原住戶之間存在既競爭又合作之關係。所謂競爭，指如果實施者房地分配多，就是原住戶房地分配少；如果某一原住戶房地分配多，就是其他原住戶房地分配少。所稱合作，指如果更新案成功，所有參與者皆共享其利；如果更新案失敗，所有參與者皆共蒙其弊。
+• (六) 釘子戶現象：部分原住戶認為越晚簽訂同意書，分配條件愈好，甚至可以向實施者拿到桌底下之利益。
+• (七) 拿翹行為：都市更新大戶若整合成功，獲利豐碩，因此大戶積極促成都市更新的成功，要價較低。反之，都市更新小戶若整合失敗，損失輕微，因此小戶採以小博大，拿翹行為，要價較高。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H921"/>
+  <dimension ref="A1:H922"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33274,6 +33274,51 @@
         </is>
       </c>
     </row>
+    <row r="922">
+      <c r="A922" t="n">
+        <v>915354</v>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>共有物裁判分割方法之次序,曾榮耀老師</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>蘇偉強</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>2026/03/10</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915354</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:36:11</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>共有物、裁判分割</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>按民法第824條規定：「共有物之分割，依共有人協議之方法行之。 分割之方法不能協議決定，或於協議決定後因消滅時效完成經共有人拒絕履行者，法院得因任何共有人之請求，命為下列之分配： 一、以原物分配於各共有人。但各共有人均受原物之分配顯有困難者，得將原物分配於部分共有人。 二、原物分配顯有困難時，得變賣共有物，以價金分配於各共有人；或以原物之一部分分配於各共有人，他部分變賣，以價金分配於各共有人。 以原物為分配時，如共有人中有未受分配，或不能按其應有部分受分配者，得以金錢補償之。」
+因此，共有物如需要終止共有關係，依前述民法第824條規定，除第1項協議分割外，第2項及第3項的裁判分割，會有三種分配結果：
+1. 原物分配：全部原物。
+2. 補償分配：部分原物、部分現金補償。
+3. 變價分配：全部變賣，分配價金。
+其中，共有物裁判分割，應採原物、補償或變價方式，其評估標準為何？ 可參最高法院113年度台上字第1022號民事判決：「按定共有物分割之方法，固可由法院自由裁量，惟仍應斟酌各共有人之意願、利害關係及其分得部分所得利用之價值等情形，酌定適當公平之方法以為分割。審諸民法第824條第2項至第4項規定，法院裁判分割共有物，固得為原物分割及變價分割，但仍以原物分割為優先考慮，令共有人得享有共有物財產權之存續價值，至共有人中有不能按其應有部分受分配，得以適當之金錢補償之，並非僅有變賣一途。」</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H922"/>
+  <dimension ref="A1:H923"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33319,6 +33319,65 @@
         </is>
       </c>
     </row>
+    <row r="923">
+      <c r="A923" t="n">
+        <v>915382</v>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>三七五耕地因市地重劃及區段徵收而終止租約或註銷租約,許文昌老師</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>2026/03/12</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915382</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:35:23</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>三七五租約、市地重劃、區段徵收、終止租約、註銷租約</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>所謂終止租約，指業佃雙方合意而終止三七五租約。所謂註銷租約，指由政府介入而註銷三七五租約，屬於直轄市或縣（市）政府之行政處分。
+• (一) 市地重劃：
+1. 註銷租約： (1)註銷時機：出租之公、私有耕地因實施市地重劃致不能達到原租賃之目的者，由直轄市或縣（市）政府逕為註銷其租約並通知當事人（平§63Ⅰ）。所稱因實施市地重劃致不能達到原租賃之目的者，指下列情形而言：
+• ①重劃後未受分配土地者。
+• ②重劃後分配之土地，經直轄市或縣（市）政府認定不能達到原租賃目的者。（平施§89）
+• (2) 補償額度：依前項規定註銷租約者，承租人得依下列規定請求或領取補償：
+• ①重劃後分配土地者，承租人得向出租人請求按重劃計畫書公告當期該土地之公告土地現值三分之一之補償。
+• ②重劃後未受分配土地者，其應領之補償地價，由出租人領取三分之二，承租人領取三分之一。（平§63Ⅱ）
+2. 終止租約：重劃前訂有耕地三七五租約之土地，如無平均地權條例施行細則第89條所定不能達到原租賃目的之情形者，主管機關應於重劃分配結果公告確定後二個月內邀集權利人協調。協調成立者，應於權利變更登記後函知有關機關逕為辦理終止租約登記（市重§48）。
+3. 租約存續：上開如協調不成者，應於權利變更登記後函知有關機關逕爲辦理租約標示變更登記（市重§48）。
+• (二) 區段徵收：
+1. 補償方式： (1)限期清理完成—發給抵價地補償： 土地所有權人申請發給抵價地之原有土地上訂有耕地租約者，直轄市或縣（市）主管機關應通知申請人限期自行清理，並依規定期限提出補償承租人之證明文件（徵§41 I）。此屬於終止租約。 (2)未限期清理完成—發給現金補償： 申請人未依前項規定辦理者，直轄市或縣（市）主管機關應核定不發給抵價地。直轄市或縣（市）主管機關經核定不發給抵價地者，應於核定之次日起十五日內發給現金補償（徵§41ⅡⅢ）。發給補償完竣，耕地三七五租約消滅。
+• ①補償額度：依法徵收之土地為出租耕地時，除由政府補償承租人為改良土地所支付之費用，及尚未收穫之農作改良物外，並應由土地所有權人，以所得之補償地價，扣除土地增值稅後餘額之三分之一，補償耕地承租人（平§11Ⅰ）。
+• ②代為扣交：上開補償承租人之地價，應由主管機關於發放補償或依法提存時，代為扣交（平§11Ⅱ）。
+2. 註銷租約： 土地所有權人申請發給抵價地之原有土地上訂有耕地租約者，除終止租約外，並得於申請時，請求徵收機關邀集承租人協調；其經協調合於下列情形者，得由地政機關就其應領之補償地價辦理代為扣繳清償及註銷租約，並以剩餘應領補償地價申領抵價地： (1)補償金額或權利價值經雙方確定，並同意由地政機關代為扣繳清償。 (2)承租人同意註銷租約。（平施§74-1）
+【註】
+1. 平：平均地權條例。
+2. 平施：平均地權條例施行細則。
+3. 市重：市地重劃實施辦法。
+4. 徵：土地徵收條例。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H923"/>
+  <dimension ref="A1:H924"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33378,6 +33378,53 @@
         </is>
       </c>
     </row>
+    <row r="924">
+      <c r="A924" t="n">
+        <v>915391</v>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>土地徵收之當事人,曾榮耀老師</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>蘇偉強</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>2026/03/17</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915391</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>2026-03-17 12:43:20</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>土地徵收、需用土地人</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>各位同學好
+今日專欄主要說明土地徵收之當事人間之法律關係，而該當事人包含以下三者：
+1. 被徵收人（土地與建物所有權人、他項權利人）
+2. 徵收請求權人（需用土地人）
+3. 徵收權人（代表國家核准徵收的中央主管機關；執行徵收的縣市主管機關）
+按「土地徵收，依本條例之規定，本條例未規定者，適用其他法律之規定」、「本條例所稱主管機關：在中央為內政部；在直轄市為直轄市政府；在縣為縣市政府」、「申請徵收土地或土地改良物，應由需用土地人擬具詳細徵收計畫書，並附具徵收土地圖冊或土地改良物清冊及土地使用計畫圖，送由核准徵收機關核准，並副知該管直轄市或縣（市）主管機關。」、「徵收土地或土地改良物，由中央主管機關核准之」、「徵收土地或土地改良物應發給之補償費，由需用土地人負擔，並繳交該直轄市或縣（市）主管機關轉發之」土地徵收條例第1條第2項、第2條、第13條、第14條、第19條分別定有明文。
+準此，土地徵收之核准機關為內政部，而補償機關為縣市政府，至於公用事業主體則為「需用土地人」之法律地位。次查土地徵收係國家因公共事業之需要，對人民受憲法保障之財產權，經由法定程序予以剝奪之謂。是土地徵收之法律關係，除法律另有規定（如：土地徵收條例第8條、第57條第2項)外，僅屬國家與需用土地人間之函請土地徵收，及國家與私有土地所有權人間之徵收關係等二面關係，需用土地人與所有權人間原則上不具有徵收法律關係。
+參考資料：最高行政法院99年度判字第1146號行政判決</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H924"/>
+  <dimension ref="A1:H925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33425,6 +33425,50 @@
         </is>
       </c>
     </row>
+    <row r="925">
+      <c r="A925" t="n">
+        <v>915405</v>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>租約標示變更登記與土地登記之標示變更登記之不同,許文昌老師</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>2026/03/19</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915405</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>2026-03-19 12:38:19</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>租約標示變更登記、土地登記之標示變更登記</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>市地重劃實施辦法第48條規定：「重劃前訂有耕地三七五租約之土地，如無本條例施行細則第八十九條所定不能達到原租賃目的之情形者，主管機關應於重劃分配結果公告確定後二個月內邀集權利人協調。協調成立者，應於權利變更登記後函知有關機關逕為辦理終止租約登記。協調不成者，應於權利變更登記後函知有關機關逕為辦理租約標示變更登記。」所稱「有關機關」，指鄉（鎮、市、區）公所。所稱「租約標示變更登記」，指三七五租約由重劃前原所有權人之土地存續於重劃後分配與原所有權人之土地。因重劃前原所有權人土地之坐落、地號及面積與重劃後分配與原所有權人土地之坐落、地號及面積不同，故應辦理租約標示變更登記。
+租約標示變更登記與土地登記之標示變更登記之不同如下：
+• (一) 法律性質不同：租約標示變更登記屬於債權（即租約）內容變更登記，土地登記之標示變更登記屬於物權內容變更登記。
+• (二) 登記機關不同：租約標示變更登記由鄉（鎮、市、區）公所辦理，土地登記之標示變更登記由地政事務所辦理。
+• (三) 法律效果不同：租約標示變更登記，非屬登記生效，亦非屬登記對抗，其作用僅是為了行政管理。土地登記之標示變更登記，採登記生效；亦即，登記完畢發生物權變動之效果。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H925"/>
+  <dimension ref="A1:H926"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33469,6 +33469,51 @@
         </is>
       </c>
     </row>
+    <row r="926">
+      <c r="A926" t="n">
+        <v>915419</v>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>廢止徵收之要件,曾榮耀老師</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>蘇偉強</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>2026/03/24</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915419</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:44:46</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>廢止徵收、土地徵收條例</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>國防部因天線移植需要，於民國52年經核准徵收ABCD等四筆土地，且經證實確已依徵收計畫建造天線塔，惟兩座天線塔分別於82年間註銷及移至其他區位，改由市府環保局使用及作公共廁所，後經所有權人提出廢止徵收，試問有無理由？
+參最高行政法院108年度判字第124號行政判決，說明如下：
+• (一) 不論收回權或撤銷、廢止徵收有其各自要件 按私有土地經政府機關依法徵收後，長久期間不為使用或不依核准計畫使用，不但妨礙土地的有效利用，也損害原土地所有權人的權益，而且失去徵收的原意。所以，土地法第219條設有在合致一定要件時，原土地所有權人可以行使收回權的規定，89年2月2日制定的土地徵收條例，於該條例第9條也有關於原土地所有權人行使收回權的規定，並於第61條規定，在土地徵收條例施行前公告徵收的土地，其申請收回，仍依施行前的規定辦理。又土地法並沒有關於撤銷徵收或廢止徵收的規定，對此土地徵收條例則設有專章規範，針對違法或不當的徵收處分，或徵收處分因情事變更無繼續存在必要時，加以撤銷或廢止，使其溯及或向將來失效，來保障被徵收人的權益。惟不論是徵收土地的收回權行使，或者是徵收處分的撤銷或廢止，都各有其不同的要件。
+• (二) 關於徵收處分的廢止，土地徵收條例第49條第2項第2、3款、第4項規定：「已公告徵收之土地，有下列情形之一者，應廢止徵收：......二依徵收計畫開始使用前，興辦之事業改變、興辦事業計畫經註銷、開發方式改變或取得方式改變。三已依徵收計畫開始使用，尚未依徵收計畫完成使用之土地，因情事變更，致原徵收土地之全部或一部已無徵收之必要。」、「前3項規定，於本條例施行前公告徵收之土地，適用之。」依此規定之徵收廢止，應依條文規範之要件逐一檢視是否合致，缺一不可，如需用土地人已依徵收計畫為被徵收土地之完成使用，即無得依前揭規定請求廢止徵收之可言。至於已依徵收計畫完成使用以後，徵收土地用途之變更，乃所有權之一般行使，與因情事變更致無徵收必要之情節無涉，此時，對於土地徵收條例施行後公告徵收之土地，縱或有同條例第9條第1項第3款「依原徵收計畫開始使用後未滿5年，不繼續依原徵收計畫使用」收回權行使之可能，因本件系爭土地之徵收，時間在土地徵收條例89年2月2日施行前之52年間，乃無此規定適用之餘地。
+結論： 系爭被徵收土地已依徵收計畫開始並完成使用，與土地徵收條例第49條第2項第2、3款廢止徵收之要件不符，故不適用廢止徵收。 本件於徵收完成後，確依照徵收計畫建造天線鐵塔，實際進行使用徵收土地達近25年之久，即便事後用地機關就系爭土地放棄原核定之用途另行規劃新的用途，仍屬徵收完畢並已按徵收計畫完成徵收標的物的開發建設，於實際開始使用以後，用地機關才變更其用途者，即屬所有權之一般行使，不涉及「情事變更，致原徵收土地已無使用之必要」。
+參考資料：最高行政法院108年度判字第124號行政判決、臺北高等行政法院 106年度訴字第184號行政判決</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H926"/>
+  <dimension ref="A1:H927"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33514,6 +33514,48 @@
         </is>
       </c>
     </row>
+    <row r="927">
+      <c r="A927" t="n">
+        <v>915428</v>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>平均地權條例第76條之照價收買,許文昌老師</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>2026/03/26</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915428</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>2026-03-26 12:48:26</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>平均地權條例、照價收買、提前收回耕地</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>依平均地權條例第28條規定，照價收買之時機有六種情形（即平均地權條例第16條、第26條、第26條之1、第47條之1、第72條及第76條）。其中，第76條規定：「出租耕地經依法編為建築用地者，出租人為收回自行建築或出售作為建築使用時，得終止租約。依前項規定終止租約，實際收回耕地屆滿一年後，不依照使用計畫建築使用者，直轄市或縣（市）政府得照價收買之。」茲分析如下：
+• (一) 立法意旨： 一般而言，公告土地現值逐年上漲。倘出租耕地經依法編為建築用地，出租人即刻收回耕地，承租人之地價補償（以公告土地現值減除預計土地增值稅後餘額之三分之一為準）偏低。因此，出租人須俟建築使用前一年內，始得收回耕地，以限制出租人提前收回耕地，而影響承租人之補償金額。
+• (二) 實務應用： 平均地權條例第76條提前收回耕地有照價收買制裁之規定，而耕地三七五減租條例第17條第1項第5款提前收回耕地卻無照價收買制裁之規定，二則法條在適用上失其均衡。因此，現行實務依平均地權條例第76條規定提前收回耕地，不予以照價收買之制裁。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H927"/>
+  <dimension ref="A1:H928"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33556,6 +33556,55 @@
         </is>
       </c>
     </row>
+    <row r="928">
+      <c r="A928" t="n">
+        <v>915446</v>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>內政部虛坪改革方向之優缺點,曾榮耀老師</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>蘇偉強</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>2026/03/31</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915446</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:50:39</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>虛坪改革、免計容積、實坪制</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>有關內政部日前虛坪改革方向包括二大重點，首先為檢討「建築技術規則」的「免計容積」規定，希望藉由合理規範社區管理室等公設的設置面積標準，避免出現娛樂交誼廳等不實用的公共設施；其次為修正「公寓大廈管理條例」，將「停車空間」由公共設施改為專有部分，使沒有買車位的住戶可免再負擔車道公設面積。
+目前各方討論之優缺點，簡要整理如下，供同學準備考試之參考：
+• (一) 優點
+1. 實坪制使產權結構更明確，產權面積等於實際使用面積。
+2. 使用者付費，用不到公共設施(如停車空間)不用花錢，使公共設施更公平分攤，公設比下降。
+3. 減少灌水、包裝，避免免計容積(如管委會空間)轉成非必要公共設施(如圖書室)，導致提高公設比及售價。
+• (二) 缺點
+1. 地下停車空間並無獨立性，如何獨立為專有而成為單獨所有權。
+2. 地下停車空間如調整為專有部分後，將出現未購買者得否使用地下公共空間之爭議。
+3. 公設比下降，所減少的面積與價格，可能轉至單價或停車位價格反應，以致於未必能降低房價，減少民眾購屋負擔。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H928"/>
+  <dimension ref="A1:H929"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33605,6 +33605,52 @@
         </is>
       </c>
     </row>
+    <row r="929">
+      <c r="A929" t="n">
+        <v>915459</v>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>債權物權化與物權債權化,許文昌老師</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>2026/04/02</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915459</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>2026-04-02 12:46:24</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>債權物權化、物權債權化</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>• (一) 債權物權化：
+1. 意義：將原本屬於債權效力之法律行為，提升為物權效力。
+2. 舉例： (1)買賣不破租賃：出租人於租賃物交付後，承租人占有中，縱將其所有權讓與第三人，其租賃契約，對於受讓人仍繼續存在。前項規定，於未經公證之不動產租賃契約，其期限逾五年或未定期限者，不適用之（民§425）。 (2)預告登記：不動產物權得喪變更之請求權，原屬債權效力。將此一請求權辦理預告登記後，提升為物權效力，而得以對抗第三人。
+• (二) 物權債權化：
+1. 意義：將原本對於不動產之物權關係，轉化成債權關係。
+2. 舉例： 不動產證券化：投資人直接購買不動產，因而對不動產擁有所有權，屬於物權關係。發行不動產證券化，將其轉化為持有不動產之有價證券，因而對不動產僅擁有債權，屬於債權關係。
+【註】 民：民法。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H929"/>
+  <dimension ref="A1:H930"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33651,6 +33651,62 @@
         </is>
       </c>
     </row>
+    <row r="930">
+      <c r="A930" t="n">
+        <v>915486</v>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>土地徵收之學理類型,曾榮耀老師</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>蘇偉強</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>2026/04/07</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915486</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>2026-04-07 12:55:46</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>土地徵收、公用徵收、開發型徵收、政策性徵收、擴張性徵收</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>• 一、公共利益目的之徵收 此類徵收，係指國家或其他需用土地人基於公益需要，依法取得私有土地之制度。依其徵收目的之不同，尚可細分如下：
+• (一) 為興辦公共事業 依土地徵收條例第3條規定，國家因公益需要，為興辦國防、交通、公用、水利、公共衛生及環境保護等事業，得徵收私有土地。此類徵收之核心，乃在於為特定公共事業之興辦而取得土地，具有典型公用徵收之性質。
+• (二) 作為開發手段 此類徵收之特色，在於徵收之發動仍係基於公共利益及整體開發目的，但開發完成後，部分土地可能轉供私人使用或收益。其常見類型如下：
+1. 產業用地之供給 產業創新條例第42條第1項，中央主管機關或直轄市、縣（市）主管機關為開發產業園區需用私有土地時，得徵收之。
+2. 土地整體開發 土地徵收條例第4條，新設都市地區或舊都市地區等為實施開發建設者，得為區段徵收。學術及實務上常將其認定為開發型徵收。
+3. 都市更新之推動 都市更新條例第43條規定，都市更新事業計畫範圍內重建區段之土地，除以權利變換方式實施外，如由主管機關或其他機關辦理者，另得以徵收、區段徵收或市地重劃方式實施之。
+• 二、基於土地政策或經濟政策目的之徵收 土地法第209條規定：「政府機關因實施國家經濟政策，得徵收私有土地，但應以法律規定者為限。」此類型之徵收，其目的乃落實特定土地政策或經濟政策，故有學者稱之為「政策性徵收」，例如：
+• (一) 土地法第29條規定，對於超過法定限額面積之私有土地，逾期不出賣所為之徵收，以調節地權分配。
+• (二) 依土地法第14條第2項，前項依法不得私有而已成為私有之土地，得依法徵收；其目的在於排除違反公法秩序之私有狀態，使土地權屬回復合法狀態。
+• 三、作為特別犧牲損失補償手段之徵收 對於因公益目的致使用受限制或禁止，而構成特別犧牲之私有土地，國家有時以徵收方式取得其所有權，並以徵收補償填補人民因此所受之特別損失。故徵收於此不僅具有取得土地之功能，亦兼具損失補償之意義。例如：
+• (一) 水土保持法第20條規定經劃定為特定水土保持區之水庫集水區，所設置保護帶內之私有土地得辦理徵收。
+• (二) 野生動物保育法第11條，經劃定為野生動物保護區之土地，必要時，得依法徵收或撥用，交由主管機關管理。
+• 四、擴張性徵收請求 一般徵收後，考量被徵收所有權人之保障，避免其損失擴大，而對於原非屬徵收範圍之土地，於符合一定要件下，基於土地所有權人之申請，得予擴張徵收，例如：
+• (一) 土地徵收條例第8條的「全部」徵收請求權：針對徵收後之不能為相當使用的殘餘部分申請一併徵收。
+• (二) 土地徵收條例第57條的「完全」徵收請求權：就原僅徵收一定空間之區分地上權後，致土地不能為相當使用時，土地所有權人得進一步請求徵收其土地所有權。
+• (三) 土地徵收條例第58條第2項：徵用期間逾3年，所有權人得請求需用土地人徵收土地或土地改良物所有權。
+• T. ABLE_PLACEHOLDER_1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H930"/>
+  <dimension ref="A1:H931"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33707,6 +33707,54 @@
         </is>
       </c>
     </row>
+    <row r="931">
+      <c r="A931" t="n">
+        <v>915498</v>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>物價與不動產價格之關係,許文昌老師</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>2026/04/09</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915498</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:58:12</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>物價上漲率、通貨膨脹、不動產價格</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>• (一) 物價上漲率與通貨膨脹：
+1. 物價上漲率：物價上漲率一般以消費者物價指數為計算依據。消費者物價指數查價項目包括食、衣、住、行、育、樂等消費支出。至於房價及房租是否包括其中，茲說明如下： (1)房價：住宅屬於固定資產。家庭購置住宅為資本性支出，並非消費性支出，故物價上漲率不採計房價。 (2)房租：房租為家庭居住之消費性支出，物價上漲率採計房租。
+2. 通貨膨脹：指在短期間內，一般物價普遍快速上漲。一般而言，消費者物價指數在5%以上，即屬通貨膨脹。
+• (二) 物價上漲對不動產價格之影響：
+1. 物價溫和上漲：物價溫和上漲對不動產價格影響輕微。亦即，物價溫和上漲對不動產價格之影響不顯著。
+2. 物價劇烈上漲：物價在短期間內劇烈上漲，即屬通貨膨脹。此時，貨幣貶值，民眾若持有貨幣就會遭受損失，因而民眾會將貨幣轉換為實體財產（如不動產、黃金等），造成不動產需求增加，不動產價格上漲。因此，物價劇烈上漲會影響不動產價格。
+• (三) 不動產價格上漲對物價之影響：
+1. 不動產價格溫和上漲：不動產價格溫和上漲對物價影響輕微。亦即，不動產價格溫和上漲對物價之影響不顯著。
+2. 不動產價格劇烈上漲：不動產價格在短期間內劇烈上漲，即屬不動產價格高漲或不動產價格飆漲。此時，房租會隨之上漲，而房租為物價之計價項目，最後造成物價上漲。因此，不動產價格劇烈上漲會影響物價。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H931"/>
+  <dimension ref="A1:H932"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33755,6 +33755,48 @@
         </is>
       </c>
     </row>
+    <row r="932">
+      <c r="A932" t="n">
+        <v>915520</v>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>保留徵收與公共設施保留地之比較,曾榮耀老師</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>蘇偉強</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>2026/04/14</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915520</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>2026-04-14 12:59:15</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>保留徵收、公共設施保留地</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>保留徵收與公共設施保留地，雖然同樣都會在正式取得土地前，先對土地使用加以限制，但二者制度依據、功能定位與法律效果並不相同。
+保留徵收係土地法上的制度，係就將來舉辦事業所需土地，預先公告徵收範圍並限制妨礙徵收之使用，其法定事由限於土地法第213條所列事項，且依第214條規定，原則上保留期間不得超過三年，逾期不徵收視為廢止；特定事業始得延長，且延長以五年為限。相對地，公共設施保留地係都市計畫法上的制度，屬都市計畫整體之一部分，都市計畫法第6條及第51條規定其不得為妨礙都市計畫或指定目的之使用，但得繼續為原來之使用或改為妨礙目的較輕之使用。司法院釋字第336號並明白指出，公共設施保留地不能比照土地法上保留徵收，預設取得期限並於屆滿時視為撤銷保留；其存廢應循都市計畫變更程序處理，兩者亦無特別法與普通法之關係。
+• T. ABLE_PLACEHOLDER_1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H932"/>
+  <dimension ref="A1:H933"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33797,6 +33797,67 @@
         </is>
       </c>
     </row>
+    <row r="933">
+      <c r="A933" t="n">
+        <v>915522</v>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>不動產租賃與三七五租佃之法律效力比較,許文昌老師</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>2026/04/16</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915522</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:03:13</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>不動產租賃、三七五租佃、買賣不破租賃</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>應先說明，本比較所稱不動產租賃，指三七五租佃以外之土地或房屋租賃。 不動產租賃與三七五租佃同屬於租賃權。然，二者之法律效力有如天壤之別。茲分析如下：
+• (一) 買賣不破租賃：
+1. 不動產租賃：出租人於租賃物交付後，承租人占有中，縱將其所有權讓與第三人，其租賃契約，對於受讓人仍繼續存在。前項規定，於未經公證之不動產租賃契約，其期限逾五年或未定期限者，不適用之（民§425）。
+2. 三七五租佃：在耕地租期屆滿前，出租人縱將其所有權讓典與第三人，其租佃契約對於受讓受典人仍繼續有效，受讓受典人應會同原承租人申請為租約變更之登記（耕§25）。
+綜上，不動產租賃及三七五租佃皆有「買賣不破租賃」之規定。然，不動產租賃有例外情形（即未經公證之不動產租賃契約，其期限逾五年或未定期限者，不適用之），而三七五租佃無例外情形。 (二)債權物權化：
+1. 不動產租賃：雖因「買賣不破租賃」，而使租賃權物權化。然，不動產租賃權與不動產他項權利競合時，不動產他項權利優先於不動產租賃權。
+2. 三七五租佃：三七五租佃因物權化之結果，而與不動產他項權利立於平等地位。因此，三七五租佃與不動產他項權利之優先性，應視成立先後而定。倘三七五租佃成立在先，則三七五租佃優先於不動產他項權利；倘不動產他項權利成立在先，則不動產他項權利優先於三七五租佃。茲以照價收買發給補償為例： (1)三七五租佃成立在先：照價收買土地設有他項權利者，他項權利補償費由直轄市或縣（市）主管機關於發給土地所有權人之補償地價內代為扣交他項權利人，並塗銷之。但他項權利價值之總和，以不超過該宗土地收買地價扣除土地增值稅及補償耕地承租人之地價後之餘額為限（平施§46Ⅰ）。 (2)抵押權成立在先：照價收買土地設有抵押權者，如其設定登記在耕地租約訂立之前，該抵押權人應優先於耕地承租人受償（平施§46Ⅲ）。
+綜上，不動產租賃與不動產他項權利之法律效力仍受「物權優於債權」之拘束。然，三七五租佃與不動產他項權利之法律效力立於平等地位。(三)終止租約之補償：
+1. 土地徵收：土地徵收所稱應有之負擔，僅限於他項權利價值及依法應補償耕地三七五租約承租人之地價（徵§35Ⅱ），不包括不動產租賃。換言之，徵收之土地，如存在三七五租佃，政府應介入處理，並以補償地價扣除土地增值稅後餘額代為扣交給承租人（平§11ⅠⅡ）；如存在不動產租賃，政府不介入處理。
+2. 市地重劃：(1)不動產租賃：不動產租賃之出租土地，因重劃而不能達到原租賃之目的者，承租人得終止租約，並得向出租人請求相當一年租金之補償（平§63-1）。 (2)三七五租佃：出租之公、私有耕地因實施市地重劃致不能達到原租賃之目的者，由直轄市或縣（市）政府逕為註銷其租約並通知當事人。依前項規定註銷租約者，承租人得依下列規定請求或領取補償：
+• ①重劃後分配土地者，承租人得向出租人請求按重劃計畫書公告當期該土地之公告土地現値三分之一之補償。
+• ②重劃後未受分配土地者，其應領之補償地價，由出租人領取三分之二，承租人領取三分之一。（平§63ⅠⅡ）
+3. 都市更新權利變換：(1)不動產租賃：權利變換範圍內出租之土地及建築物，因權利變換而不能達到原租賃之目的者，租賃契約終止，承租人並得依下列規定向出租人請求補償。但契約另有約定者，從其約定：
+• ①出租土地係供為建築房屋者，承租人得向出租人請求相當一年租金之補償，所餘租期未滿一年者，得請求相當所餘租期租金之補償。
+• ②前款以外之出租土地或建築物，承租人得向出租人請求相當二個月租金之補償。（都更§58Ⅰ）
+• (2) 三七五租佃：權利變換範圍內出租之土地訂有耕地三七五租約者，應由承租人選擇依都市更新條例第60條（分配房地）或耕地三七五減租條例第17條（補償承租人為改良土地所支付之費用、尚未收穫之農作改良物之價額，及終止租約當期之公告土地現值，減除土地增值稅後餘額之三分之一）規定辦理（都更§58Ⅱ）。
+綜上，對三七五租佃之補償額度較多，對不動產租賃補償額度較少，二者之差距甚大。 【註】
+1. 民：民法。
+2. 平：平均地權條例。
+3. 平施：平均地權條例施行細則。
+4. 耕：耕地三七五減租條例。
+5. 都更：都市更新條例。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H933"/>
+  <dimension ref="A1:H934"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33858,6 +33858,47 @@
         </is>
       </c>
     </row>
+    <row r="934">
+      <c r="A934" t="n">
+        <v>915521</v>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>殘餘地一併徵收請求權及接連地損失補償請求權之差異</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>2026/04/21</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915521</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>2026-04-21 12:58:54</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>殘餘地一併徵收、接連地損失補償</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>殘餘地一併徵收與接連地損失補償，皆屬土地所有權人主動提出，惟在制度目的與法律效果上均不相同。
+• T. ABLE_PLACEHOLDER_1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H934"/>
+  <dimension ref="A1:H935"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33899,6 +33899,56 @@
         </is>
       </c>
     </row>
+    <row r="935">
+      <c r="A935" t="n">
+        <v>915552</v>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>預告登記對土地法第34條之1之影響</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915552</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>2026-04-23 12:59:04</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>土地法、預告登記、優先購買權</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>共有人其中一人之土地持分經預告登記後，對土地法第34條之1第1項（多數決）及第4項（優先購買權）之影響，說明如下：
+• (一) 多數決：
+1. 經預告登記部分，不計入同意共有人之人數及應有部分。
+2. 他共有人之應有部分經預告登記且涉及對價或補償者，應提出該共有人已受領與經原預告登記請求權人同意之證明文件及印鑑證明；為該共有人提存者，應提出已於提存書對待給付之標的及其他受取提存物所附之要件欄內記明提存物受取人領取提存物時，須檢附預告登記請求權人同意之證明文件及印鑑證明。登記機關應逕予塗銷該預告登記，於登記完畢後通知預告登記請求權人（土執§9）。
+• (二) 優先購買權：
+1. 經預告登記部分，屬於不同意共有人。據此，部分共有人依土地法第34條之1第1項規定出賣共有土地全部時，不同意共有人有優先購買權。
+2. 預告登記屬於限制登記之一種。所稱限制登記，謂限制登記名義人處分其土地權利所為之登記（登§136Ⅰ）。據此，預告登記僅限制其出賣，未限制其購買，因此經預告登記之共有人仍有優先購買權。
+綜上，共有人其中一人之土地持分經預告登記後，其他共有人仍得依土地法第34條之1第1項出賣其土地，而受預告登記之共有人仍得依土地法第34條之1第4項主張優先購買權。
+【註】
+1. 登：土地登記規則。
+2. 土執：土地法第三十四條之一執行要點。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H935"/>
+  <dimension ref="A1:H936"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33949,6 +33949,55 @@
         </is>
       </c>
     </row>
+    <row r="936">
+      <c r="A936" t="n">
+        <v>915559</v>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>不動產之法律定義</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>2026/04/28</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915559</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>2026-04-28 13:26:50</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>國有財產法、不動產經紀業管理條例、不動產估價、不動產證券化條例、土地法</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>「不動產」因各法規範目的不同，其對不動產之界定範圍並不完全一致。民法著重於物權客體之基本劃分，國有財產法重在國家財產之管理分類，不動產經紀業管理條例偏重交易客體之掌握，不動產估價法制則著眼於估價標的與權利價值之評估，不動產證券化條例更基於金融工具運作需要，而擴大不動產之範圍：
+• 一、相關法規之定義
+• (一) 民法 稱不動產者，謂土地及其定著物。不動產之出產物，尚未分離者，為該不動產之部分(民法§66)。此為我國不動產概念之基本定義，係以「土地」與「定著物」作為不動產之核心範圍。
+• (二) 國有財產法 不動產，指土地及其改良物暨天然資源。而土地及改良物，其定義依土地法之有關規定(國產§3)。所稱天然資源，係指原始森林、天然氣、地熱、溫泉、水資源、地下資源及海底資源等(國有財產法施行細則§4)。可見國有財產法上之不動產概念，較民法更為廣泛，並考量天然資源攸關國計民生，具公益性，不宜被私人壟斷，而將其納入不動產範圍。
+• (三) 不動產經紀業管理條例 不動產，指土地、土地定著物或房屋及其可移轉之權利；房屋指成屋、預售屋及其可移轉之權利(經紀§4)。本條例係以不動產交易管理為目的，因此除物之本體外，亦將可移轉之權利一併納入規範，例如設定地上權房屋之使用權等。
+• (四) 不動產估價師法 不動產估價師受委託人之委託，辦理土地、建築改良物、農作改良物及其權利之估價業務。其中，權利估價，包括地上權、典權、永佃權、農育權、不動產役權、耕作權、抵押權、租賃權、市地重劃、容積移轉及都市更新權利變換之估價(不動產估價技術規則§114)。由此可知，估價法制上之不動產概念，除物之本體外，亦及於附隨其上之各類財產權利。
+• (五) 不動產證券化條例 不動產，指土地、建築改良物、道路、橋樑、隧道、軌道、碼頭、停車場與其他具經濟價值之土地定著物及所依附之設施，但以該設施與土地及其定著物分離即無法單獨創造價值，土地及其定著物之價值亦因而減損者為限(證券§4)。此一定義係基於不動產金融化、收益化之制度目的，故其範圍較一般民法上之不動產概念更為擴張。
+• 二、民法與土地法之比較
+• (一) 意義 土地法並未如民法一般，直接以「不動產」作成統一性定義，而係分別就「土地」與「土地改良物」加以規範。土地法體系下之規範重心，不在抽象之不動產概念，而在以土地為核心，並將附著於土地上、足以增益土地利用價值之改良物納入規範範圍。
+• (二) 定著物及建築改良物 土地法的建築改良物，與民法所稱之定著物，係非土地之構成部分，繼續附著於土地，不易移動其位置，而獨立地達一定經濟上使用目的之物，兩者應可視為同義(參陳立夫，2011，土地法研究(二)，新學林，第11頁)。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H936"/>
+  <dimension ref="A1:H937"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33998,6 +33998,56 @@
         </is>
       </c>
     </row>
+    <row r="937">
+      <c r="A937" t="n">
+        <v>915560</v>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>禁止處分登記對土地法第34條之1之影響</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>2026/04/29</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915560</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:19:18</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>禁止處分登記、優先購買權</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>禁止處分登記包括法院或行政執行分署之禁止處分登記（如查封登記、假扣押登記、假處分登記、破產登記等）及政府機關之禁止處分登記（如地政機關依平均地權條例第59條所為登記、稅捐機關依稅捐稽徵法第24條所為登記、環保機關依土壤及地下水污染整治法第21條所為之登記等）。
+共有人其中一人之土地持分經禁止處分登記後，對土地法第34條之1第1項（多數決）及第4項（優先購買權）之影響，說明如下：
+• (一) 多數決：
+1. 經禁止處分登記部分，不計入同意共有人之人數及應有部分。
+2. 徵詢原囑託法院或機關： (1)無礙執行效果：他共有人之應有部分經法院或行政執行分署囑託查封、假扣押、假處分、暫時處分、破產登記或因法院裁定而為清算登記者，登記機關應依規定徵詢原囑託或裁定機關查明有無妨礙禁止處分之登記情形，無礙執行效果者，應予受理登記，並將原查封、假扣押、假處分、暫時處分、破產登記或法院裁定開始清算程序事項予以轉載，登記完畢後通知原囑託或裁定機關及債權人（土執§9⑥）。 (2)有礙執行效果：徵詢結果，有礙執行效果者，應以書面敘明理由及法令依據，駁回登記之申請（土執§9⑥）。 此外，他共有人之應有部分經有關機關依法律囑託禁止處分登記者，登記機關應洽原囑託機關意見後，依上開規定辦理（土執§9⑥）。
+• (二) 優先購買權：
+1. 有礙執行效果：部分共有人不能依土地法第34條之1第1項出賣共有土地全部，因此無優先購買權可言。
+2. 無礙執行效果： (1)登記機關徵詢原囑託法院或機關結果，無礙執行效果，因此准於辦理部分共有人依土地法第34條之1第1項出賣其土地之登記。 (2)經禁止處分登記部分，屬於不同意共有人。據此，部分共有人依土地法第34條之1第1項規定出賣共有土地全部時，不同意共有人有優先購買權。 (3)禁止處分登記屬於限制登記之一種。所稱限制登記，謂限制登記名義人處分其土地權利所為之登記（登§136Ⅰ）。據此，禁止處分登記僅限制其出賣，未限制其購買，因此經禁止處分登記之共有人仍有優先購買權。
+【註】
+1. 登：土地登記規則。
+2. 土執：土地法第三十四條之一執行要點。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H937"/>
+  <dimension ref="A1:H938"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34048,6 +34048,64 @@
         </is>
       </c>
     </row>
+    <row r="938">
+      <c r="A938" t="n">
+        <v>915580</v>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>房屋稅計算範例</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>2026/05/05</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915580</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:09:13</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>房屋稅課稅、房屋稅</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t xml:space="preserve">甲為自然人，於115年期房屋稅課稅年度持有下列9戶住家用房屋，均坐落於臺中市，且均為甲單獨所有。甲已於法定期限內完成相關使用情形申報，且各戶均全年持有、全年使用情形不變。試問：甲114年期各戶房屋之房屋課稅現值、適用稅率及應納房屋稅各為多少？總應納房屋稅為多少？
+• T. ABLE_PLACEHOLDER_1
+註：請依據所附各縣市適用稅率級距計算。
+[圖片1]
+解答
+• (一) 計算各戶房屋現值
+房屋現值＝核定單價 × 面積 ×（1－折舊率 × 折舊年數）× 路段率
+• T. ABLE_PLACEHOLDER_2
+• (二) 判斷各房屋適用稅率
+本題應先依房屋使用情形分類，而非單純以甲持有9戶全部合併適用同一稅率。
+1. 自住住家用房屋 A、B屋均供自住使用，且已設戶籍，合計2戶，未超過全國3戶限制，故適用自住住家用稅率：A、B屋＝1.2%。
+2. 出租達租金標準及繼承取得共有房屋 C屋為出租且申報所得達租金標準；D、I屋為繼承取得共有房屋。C、D、I合計為3戶，屬4戶以下，故適用稅率：C、D、I屋＝1.5%。
+3. 其他非自住住家用房屋 E、F、G、H屋均為空置未使用，屬其他非自住住家用房屋合計4戶，屬3至4戶級距，故適用較高稅率：E、F、G、H屋＝3.8%。
+• (三) 計算各戶應納房屋稅
+• T. ABLE_PLACEHOLDER_3
+因此，甲114年期房屋稅總額為各戶加總＝172,220元。
+## 文章圖片
+![圖片1](./images/915580_682b6f97.png)
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H938"/>
+  <dimension ref="A1:H939"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34106,6 +34106,51 @@
         </is>
       </c>
     </row>
+    <row r="939">
+      <c r="A939" t="n">
+        <v>915613</v>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>土地登記效力之態樣</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>2026/05/07</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915613</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>2026-05-07 13:41:15</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>土地登記、不動產物權</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>我國土地登記效力之態樣有三：
+• (一) 登記生效要件主義：亦稱設權登記；凡基於法律行為之不動產物權登記，皆採登記生效要件主義。意謂須經土地登記完畢，始發生不動產物權變動之效力。換言之，不動產物權，依法律行為而取得、設定、喪失及變更者，非經登記，不生效力（民§758I）。
+• (二) 登記處分要件主義：亦稱宣示登記；凡基於非法律行為之不動產物權變動，皆採登記處分要件主義。意謂於事實發生時，不待登記，即發生不動產物權變動之效力。惟日後擬處分該不動產物權，須先辦理土地登記。換言之，因繼承、強制執行、徵收、法院之判決或其他非因法律行為，於登記前已取得不動產物權者，應經登記，始得處分其物權（民§759）。
+• (三) 登記對抗要件主義：凡屬債權登記，皆採登記對抗要件主義。意謂債權於契約成立時，即發生效力，登記之作用在於公示，以對抗第三人。如民法第826條之1、第836條之1、第836條之2、第841條之2、第873條之1、第913條等是。
+【註】
+民：民法。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H939"/>
+  <dimension ref="A1:H940"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34151,6 +34151,47 @@
         </is>
       </c>
     </row>
+    <row r="940">
+      <c r="A940" t="n">
+        <v>915666</v>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>耕地租用、租佃與租賃規定之比較</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>2026/05/12</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915666</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>2026-05-12 13:51:23</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>耕地租用、耕地三七五減租條例、收回自耕</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>耕地租用，具有濃厚之農地政策與社會保護色彩，與一般房屋或基地租賃不同。其制度設計，不僅涉及租賃契約之私法關係，更與扶植自耕農、保障農民生活、維持農業生產秩序及因應農地政策調整密切相關。故我國法制上，除土地法就耕地租用之成立、地租、擔保、終止及爭議處理設有規範外，並另以耕地三七五減租條例作為特別法，建立較強之承租人保護體系；其後，農業發展條例於民國89年修正施行後，對新訂立之農業用地租賃契約，則改採較強調契約自由與農業經營彈性之制度。是以，耕地租用之說明，應特別區分舊制耕地租佃關係與89年後新制農業用地租賃之適用範圍與法律效果。
+• T. ABLE_PLACEHOLDER_1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H940"/>
+  <dimension ref="A1:H941"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34192,6 +34192,55 @@
         </is>
       </c>
     </row>
+    <row r="941">
+      <c r="A941" t="n">
+        <v>915674</v>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>公同共有繼承登記及分別共有繼承登記</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915674</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:27:36</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>公同共有繼承登記、分別共有繼承登記</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>繼承登記分為公同共有繼承登記與分別共有繼承登記二種。遺產分割前辦理公同共有繼承登記，遺產分割後辦理分別共有繼承登記。實務上，繼承人得直接辦理分別共有繼承登記；繼承人亦得先辦理公同共有繼承登記，日後再辦理分別共有繼承登記。採用前者或後者，視其符合申請條件而定。
+• (一) 公同共有繼承登記與分別共有繼承登記之比較：
+1. 申請人不同： (1)公同共有繼承登記：由任何繼承人為全體繼承人申請之（土§73I）。詳言之，繼承人為二人以上，部分繼承人因故不能會同其他繼承人共同申請繼承登記時，得由其中一人或數人為全體繼承人之利益，就被繼承人之土地，申請為公同共有之登記（登§120I）。 (2)分別共有繼承登記：經繼承人全體同意，得申請為分別共有登記（登§120I）。另，共有人不得以土地法第34條之1多數決將共有不動產由公同共有型態變更為分別共有型態。
+2. 繳納遺產稅不同： (1)公同共有繼承登記：繼承人為二人以上時，經部分繼承人按其法定應繼分繳納部分遺產稅款、罰鍰及加徵之滯納金、利息後，為辦理不動產之公同共有繼承登記，得申請主管稽徵機關核發同意移轉證明書；該登記為公同共有之不動產，在全部應納款項未繳清前，不得辦理遺產分割登記或就公同共有之不動產權利為處分、變更及設定負擔登記（遺贈 §41-1）。 (2)分別共有繼承登記：繳清全部遺產稅款、罰緩及加徵之滯納金、利息後，始得辦理分別共有登記。遺產稅未繳清前，不得分割遺產、交付遺贈或辦理移轉登記（遺贈§8I）。
+3. 效力不同： (1)公同共有繼承登記：繼承登記後，繼承人對該不動產維持公同共有關係（即共有人之間無持分劃分權利範圍）。 (2)分別共有繼承登記：繼承登記後，繼承人對該不動產維持分別共有關係（即共有人之間有持分劃分權利範圍）。
+• (二) 法規應用：
+1. 土地或建築改良物，自繼承開始之日起逾一年未辦理繼承登記者，經該管直轄市或縣市地政機關查明後，應即公告繼承人於三個月內聲請登記，並以書面通知繼承人；逾期仍未聲請者，得由地政機關予以列冊管理。前項列冊管理期間為十五年，逾期仍未聲請登記者，由地政機關書面通知繼承人及將該土地或建築改良物清冊移請財政部國有財產署公開標售。經五次標售而未標出者，登記為國有（土§73-1）。 上開所稱繼承登記，包括公同共有繼承登記及分別共有繼承登記。換言之，凡辦竣公同共有繼承登記或分別共有繼承登記，皆不必受土地法第73條之1之拘束。
+2. 下列土地不得移轉、設定負擔或租賃於外國人：(1)林地；(2)漁地；(3)狩獵地；(4)鹽地；(5)礦地；(6)水源地；(7)要塞軍備區域及領域邊境之土地。前項移轉，不包括因繼承而取得土地。但應於辦理繼承登記完畢之日起三年內出售與本國人，逾期未出售者，由直轄市、縣（市）地政機關移請國有財產署辦理公開標售（土§17）。 上開繼承登記，因公同共有繼承登記與分別共有繼承登記而產生不同效果： (1)倘繼承登記為公同共有繼承登記，如繼承人其中一人為外國人，則該外國人不得就其公同共有部分單獨出售。日後，國有財產署亦不得針對該公同共有部分辦理公開標售。 (2)倘繼承登記為分別共有繼承登記，如繼承人其中一人為外國人，則該外國人得就其分別共有部分單獨出售。日後，國有財產署亦得針對該分別共有部分辦理公開標售。
+3. 土地經辦理查封、假扣押、假處分、暫時處分、破產登記或因法院裁定而為清算登記後，未為塗銷前，登記機關應停止與其權利有關之新登記。但公同共有繼承登記者，不在此限（登§141I）。上開禁止處分登記後，尚得辦理公同共有繼承登記，但不得辦理分別共有繼承登記。
+【註】 土：土地法。 登：土地登記規則。 遺贈：遺產及贈與稅法。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H941"/>
+  <dimension ref="A1:H942"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34241,6 +34241,46 @@
         </is>
       </c>
     </row>
+    <row r="942">
+      <c r="A942" t="n">
+        <v>915681</v>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>耕地不同原因收回之補償比較</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915681</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>2026-05-19 14:33:04</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>平均地權條例、改良土地</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>• T. ABLE_PLACEHOLDER_1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H942"/>
+  <dimension ref="A1:H943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34281,6 +34281,51 @@
         </is>
       </c>
     </row>
+    <row r="943">
+      <c r="A943" t="n">
+        <v>915691</v>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>地籍圖重測申請複丈之要件</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>2026/05/21</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915691</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>2026-05-21 14:38:13</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>地籍測量、複丈</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>土地法第46條之3第1項及第2項規定：「重新實施地籍測量之結果，應予公告，其期間為三十日。土地所有權人認為前項測量結果有錯誤，除未依前條之規定設立界標或到場指界者外，得於公告期間內，向該管地政機關繳納複丈費，聲請複丈。經複丈者，不得再聲請複丈。」準此，土地所有權人申請複丈之要件如下：
+• (一) 土地所有權人認為測量結果有錯誤：倘非屬土地所有權人認為測量結果有錯誤，而是土地所有權人以指界錯誤之由，不得申請複丈（司法院釋字第374號解釋）。
+• (二) 土地所有權人依規定設立界標或到場指界：倘土地所有權人未依規定設立界標或到場指界，不得申請複丈。
+• (三) 公告期間內提出：重新實施地籍測量之結果，應公告30日。土地所有權人應於前揭公告期間內申請複丈，逾期不得申請複丈。
+• (四) 繳納複丈費：土地所有權人應依規定繳納複丈費。倘複丈結果有錯誤，已繳複丈費予以退還。
+• (五) 複丈以一次為限：複丈僅限一次，不得申請再複丈。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H943"/>
+  <dimension ref="A1:H945"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34326,6 +34326,111 @@
         </is>
       </c>
     </row>
+    <row r="944">
+      <c r="A944" t="n">
+        <v>915718</v>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>建物測量成果圖與建物標示圖之差異</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915718</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:39:46</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>建物測量成果圖、建物標示圖</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>兩者目的皆是為申辦建物所有權第一次登記，圖資內容也都包含建物平面圖與位置圖，惟其差異如下：
+1. 意義(1)建物測量成果圖 建物第一次測量，應測繪建物位置圖及其平面圖。登記機關於測量完竣後，應發給建物測量成果圖。因此，建物測量成果圖即向登記機關申辦建物第一次測量所繪製之平面圖與位置圖成果。 (2)建物標示圖 申請建物所有權第一次登記前，應先向登記機關申請建物第一次測量。但在中華民國102年10月1日以後領有使用執照之建物，檢附依使用執照竣工平面圖繪製及簽證之建物標示圖辦理登記者，不在此限。亦即建物標示圖係直接依據使用執照竣工圖說繪製平面圖與位置圖，免向登記機關申辦建物第一次測量，縮短申請建物所有權第一次登記辦理時間。
+2. 過程 (1)建物測量成果圖：應向登記機關申辦建物第一次測量。 (2)建物標示圖：免向登記機關申辦建物第一次測量。
+3. 繪製者 (1)建物測量成果圖
+• A.由登記機關實地測量。
+• B.於實施建築管理地區，依法建造完成之建物，其建物第一次測量，得依使用執照竣工圖說轉繪建物平面圖及位置圖，免通知實地測量。依規定轉繪之建物平面圖及位置圖，得由開業之建築師、測量技師、地政士或其他與測量相關專門職業及技術人員為轉繪人。
+• (2) 建物標示圖 應由開業之建築師、測量技師或其他依法規得為測量相關簽證之專門職業及技術人員辦理依使用執照竣工平面圖繪製及簽證。</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="n">
+        <v>915719</v>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>土地登記之更正與地籍測量之更正的比較</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915719</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:39:52</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>土地登記之更正、地籍測量之更正</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>• (一) 土地登記之更正：登記人員或利害關係人，於登記完畢後，發現登記錯誤或遺漏時，非以書面聲請該管上級機關查明核准後，不得更正。但登記錯誤或遺漏，純屬登記人員記載時之疏忽，並有原始登記原因證明文件可稽者，由登記機關逕行更正之（土§69）。
+• (二) 地籍測量之更正：已辦地籍測量之地區，發現錯誤，除有下列情形之一者，得由登記機關逕行辦理更正外，應報經直轄市或縣（市）主管機關核准後始得辦理：
+1. 原測量錯誤純係技術引起。
+2. 抄錄錯誤。
+前項第1款所稱原測量錯誤純係技術引起，指原測量錯誤純係觀測、量距、整理原圖、訂正地籍圖或計算面積等錯誤所致，並有原始資料可稽：第2款所稱抄錄錯誤，指錯誤因複丈人員記載之疏忽所引起，並有資料可資核對（測§232）。
+• (三) 兩者比較：
+1. 相同點： (1)二者同屬地籍錯誤之更正。 (2)二者皆須報請直轄市或縣（市）主管機關核准。
+2. 相異點：(1)原因不同：
+• ①土地登記之更正： 發生原因有二： A.登記錯誤：指登記事項與登記原因證明文件所載之內容不符者（登§13）。 B.登記遺漏：指應登記事項而漏未登記者（登§13）。
+• ②地籍測量之更正： 發生原因有二： A.測量錯誤：指施測方法所發生之錯誤。 B.抄錄錯誤：指複丈人員記載所發生之錯誤。
+• (2) 條件不同：
+• ①土地登記之更正：土地登記之更正須「不得違反原登記之同一性」（即不得變更原登記之法律關係）。此乃權利關係不實受土地法第43條（登記公信力）之保護。
+• ②地籍測量之更正：地籍測量之更正無須「不得違反原登記之同一性」。此乃土地位置、土地形狀、土地面積等測量不實不受土地法第43條（登記公信力）之保護。
+• (3) 逕行更正情形不同：
+• ①土地登記之逕行更正：登記錯誤或遺漏，純屬登記人員記載時之疏忽，並有原始登記原因證明文件可稽者，由登記機關逕行更正之（土§69）。
+• ②地籍測量之逕行更正：登記機關逕行更正之情形有二： A.原測量錯誤纯係技術引起：指原測量錯誤纯係觀測、量距、整理原圖、訂正地籍圖或計算面積等錯誤所致，並有原始資料可稽。 B.抄錄錯誤：指錯誤因複丈人員記載之疏忽所引起，並有資料可資核對。（測§232）
+【註】
+1. 土：土地法。
+2. 登：土地登記規則。
+3. 測：地籍測量實施規則。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H945"/>
+  <dimension ref="A1:H946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34431,6 +34431,55 @@
         </is>
       </c>
     </row>
+    <row r="946">
+      <c r="A946" t="n">
+        <v>915731</v>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>私有土地面積最高額限制</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915731</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>2026-06-02 15:57:07</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>私有土地、私有建築用地、土地面積最高額</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>• (一) 一般性規定
+1. 原則 (1)直轄市或縣（市）政府對於私有土地，得斟酌地方情形，按土地種類及性質，分別限制個人或團體所有土地面積之最高額(土法§28 I)。旨在防止土地集中與壟斷，並兼顧土地之適當分配與利用。 (2)限制私有土地面積之最高額，應經中央地政機關之核定(土法§28 II)。
+2. 標準 依土地法第28條限制土地面積最高額之標準，應分別宅地、農地、興辦事業等用地(土法施§7)規範之： (1)宅地以十畝（10市畝=66.67公畝=2,016.67坪）為限。 (2)農地以其純收益足供一家十口之生活為限。 (3)興辦事業用地視其事業規模之大小定其限制。
+3. 處理 (1)私有土地受土地面積最高額限制時，由該管直轄市或縣（市）政府規定辦法，限令於一定期間內，將額外土地分劃出賣(土法§29 I)。 (2)不依規定分劃出賣者，該管直轄市或縣（市）政府得依本法徵收之(土法§29 II)。 (3)徵收之補償地價，得斟酌情形搭給土地債券(土法§29 III)。
+• (二) 尚未建築之私有建築用地
+1. 原則 直轄市或縣（市）政府對於尚未建築之私有建築用地，應限制土地所有權人所有面積之最高額(平權§71 I)，以防止尚未建築建築用地過度集中與囤積，促進建築用地之利用。
+2. 標準 (1)以十公畝(302.5坪)為限(平權§71 II前段)。 (2)但工業用地、學校用地及經政府核准之大規模建築用地，應視其實際需要分別訂定之(平權§71 II後段)。 又計算尚未建築土地面積最高額時，對於因法令限制不能建築之土地，應予扣除(平權§71 III)。
+3. 處理 (1)超額土地，直轄市或縣（市）政府應通知土地所有權人於二年內出售或建築使用(平權§72 I前段)。 (2)逾期未出售或未建築使用者，得予照價收買，整理後出售與需用土地人建築使用(平權§72 I中段)。 (3)但在建設發展較緩之地段，不在此限(平權§72 I後段)。所稱建設發展較緩之地段，指公共設施尚未完竣地區或依法不得核發建造執照之地區。其範圍由直轄市或縣(市)主管機關劃定，作為限制最高額土地之依據(平權施§96)。
+• T. ABLE_PLACEHOLDER_1
+註：於尚未建築之私有建築用地，應優先適用平均地權條例；至其餘私有土地，則回歸土地法之一般規定。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H946"/>
+  <dimension ref="A1:H947"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34480,6 +34480,55 @@
         </is>
       </c>
     </row>
+    <row r="947">
+      <c r="A947" t="n">
+        <v>915753</v>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>地價稅及空地稅之計算實例</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>2026/06/04</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915753</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:32:09</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>地價稅、空地稅</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t xml:space="preserve">甲於台北市有一筆土地，面積500平方公尺，申報地價每平方公尺800元，設台北市累進起點地價50,000元，空地稅按地價稅基本稅額加徵二倍，試計算甲應繳納多少地價稅及空地稅？
+【解答】
+• (一) 地價稅：[圖片1]
+1. 申報地價總額： 800×500＝400,000元
+2. 地價稅： 50,000×10‰+(300,000-50,000)×15‰+(400,000-300,000)×25‰＝6,750元
+• (二) 空地稅： 400,000×10‰＝4,000元 4,000×2＝8,000元
+答：地價稅為6,750元，空地稅8,000元。
+## 文章圖片
+![圖片1](./images/915753_518d7125.png)
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H947"/>
+  <dimension ref="A1:H948"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34529,6 +34529,50 @@
         </is>
       </c>
     </row>
+    <row r="948">
+      <c r="A948" t="n">
+        <v>915777</v>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>一般徵收與區段徵收之差異</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915777</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>2026-06-09 14:20:18</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>一般徵收、區段徵收</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>• 一、一般徵收之概念 一般徵收，係指國家因公益之必要，為興辦特定公用事業，依法一次個別的取得私有土地或土地改良物所有權之制度。其目的在於取得特定公用事業所必需之土地，屬土地徵收制度中最基本、最典型之類型。其法律效果，係由需用土地人終局取得土地或土地改良物所有權，而原所有權人及其他權利人之權利義務，於補償完竣時終止。
+• 二、區段徵收之概念 區段徵收，係指國家基於新都市開發、舊都市更新或其他整體開發建設之需要，對一定區域內之土地，因應重新分宗整理之必要，而就全區土地予以徵收之制度。其於完成公共設施開闢、土地整理及重行分配後，再將部分土地分配予原土地所有權人或予以處分，以達成整體開發之目的。故區段徵收不僅具有徵收之性質，並兼具土地整理、公共設施配置及開發利益分配之功能。土地法第212條即明定：「於一定區域內之土地，應重新分宗整理，而為全區土地之徵收」。應特別注意的是，區段徵收雖具有「共同開發、利益共享」之制度特徵，且往往帶有較明顯之財務與開發效益分配考量，但其本質上仍屬土地徵收之一種類型，具有公權力強制性，並非以土地所有權人自主合意參與為前提，故與一般合意共同開發有本質上之差異。
+• 三、一般徵收與區段徵收之比較 一般徵收係以取得特定公共事業所需土地為目的之基本型徵收；區段徵收則係以一定區域整體開發為目的之開發型徵收。二者雖同屬土地取得制度，但其制度目的、適用情形、取得範圍、補償方式等均不相同。
+• T. ABLE_PLACEHOLDER_1
+資料來源：曾榮耀編撰，2026，土地法規理論與實務，高點文化。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H948"/>
+  <dimension ref="A1:H949"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34573,6 +34573,49 @@
         </is>
       </c>
     </row>
+    <row r="949">
+      <c r="A949" t="n">
+        <v>915812</v>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>土地稅有關一處、一次、一屋、一戶之綜合整理</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915812</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>2026-06-11 15:33:34</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>自用住宅用地、地價稅、土地增值稅</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>• (一) 一處：自用住宅用地之地價稅適用優惠稅率（2‰），土地所有權人與其配偶及未成年之受扶養親屬以一處為限。
+• (二) 一次：自用住宅用地之土地增值稅適用優惠稅率（10%），一人一生以一次為限。
+• (三) 一屋：自用住宅用地之土地增值稅適用一人一生一次優惠稅率（10%）後，如再出售自用住宅用地時，土地所有權人與其配偶及未成年子女，無該自用住宅以外之房屋（即僅有一屋），則不受前揭一次之限制（亦即，仍得再適用10%之優惠稅率，而無次數之限制）。
+• (四) 一戶：自住房屋之房屋稅優惠稅率（1%），所有權人、配偶及未成年子女於全國僅持有一戶房屋，始得適用。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H949"/>
+  <dimension ref="A1:H950"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34616,6 +34616,54 @@
         </is>
       </c>
     </row>
+    <row r="950">
+      <c r="A950" t="n">
+        <v>915843</v>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>不動產經紀人證書被撤銷</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915843</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>2026-06-16 16:23:51</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>不動產經紀人證書</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>近來某議員的不動產經紀人證書經網紅檢舉遭內政部及台北市政府撤銷，其主要原因在不動產經紀業管理條例有規範經紀人員的積極資格與消極資格：
+• (一) 積極資格 中華民國國民經不動產經紀人考試及格並依本條例領有不動產經紀人證書者，得充不動產經紀人。(經§13) 經不動產經紀人考試及格者，應具備一年以上經紀營業員經驗，始得向直轄市或縣 (市) 政府請領經紀人證書。(經§14)
+• (二) 消極資格 有第六條第一項第一款至第四款或第七款情形之一者，不得充任經紀人員。已充任者，應撤銷或廢止其證書或證明。(經§14)
+1. 無行為能力或限制行為能力者。
+2. 受破產之宣告尚未復權者。
+3. 犯詐欺、背信、侵占罪、性侵害犯罪防治法第二條所定之罪、組織犯罪防制條例第三條第一項、第二項、第六條、第九條之罪，經受有期徒刑一年以上刑之宣告確定，尚未執行完畢或執行完畢或赦免後未滿三年者。但受緩刑宣告者，不在此限。
+4. 受感訓處分之裁定確定，尚未執行完畢或執行完畢後未滿三年者。
+5. 受停止執行業務處分尚未執行完畢，或廢止經紀人員證書或證明處分未滿五年者。
+其中，主要是對於曾犯詐欺、侵占、背信、貪污等誠信犯罪者予以限制，以保障不動產交易安全。因此，該議員必須要在執行完畢滿三年才能重新申領證書。但應注意並非撤銷其考試及格證書，而是撤銷經紀人證書。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H950"/>
+  <dimension ref="A1:H951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34664,6 +34664,50 @@
         </is>
       </c>
     </row>
+    <row r="951">
+      <c r="A951" t="n">
+        <v>915846</v>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>優先購買權之法律性質</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915846</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:09:54</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>優先購買權</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t xml:space="preserve">優先購買權有請求權性質及形成權性質二說。通說採形成權性質。亦即因優先購買權人一方之意思表示，而使法律關係發生變動。然，若優先購買權人須向政府申請核准，始得適用，宜採請求權性質。如土地法第73條之1、地籍清理條例第12條、祭祠公業條例第52條等是。
+茲以下圖表示優先購買權法律性質及效力之架構。 [圖片1]
+## 文章圖片
+![圖片1](./images/915846_2fa2dcf2.png)
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H951"/>
+  <dimension ref="A1:H952"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34708,6 +34708,50 @@
         </is>
       </c>
     </row>
+    <row r="952">
+      <c r="A952" t="n">
+        <v>915870</v>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>耕地承租人未自任耕作之效力</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>2026/06/23</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915870</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>2026-06-23 14:24:08</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>自任耕作</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>各位同學好 本週專欄來談有關於土地法上課提到的耕地租用(佃)之概念，根據最高法院112年度台上字第2852號民事判決為案例，茲整理重點如下：
+• A. 為甲土地之所有權人，於民國64年間將甲土地出租予B之被繼承人耕作，雙方並約定承租人不得擅自興建建物或變更土地用途。嗣後，B之被繼承人於甲土地上興建鐵架、水塔及建物，並將部分建物作為餐廳營業使用。其後，B之被繼承人死亡，B等人為其全體繼承人。 A主張，B之被繼承人未自任耕作，且將耕地作為非農業使用，已違反耕地租約及耕地三七五減租條例之規定，故租約應屬無效。A遂依所有物返還請求權及不當得利之規定，請求B拆除地上物、返還甲土地，並給付相當於租金之不當得利。 B則抗辯，B之被繼承人與A間另有租地建屋契約，並非無權占有；且A長期知悉地上物存在，仍收取相關款項，嗣後始請求拆屋還地，應有違誠信原則及權利失效。試問：A之請求有無理由？
+判決重點 按承租人應自任耕作，並不得將耕地全部或一部轉租於他人。承租人違反前項規定時，原訂租約無效，得由出租人收回自行耕種或另行出租，耕地三七五減租條例第16條第1、2項定有明文。所謂自任耕作，係指承租人應以承租土地供自己從事耕作之用；若承租人以承租土地建築房屋、居住或供其他非耕作使用，均屬未自任耕作。即使未自任耕作情形僅存在於承租土地之一部，全部租約仍向後歸於無效，租賃關係消滅，且不因出租人嗣後繼續收取費用，而使無效之租約恢復效力。
+本題結論 本題中，B之被繼承人承租A所有之甲土地後，並未將土地作為耕作使用，反而於其上興建地上物，並將部分建物作為餐廳營業使用，已屬未自任耕作。依耕地三七五減租條例第16條規定，原耕佃租約應向後歸於無效。又B主張另有租地建屋契約，若未能證明其存在，且A縱曾收取相關費用，也不當然使無效租約恢復效力。因此，B繼承人占有甲土地欠缺合法權源，A依民法第767條第1項請求拆除地上物、返還土地，並依民法第179條請求相當於租金之不當得利，應屬有理由。
+資料來源：參考最高法院112年度台上字第2852號民事判決。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H952"/>
+  <dimension ref="A1:H953"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34752,6 +34752,49 @@
         </is>
       </c>
     </row>
+    <row r="953">
+      <c r="A953" t="n">
+        <v>915885</v>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>股市與房市之關連性</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915885</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:03:36</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>股市與房市</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>就一般民眾而言，最常見之投資標的不外股票及房屋。因此，股市與房市呈現關連性。
+• (一) 股市與房市同方向發展：民眾投資股市，所賺到的錢，累積至一定金額，就會去購買房屋。因此，股市與房市同方向發展。亦即，股市繁榮，房市跟著繁榮。
+• (二) 股市與房市反方向發展：民眾投資股市，所賺到的錢，不去購買房屋，而是再投入股市，造成股市有泡沫化現象。因為房市管制嚴格，獲利有限，且房市正值不景氣，無利可圖。最後造成股市與房市反方向發展。亦即，股市繁榮，房市蕭條。
+綜上，現階段股市與房市呈現反方向發展，就如同上開(二)所述。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H953"/>
+  <dimension ref="A1:H954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34795,6 +34795,58 @@
         </is>
       </c>
     </row>
+    <row r="954">
+      <c r="A954" t="n">
+        <v>915903</v>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>租約租用(佃)的自任耕作意涵</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915903</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:53:20</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>三七五租約續訂登記、自任耕作</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>• 一、案例事實 甲公司所有A、B、C等多筆土地，長期出租予乙等人或其先人作為魚塭、養殖使用，雙方曾簽訂多份土地租賃契約。租期屆滿後，乙等人主張雙方間為耕地三七五租賃關係，且乙等人願意繼續承租，遂請求甲公司會同辦理三七五租約續訂登記。 甲公司則抗辯：乙等人在魚塭旁搭建塭寮、簡易房舍、貨櫃、水泥路、神明廳、廚房、床鋪、衛浴等設施，已非單純養殖使用，而有在承租土地上建築房屋供居住使用、未自任耕作之情形；同時，部分承租人未居住於當地、另有工作或不具自耕能力，亦不得主張續租。 試問：乙等人請求甲公司會同辦理三七五租約續訂登記，有無理由？
+• 二、相關法條
+1. 農業發展條例第20條規定，民國89年1月4日修正施行後所訂立的農業用地租賃契約，原則上不適用耕地三七五減租條例；但在該日以前已依三七五條例、土地法或其他法律訂定租約者，除另有約定外，其權利義務、續約、修正及終止，仍依原法律規定。
+2. 土地法第106條規定，以自任耕作為目的，約定支付地租使用他人農地者，為耕地租用；且耕作包括漁牧。
+3. 耕地三七五減租條例第6條第1項規定，耕地租約應以書面為之；租約的訂立、變更、終止或換訂，應由出租人會同承租人申請登記。
+4. 耕地三七五減租條例第16條規定，承租人應自任耕作，並不得將耕地全部或一部轉租於他人；違反者，原訂租約無效，出租人得收回自行耕種或另行出租。
+5. 耕地三七五減租條例第20條規定，耕地租約於租期屆滿時，除出租人依本條例收回自耕外，如承租人願繼續承租者，應續訂租約。
+• 三、重要判決觀念以下判決文字為配合案例說明，已將當事人及土地資料改以代號表示。
+1. 所謂承租人應「自任耕作」，係指承租人應以承租之土地供自己從事耕作之用而言，解釋上並非播種、施肥、去草、除蟲、採收等農作過程，悉須由承租人本人親自為之。苟將農作過程之一部分交與他人操作，而本身仍總理其事者，仍不違自耕之本旨，殊非法所不許（最高法院85年度台上字第423號判決意旨參照）。
+2. 於A、B、C等承租土地上所搭建之建物，係用以放置養殖所需飼料及工具等物品，而水產養殖需要較多人力與時間投入，甚至需要守夜以免遭到偷竊，塭寮內為此設計休憩及用餐空間，亦與養殖有合理關聯性。至於神明廳，僅係供承租人乙等人自行祭拜，祈求進行養殖工作能夠平安豐收，使人心靈上得到安全感並保有希望，從民間信仰與精神層面上觀之，亦應認與養殖間具有合理關聯。是揆諸首揭說明，自難認乙等人有不自任耕作之情。
+3. 訂立三七五租約，並無限制承租人需設戶籍於當地、不得另有工作之條件，尚難以承租人未設籍於當地、另有工作，遽認承租人不具自耕能力或未自任耕作；且縱承租人未能悉數親自操作全部農事作業，但以自己為耕作主體，總理其事，而委由其親屬參與協助耕作或僱請第三人操作部分者，即尚難謂不自任耕作或係將耕地轉租於他人。
+• 四、結論 乙等人請求甲公司會同辦理三七五租約續訂登記，有理由。 本案重點有三：第一，系爭租約可認定在民國89年1月4日前即已簽訂，仍有耕地三七五減租條例適用；第二，土地法第106條所稱耕作包括漁牧，因此魚塭養殖仍可能屬耕地租用範圍；第三，乙等人雖於土地上設置塭寮、簡易房舍、神明廳、廚房、床鋪、衛浴等設施，但法院認為上開設施多與水產養殖、工具飼料放置、臨時休息、守夜及民間信仰有合理關聯，尚難認為係供居住使用或有不自任耕作之情形。 此外，三七五租約並未要求承租人必須設籍當地或不得另有工作；只要承租人仍以自己為耕作主體、總理其事，即使由親屬協助或僱請他人操作部分農事，也不當然構成不自任耕作或轉租。因此，甲公司拒絕會同辦理續訂登記之抗辯，難認有理由。
+資料來源：臺灣高等法院臺南分院110年度上字第32號民事判決。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H954"/>
+  <dimension ref="A1:H955"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34847,6 +34847,46 @@
         </is>
       </c>
     </row>
+    <row r="955">
+      <c r="A955" t="n">
+        <v>915910</v>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>股票市場與不動產市場之比較</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>2026/07/02</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915910</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:27:53</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>股票市場、不動產市場</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>最近，股票市場受AI發展之影響，非常熱絡；不動產市場受政府打房之影響，非常低迷。這兩個市場形成強烈對比，茲分析這兩個市場性質之差異如下： (一)股票為全國性市場，不動產為地區性市場。 (二)股票具有集中市場，不動產無集中市場。 (三)股票市場之資訊充分流通，不動產市場之資訊未充分流通。 (四)股票市場之流動性高，不動產市場之流動性低。 (五)同一上市公司之每一張股票具有產品同質性，每一筆不動產具有產品異質性。 (六)股票可以細分交易（零股交易），故買賣總價較低。不動產無法細分交易，故買賣總價較高。 (七)股票交易之稅費負擔較輕，不動產交易之稅費負擔較重。 (八)股票市場之交易成本較低，不動產市場之交易成本較高。 (九)股票市場之運行較有效率，不動產市場之運行較無效率。 (十)股票市場不易發生市場失靈，不動產市場容易發生市場失靈。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H955"/>
+  <dimension ref="A1:H956"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34887,6 +34887,65 @@
         </is>
       </c>
     </row>
+    <row r="956">
+      <c r="A956" t="n">
+        <v>915931</v>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>區權會決議不合理，少數區權人只能接受嗎？—從最高法院判決看多數決的界線</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>2026/07/07</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915931</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>2026-07-07 14:04:55</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>區權會決議、少數區權人</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>• 一、案例事實 A大廈為商場與住宅混合之綜合大廈，甲為A大廈商場部分之區分所有權人。甲將其所有之商場樓層出租予他人經營老人養護機構。 嗣後，A大廈召開區分所有權人會議，作成兩項決議：第一，修改住戶規約中有關管理費收費標準之規定，調整特定營業使用類別之管理費；第二，修改地下停車場管理辦法，增列貨車、機車、救護車、特種營業用車及其他車輛不得進入地下停車場之規定。甲認為，上開決議實際上是針對其將商場出租作為老人養護機構使用而來，不僅增加其管理費負擔，也影響其承租人使用地下停車場之便利，屬於藉由多數決形成對少數區分所有權人不利之決議，構成權利濫用，並違反誠信原則、公序良俗。甲遂請求確認該等區分所有權人會議決議無效。 試問：區分所有權人會議以多數決作成之決議，若少數區分所有權人認為內容不合理，是否即得主張該決議無效？
+• 二、相關法條
+1. 公寓大廈管理條例第3條第7款規定，區分所有權人會議，係指區分所有權人為共同事務及涉及權利義務之有關事項，召集全體區分所有權人所舉行之會議。
+2. 公寓大廈管理條例第9條第1項規定，各區分所有權人按其共有之應有部分比例，對建築物之共用部分及其基地有使用收益之權。但另有約定者，從其約定。
+3. 公寓大廈管理條例第10條第2項規定，共用部分、約定共用部分之修繕、管理、維護，由管理負責人或管理委員會為之；其費用由公共基金支付或由區分所有權人按其共有之應有部分比例分擔。但修繕費係因可歸責於區分所有權人或住戶之事由所致者，由該區分所有權人或住戶負擔。其費用若區分所有權人會議或規約另有規定者，從其規定。
+4. 公寓大廈管理條例第23條第1項規定，有關公寓大廈、基地或附屬設施之管理使用及其他住戶間相互關係，除法令另有規定外，得以規約定之。
+5. 公寓大廈管理條例第31條規定，區分所有權人會議之決議，除規約另有規定外，應有區分所有權人三分之二以上及其區分所有權比例合計三分之二以上出席，以出席人數四分之三以上及其區分所有權比例占出席人數區分所有權四分之三以上之同意行之。
+6. 民法第56條第2項規定，總會決議之內容違反法令或章程者，無效。
+7. 民法第72條規定，法律行為有背於公共秩序或善良風俗者，無效。
+8. 民法第148條規定，權利之行使，不得違反公共利益，或以損害他人為主要目的；行使權利、履行義務，應依誠實及信用方法。
+• 三、重要判決觀念
+1. 多數決不是不能審查，但不能只因少數區權人權益受影響，就當然認定決議無效 區分所有權人會議經由多數決作成之決議，與少數區分所有權人之權益發生衝突時，其是否係藉由多數決方式，形成對少數區分所有權人不利之分擔決議或約定，應有充分理由，始不悖離「按應有部分比例分擔」之原則。 且是否係以損害該少數區分所有權人為主要目的，基於公平法理，法院固得加以審查，惟應從大廈全體住戶因該決議之權利行使所能取得之利益，與該少數區分所有權人及國家社會因其權利行使所受之損失，比較衡量以定之。 倘該決議之權利行使，大廈住戶全體所得利益極少，而該少數區分所有權人及國家社會所受之損失甚大者，非不得視為以損害他人為主要目的；不能單憑該決議對少數區分所有權人現擁有之權益有所減損，即認其係藉由多數決方式，形成對少數區分所有權人不利之分擔決議或約定，認以損害他人為主要目的，而屬權利濫用，或違反公序良俗。（最高法院97年度台上字第2347號民事判決）
+2. 管理費調整若有使用類別、公共支出、管理成本等合理基礎，未必構成權利濫用 A大廈為一商場與住宅混合之大廈，其規約按住家、辦公室、停車位及其他依消費場所意外險實施辦法所規定之行業不同，採不同之收費標準，應為法之所許。 而按管理費用是用於人事費、稅捐、維護修繕公寓大廈各項公共設施與日常開支所需及其他基地、共用部分之經常管理費用，故調漲管理費自需有正當且必要之理由。 且由於甲所出租作為老人養護機構使用之空間，其區分所有權合計占全部區分所有權一定比例，所使用者又為出入人員眾多，管理較難之空間，依公寓大廈管理條例第10條第2項之規定，其共有之應有部分比例分擔亦已達相當比例，是以調整後其支出之管理費用，占全部之比例，並未悖離「按應有部分比例分擔」之原則，A大廈管理委員會之決議應有充分理由，甲上開主張不可採。（最高法院97年度台上字第2347號民事判決）
+3. 停車場管理辦法若是基於安全、管理、設備維護目的，也未必當然違法 A大廈之地下停車場為整棟建物之共同部分，車場車位為約定專用，其定有地下停車場管理辦法加以規範。 依該停車場管理辦法規定可見，訂定停車場管理之目的，在於維護汽車昇降機之使用，及為維護社區住戶居住安全，乃限制汽車以外之車輛，如貨車因載重物品容易致昇降機損壞，且出入人員未能明確辨別，機車因進出太過快速機動性強，不易管理，所以為避免管理維護上增加困擾，憑證通行，一證一車，汽車以外之車輛及機車禁止進入。 系爭決議增訂「救護車、特種營運用車及其他之車輛」不得進入等，亦係基於管理不易，出入人員複雜，乃本諸相同之理由禁止進入，用以強化原先規定而已，與甲主張不明車輛或大樓住戶以外之人士所駕駛之車輛不得進入之本旨相同，難謂有增限他種車輛不得進入之管制。（最高法院97年度台上字第2347號民事判決）
+• 四、結論 甲主張區分所有權人會議決議無效，未必有理由。
+1. 區分所有權人會議作成決議後，少數區分所有權人若認為內容不合理，並非完全沒有救濟空間。若決議內容違反法令、規約、公序良俗，或係以損害特定少數區分所有權人為主要目的，仍可能依民法第56條第2項、第72條、第148條等規定，主張該決議無效。
+2. 但是，少數區分所有權人不能只因為決議結果對自己不利，就當然認為該決議是「多數暴力」或權利濫用。法院會進一步審查：該決議是否具有管理上之正當目的、是否有必要性、是否符合共用部分管理維護之需要、是否有充分理由偏離單純按應有部分比例分擔之原則，以及大廈全體住戶所得利益與少數區分所有權人所受損失之間，是否明顯失衡。
+3. 本案中，A大廈為住商混合大樓，區分所有權人會議依使用類別調整管理費，若係基於公共設施維修、日常管理、人員出入增加、管理成本提高等理由，且調整後負擔比例仍未明顯悖離應有部分比例分擔原則，即難認為當然構成權利濫用。至於地下停車場管理辦法限制特定車輛進入，若係基於汽車昇降機維護、社區安全、出入人員辨識及管理困難等考量，也未必當然違法。
+4. 因此，區權會決議雖然尊重多數決，但多數決仍有界線；少數區權人若要主張決議無效，重點不在於單純表示「我覺得不合理」，而是必須具體指出該決議欠缺充分理由、負擔明顯失衡，或係以損害特定少數區權人為主要目的。換言之，社區自治不是多數說了就算，但少數要翻轉決議，也必須提出足以證明決議違法或權利濫用的具體理由。
+資料來源： 最高法院97年度台上字第2347號民事判決。 最高法院92年度台上字第2517號民事判決。 公寓大廈管理條例。 民法第56條、第72條、第148條。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H956"/>
+  <dimension ref="A1:H957"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34946,6 +34946,51 @@
         </is>
       </c>
     </row>
+    <row r="957">
+      <c r="A957" t="n">
+        <v>915945</v>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>類空地稅及類照價收買</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>2026/07/09</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915945</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:28:13</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>空地稅、照價收買、加徵地價稅、強制收買</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>平均地權條例對於「空地」，得採空地稅或照價收買加以制裁。其相關規定如下：
+• (一) 空地：指已完成道路、排水及電力設施，於有自來水地區並已完成自來水系統，而仍未依法建築使用；或雖建築使用，而其建築改良物價値不及所占基地申報地價百分之十，且經直轄市或縣（市）政府認定應予增建、改建或重建之私有及公有非公用建築用地（平§3⑦）。
+• (二) 空地稅及照價收買：直轄市或縣（市）政府對於私有空地，得視建設發展情形，分別劃定區域，限期建築、增建、改建或重建；逾期未建築、增建、改建或重建者，按該宗土地應納地價稅基本稅額加徵二倍至五倍之空地稅或照價收買。經依前項規定限期建築、增建、改建或重建之土地，其新建之改良物價值不及所占基地申報地價百分之五十者，直轄市或縣（市）政府不予核發建築執照（平§26）。
+新市鎮開發條例為督促區內土地限期使用，亦有類似規定。然，因不符合平均地權條例之空地定義，故不稱為「空地稅及照價收買」，而稱為「加徵地價稅及強制收買」。亦即：
+主管機關為促進新市鎮之發展，得依新市鎮特定區計畫之實施進度，限期建築使用。逾期未建築使用者，按該宗土地應納地價稅基本稅額之五倍至十倍加徵地價稅；經加徵地價稅滿三年，仍未建築使用者，按該宗土地應納地價稅基本稅額之十倍至二十倍加徵地價稅或由主管機關照當期公告土地現值強制收買。前項限期建築之土地，其限期建築之期限，不因移轉他人而受影響，對於不可歸責於土地所有權人之事由而遲誤之期間，應予扣除（新§18ⅠⅡ）。
+【註】 平：平均地權條例。 新：新市鎮開發條例。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H957"/>
+  <dimension ref="A1:H958"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34991,6 +34991,50 @@
         </is>
       </c>
     </row>
+    <row r="958">
+      <c r="A958" t="n">
+        <v>915972</v>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>外牆漏水，到底是住戶自己修，還是管委會要修？</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>2026/07/14</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915972</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>2026-07-14 13:04:11</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>公寓大廈管理條例</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>• 一、案例事實 A大廈為已成立管理委員會之公寓大廈。甲為A大廈某戶區分所有權人，近年發現其室內靠外牆處出現滲漏水、壁癌及油漆剝落情形。經初步檢查，疑似係因大廈外牆磁磚老化、防水層破損或外牆構造年久失修所造成。 甲遂請求A大廈管理委員會安排外牆防水及修繕，並由公共基金或全體區分所有權人依比例分擔費用。惟管理委員會表示，漏水位置對應甲住家外側，應由甲自行負責；部分住戶也認為「外牆就在你家外面」，不應由全體住戶共同負擔。試問：公寓大廈外牆漏水時，應由個別住戶自行修繕，還是由管理委員會負責修繕、管理、維護？
+• 二、相關法條(一)公寓大廈管理條例第3條第4款規定，共用部分，指公寓大廈專有部分以外之其他部分及不屬專有之附屬建築物，而供共同使用者。 (二)公寓大廈管理條例第7條第3款規定，公寓大廈之基礎、主要樑柱、承重牆壁、樓地板及屋頂之構造，屬於不得為約定專用部分之共用部分。 (三)公寓大廈管理條例第8條第1項規定，公寓大廈周圍上下、外牆面、樓頂平臺及不屬專有部分之防空避難設備，其變更構造、顏色、設置廣告物、鐵鋁窗或其他類似行為，除應依法令規定辦理外，並應受規約或區分所有權人會議決議之限制。 (四)公寓大廈管理條例第10條第1項規定，專有部分、約定專用部分之修繕、管理、維護，由各該區分所有權人或約定專用部分之使用人為之，並負擔其費用。 (五)公寓大廈管理條例第10條第2項規定，共用部分、約定共用部分之修繕、管理、維護，由管理負責人或管理委員會為之；其費用由公共基金支付或由區分所有權人按其共有之應有部分比例分擔。但修繕費係因可歸責於區分所有權人或住戶之事由所致者，由該區分所有權人或住戶負擔。 (六)公寓大廈管理條例第36條第2款規定，管理委員會之職務包括共有及共用部分之清潔、維護、修繕及一般改良。 (七)公寓大廈管理條例第56條第3項規定，辦理公寓大廈建物所有權第一次登記，獨立建築物所有權之牆壁以牆之外緣為界；建築物共用之牆壁，以牆壁之中心為界；附屬建物以其外緣為界辦理登記；有隔牆之共用牆壁，以牆壁之中心為界，無隔牆設置者，以使用執照竣工平面圖區分範圍為界，其面積應包括四周牆壁之厚度。
+• 三、重要判決觀念(一)外牆涉及大樓整體外觀及防水功能，不能簡單認定為個別住戶專有部分 本件系爭外牆係屬大廈之外牆面，與大樓外觀息息相關，而本件外牆之滲漏水修補係因外牆磁磚老化，衡情必涉及外牆磁磚之汰換與防漏處理等情，亦經新北市建築師公會於鑑定報告書列舉明確。如認此重要部位屬區分所有權人之專有部分未經其他共有人同意而得任意處置，無異將影響公寓大廈之整體外觀，亦有違公寓大廈管理條例第7條第3款、第8條第1項制定之原意所在。（臺灣高等法院104年度上易字第605號民事判決）(二)在區分所有權人內部關係上，建築物外牆仍應認為由區分所有權人共有 公寓大廈管理條例第56條第3項規定，辦理公寓大廈建物所有權第一次登記，獨立建築物所有權之牆壁以牆之外緣為界；建築物共用之牆壁，以牆壁之中心為界；附屬建物以其外緣為界辦理登記；有隔牆之共用牆壁，以牆壁之中心為界，無隔牆設置者，以使用執照竣工平面圖區分範圍為界，其面積應包括四周牆壁之厚度。蓋區分所有權人之單獨所有權，如以區分所有之空間為範圍，違反物權須以物為標的之原則，故以上開規定規範建築物登記所有權之範圍，俾維持區分所有建築物為物的性質，但解釋上應認為此屬於區分所有權之對外關係（例如買賣、課稅等），於區分所有權人相互間之內部關係，仍應認為建築物之外牆為區分所有權人所共有。（臺灣高等法院104年度上易字第605號民事判決）(三)共用牆體、防水層等共用部分漏水，原則上由管理委員會負責修繕 按共用部分指公寓大廈專有部分以外之其他部分及不屬專有之附屬建築物，而供共同使用者；公寓大廈共用部分不得獨立使用供做專有部分。公寓大廈基礎、主要樑柱、承重牆壁、樓地板及屋頂之構造，並不得為約定專用部分。共用部分、約定共用部分之修繕、管理、維護，由管理負責人或管理委員會為之。其費用由公共基金支付或由區分所有權人按其共有之應有部分比例分擔之。（臺灣臺北地方法院113年度訴字第4056號民事判決）(四)若漏水原因來自共用部分，管委會即負有維護、修繕責任 是連續壁、樓板及排水溝渠均為系爭公寓大廈之共用部分而為區分所有權人所共有，揆諸前開規定，公寓大廈共用部分之修繕、管理、維護本應由管理委員會負責，被告既為系爭公寓大廈管理委員會，對於系爭地下室天井區域自有維護、修繕之責，其修繕費用由公共基金支付。（臺灣臺北地方法院113年度訴字第4056號民事判決）
+• 四、結論 (一)甲請求A大廈管理委員會辦理外牆漏水修繕，原則上有理由。 (二)公寓大廈之外牆，雖然在位置上可能正好對應到某一戶的室內牆面，但外牆涉及大樓整體外觀、建築物結構、防水功能及全體住戶共同利益，並非當然屬於個別住戶可以單獨處分或自行負責的專有部分。司法實務見解亦指出，在區分所有權人相互間之內部關係上，建築物外牆仍應認為由區分所有權人共有。 (三)若漏水原因來自外牆磁磚老化、防水層破損、共用牆體或其他共用部分，原則上應依公寓大廈管理條例第10條第2項，由管理委員會負責修繕、管理、維護，修繕費用則由公共基金支付，或由區分所有權人按共有應有部分比例分擔。 (四)不過，若能證明漏水是因特定住戶擅自施工、破壞外牆、防水層、結構體，或違規設置鐵窗、冷氣、管線、招牌等可歸責行為所造成，仍可能依公寓大廈管理條例第10條第2項但書，由該特定住戶負擔修繕費用。
+資料來源： 臺灣高等法院104年度上易字第605號民事判決。 臺灣臺北地方法院113年度訴字第4056號民事判決。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H958"/>
+  <dimension ref="A1:H959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35035,6 +35035,55 @@
         </is>
       </c>
     </row>
+    <row r="959">
+      <c r="A959" t="n">
+        <v>915983</v>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>營建成本上漲，是否會造成房價上漲？</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>2026/07/16</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=915983</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:16:48</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>營建成本上漲、房價上漲</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t xml:space="preserve">建材、工資等營建成本上漲，社會普遍認為房價會跟著上漲，但筆者不以為然。茲分短期分析及長期分析說明如下：
+• (一) 短期分析：房價是房屋需求與房屋供給所決定，而非生產成本所決定。如圖所示，D代表房屋需求曲線，S代表房屋供給曲線。D與S之交點，決定房價P0及房屋交易量Q0。基上，就短期分析而言，營建成本上漲，不會造成房價上漲。
+[圖片1]
+• (二) 長期分析：營建成本係房屋之生產成本之一。因此生產成本增加，房價隨之上漲。如圖所示，營建成本上漲，S左上移至S′，則房價由P0上漲為P1。基上，就長期分析而言，營建成本上漲，會造成房價上漲。
+• (三) 結論：
+1. 就短期分析而言，營建成本上漲，不會造成房價上漲；就長期分析而言，營建成本上漲，會造成房價上漲。然，所謂經濟分析，一般指短期分析或短期現象，而非指長期分析或長期現象。
+2. 營建成本上漲，短期不會造成房價上漲。此時，建設公司無利可圖或甚至虧損，因此建設公司遂減少推出新案，導致市場上之房屋供給減少。經過數年後，房價才會因房屋供給減少而上漲。前揭所稱「數年後」，即長期分析。
+## 文章圖片
+![圖片1](./images/915983_a3034e6b.png)
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H959"/>
+  <dimension ref="A1:H960"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35084,6 +35084,56 @@
         </is>
       </c>
     </row>
+    <row r="960">
+      <c r="A960" t="n">
+        <v>916010</v>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>違規住戶一定能用惡鄰條款趕走嗎？</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>2026/07/21</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916010</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>2026-07-21 13:13:37</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>惡鄰條款、公寓大廈管理條例</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>• 一、案例事實 甲社區為已成立管理委員會之公寓大廈，乙為甲社區A屋之住戶。乙曾自行增建、變更A屋外觀，並占用甲社區共有土地，因而與甲社區管理委員會及其他住戶發生爭議。 甲社區管理委員會認為，乙上開行為已違反法令及社區規約，且乙與社區住戶間長期相處不睦，彼此之間已有多件民事、刑事訴訟，顯示雙方已難以維持共同居住關係。因此，甲社區管理委員會依公寓大廈管理條例第22條第1項第3款規定，請求法院判命乙自A屋強制遷離。 試問：住戶違反法令或規約時，是否只要社區住戶認為難以相處，管理委員會即可依公寓大廈管理條例第22條第1項第3款，請求法院強制其遷離？
+• 二、相關法條
+1. 公寓大廈管理條例第5條規定，區分所有權人對專有部分之利用，不得有妨害建築物之正常使用及違反區分所有權人共同利益之行為。
+2. 公寓大廈管理條例第6條第1項第1款規定，住戶於維護、修繕專有部分、約定專用部分或行使其權利時，不得妨害其他住戶之安寧、安全及衛生。
+3. 公寓大廈管理條例第8條第1項規定，公寓大廈周圍上下、外牆面、樓頂平臺及不屬專有部分之防空避難設備，其變更構造、顏色、設置廣告物、鐵鋁窗或其他類似行為，除應依法令規定辦理外，並應受規約或區分所有權人會議決議之限制。
+4. 公寓大廈管理條例第9條第2項規定，住戶對共用部分之使用應依其設置目的及通常使用方法為之。
+5. 公寓大廈管理條例第22條第1項第3款規定，住戶有「其他違反法令或規約情節重大者」，由管理負責人或管理委員會促請其改善，於3個月內仍未改善者，管理負責人或管理委員會得依區分所有權人會議之決議，訴請法院強制其遷離。
+6. 公寓大廈管理條例第22條第2項規定，前項住戶如為區分所有權人時，管理負責人或管理委員會得依區分所有權人會議之決議，訴請法院命區分所有權人出讓其區分所有權及其基地所有權應有部分。
+• 三、重要判決觀念(一)第22條第1項第3款所稱「情節重大」，須達嚴重違反義務、無法維持共同群居關係之程度 公寓大廈管理條例第22條第1項第3款規定所稱「違反法令或規約情節重大，得訴請強制遷離」之情形，應以該住戶違反法令或規約而嚴重違反對他區分所有人之義務，致無法維持共同群居關係，經管委會促請其改善，於3個月內仍未改善，經區分所有權人會議決議訴請法院強制遷離始足當之。 (二)強制遷離須審查比例原則，不能逾越適當性、必要性與限制妥當性 另外，應考量強制遷離有無逾越遷離之適當性、必要性、限制妥當性，俾符合比例原則。 (三)即使有增建、變更外觀及占用共有土地，仍不當然構成情節重大 乙雖有自行增建及變更A屋外觀並占有甲社區共有土地，而違反法令及社區規約之情事，惟情節尚非重大，且乙已經拆除系爭增建物，將共有土地返還予區分所有權人全體。 (四)住戶間相處不睦、相互興訟，不當然可作為強制遷離理由 另乙與甲社區住戶間，雖因相處不睦而有相互興訟之情事，然此為乙與甲社區住戶權利之正當行使。 (五)不能只因住戶提起多件民、刑事訴訟、彼此關係不佳，就限制其居住自由 如僅以乙對於甲社區住戶提出多件民、刑事訴訟，彼此關係不洽，即認有強制遷離乙，而限制乙居住自由之情事，尚難認符合比例原則。
+• 四、結論 甲社區管理委員會依公寓大廈管理條例第22條第1項第3款，請求乙自A屋強制遷離，無理由。 本案可以看出，公寓大廈管理條例第22條第1項第3款所謂「其他違反法令或規約情節重大者」，並不是只要住戶有違規行為，或社區住戶認為彼此難以相處，即可啟動強制遷離。法院仍會審查該違規行為是否已嚴重違反對其他區分所有權人之義務，是否已達無法維持共同群居關係之程度，以及強制遷離是否符合比例原則。 惡鄰條款是公寓大廈共同生活秩序中的最後手段，不是一般住戶糾紛、鄰里不和或輕微違規的快速驅離工具。若違規行為已改善，或尚未嚴重到無法維持共同居住關係，法院未必會准許強制遷離。管理委員會若要依第22條第1項第3款提起訴訟，必須具體證明違規內容、違規程度、未改善狀況，以及強制遷離確有必要。
+資料來源：臺灣高等法院108年度上易字第1330號民事判決。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H960"/>
+  <dimension ref="A1:H961"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35134,6 +35134,47 @@
         </is>
       </c>
     </row>
+    <row r="961">
+      <c r="A961" t="n">
+        <v>916016</v>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>土地撥用與土地徵收之比較</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916016</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>2026-07-23 13:22:14</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>土地撥用、土地徵收</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>今年，公務人員高考「土地法規（含土地登記）」考試科目，第一題是「經濟部水利署如何取得縣所有之閒置國小用地」。部分考生以「土地徵收」作答，其實應以「土地撥用」作答。理由是「土地徵收」只能徵收私有土地，不得徵收公有土地。相對地，政府機關取得公有土地唯有靠「土地撥用」。茲分析土地徵收與土地撥用之不同如下表。
+• T. ABLE_PLACEHOLDER_1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H961"/>
+  <dimension ref="A1:H962"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35175,6 +35175,60 @@
         </is>
       </c>
     </row>
+    <row r="962">
+      <c r="A962" t="n">
+        <v>916019</v>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>農地房地合一稅免納要件與農用證明之核發</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>2026/07/28</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916019</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:32:39</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>房地合一、農用證明、農地免稅</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>各位學員可先參考最近地政界滿多人討論的案件： 水泥地覆土逃稅！溪州博士課長放水判5年半‪@newsebc‬ - YouTube‬ 臺灣高等法院 臺中分院 114 年度上訴字第 788 號刑事判決
+我們這邊就不討論圖利罪，主要著重在考試範圍，也就是有關房地合一稅之相關規定進行說明。尤其，這次地政士土地稅法規就考到這邊，如果有背到我們上課所說的「自(住)、農(用)、徵(收)、(公)保」就沒問題了：
+（一）原則：房地交易所得應課徵所得稅 《所得稅法》第4條之4規定，個人或營利事業交易2016年1月1日以後取得的房屋、房屋及其坐落基地，或依法得核發建造執照的土地，原則上應依房地合一制度課徵所得稅。 同條亦規定，依《農業發展條例》申請興建的農舍，不列入房地合一制度所稱的「房屋」範圍；但是農舍坐落的土地，仍須另外判斷是否屬房地合一課稅土地，以及是否符合農地免稅規定。
+（二）例外：農用且不課徵土地增值稅之農地免稅 《所得稅法》第4條之5第1項第2款規定，符合《農業發展條例》第37條及第38條之1，可以申請不課徵土地增值稅的土地，其交易免納所得稅。 其中，《農業發展條例》第37條第1項則規定，必須同時具備兩個主要條件：
+1. 土地是「作農業使用之農業用地」。
+2. 移轉給自然人。
+符合者，才得申請不課徵土地增值稅。 因此，房地合一稅免稅並不是看到土地登記或使用分區屬於農業用地就自動適用，而是必須進一步確認土地在移轉時確實作農業使用，且需不課徵土地增值稅。
+（三）農用證明之核發原則 農業用地作農業使用證明（實務一般簡稱農用證明）的作用，是由農業主管機關透過書面資料及現場勘查，確認土地是否真正作農業使用。依本案所適用的《農業用地作農業使用認定及核發證明辦法》第5條，具有下列情況，即不得認定為作農業使用：
+1. 農業設施或農舍超過核准面積；
+2. 未依核定用途使用；
+3. 阻斷排灌水系統；
+4. 現場有與農業經營無關或妨礙耕作的障礙物；
+5. 有砂石、廢棄物、柏油或水泥等使用情形。
+本案水泥鋪面未拆除，只以泥土覆蓋，正屬於不得認定為農業使用的情形。 因此，從這個判決來看，由於農用證明不只影響農地管制，也同時影響稅捐負擔義務，以致核發農證的公務員負有高度的實質審查義務。
+（四）本案免除的是房地合一所得稅，不只是土地增值稅 這是本案最值得注意的地方。一般人申請農用證明，常只想到「農地移轉不課土地增值稅」；但在房地合一制度下，只要土地符合《農業發展條例》第37條得不課徵土地增值稅的資格，也會連動適用《所得稅法》第4條之5，使該土地交易免納房地合一所得稅。因此，農用證明實際上具有雙重稅捐效果。本案地主透過違法農證取得的具體利益，就是免繳130萬元左右的房地合一所得稅。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H962"/>
+  <dimension ref="A1:H963"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35229,6 +35229,61 @@
         </is>
       </c>
     </row>
+    <row r="963">
+      <c r="A963" t="n">
+        <v>916034</v>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>簡介「可負擔住宅」</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916034</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:24:57</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>可負擔住宅</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>桃園市政府釋出捷運站周邊容積獎勵之建商回捐住宅，推出「可負擔住宅」。
+• (一) 特色：
+1. 申請條件：(1)設籍桃園市1年以上。 (2)申請人及其配偶為25歲以上，未滿45歲，育有或懷有未成年子女。 (3)申請人及其配偶每人每月平均收入應高於桃園市最低生活標準之2.5倍至3.5倍。
+2. 產權處理：產權信託於桃園住都中心（行政法人）名下，民眾只取得房屋使用權。
+3. 貸款條件：由政府擔保，比照首購，協助承購人向銀行辦理優惠貸款。
+4. 轉售限制：只能透過市政府平台轉售，轉售價格不得超過原買價。
+• (二) 優點：
+1. 提供婚育家庭，長期且穩定之居住空間，解決現行「社會住宅」無法長期居住之缺點。
+2. 信託管理機制，全面去商品化，解決過去「合宜住宅」淪為套利商品之缺點。
+3. 協助婚育家庭取得住宅，提供可負擔價格及可負擔貸款，鼓勵結婚生子。
+4. 可負擔住宅只售不租，銜接只租不售之社會住宅與自由市場之「自有住宅」的過渡選項。
+• (三) 缺點：
+1. 可負擔住宅相當於房屋買賣，屬於一次性消費，缺乏循環機制，無法讓更多民眾受惠。
+2. 可負擔住宅之量體，隨著政府整體開發之脚步，藉助建商增額容積之回饋，來源受限。
+3. 可負擔住宅是住宅市場之一種創新制度。執行過程，恐會產生一些意想不到的問題，有待克服。
+4. 可負擔住宅推行能否成功，取決於政府、銀行及購屋者三方面是否認同，缺一不可。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H963"/>
+  <dimension ref="A1:H964"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35284,6 +35284,52 @@
         </is>
       </c>
     </row>
+    <row r="964">
+      <c r="A964" t="n">
+        <v>916057</v>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>基地部分設定地上權後出賣之優先購買權範圍</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916057</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:47:04</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>地上權、優先購買權</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>土地所有人僅就一筆土地之一部分設定地上權，地上權人並於其上建屋；嗣土所有人負債，債權人聲請拍賣整筆土地。拍定後，地上權人究竟只能優先承買地上權範圍內的基地，還是得承買整筆土地？問題看似只是面積計算，實際上同時牽涉土地能否分割、剩餘土地能否單獨使用，以及土地法第104條所稱「同樣條件」是否包括整體買賣標的。
+• 一、早期函釋：原則限於地上權範圍 司法院（72）廳民二字第0109號函所設案例，正是300坪土地中僅100坪設定地上權並建屋，嗣整筆土地遭拍賣。研究意見認為，土地法第104條旨在使土地利用權與所有權歸於同一主體，故除基地有不能分割情形外，地上權人只能就100坪地上權範圍行使優先承買權。惟該函雖保留「不能分割」的例外，並未進一步說明此時應承買全部土地，或僅取得一定應有部分（陳立夫，2024：85）。
+• 二、執行實務：不能分割時如何處理，見解並不一致 司法院94年第4期民事業務研究會認為，執行法院應先測量優先承買範圍，並查明該部分能否分割及單獨使用；如可分割，得分標拍賣；如不能分割，或分割後形成畸零地、不能單獨使用，優先承買權人應就全部土地合併主張，不得只買房屋坐落部分（司法院，2005：80-82）。 然而，臺灣高等法院暨所屬法院95年法律座談會民執類提案第17號並未正式採取此說。其審查意見反而主張：可分割時辦理分割；不可分割時，由地上權人按其權利範圍與拍定人成立共有關係。最終問題（一）由提案機關同意保留，並無統一結論（臺灣高等法院，2006：民執類提案第17號）。
+• 三、最高法院近年見解：部分承買為原則，不能分割為例外 最高法院111年度台上字第2832號判決認為，承租人僅承租基地一部分時，除土地不能分割外，優先承買權原則上僅限於承租範圍；部分承買時，「同樣條件」則可解為實質相同，並綜合價金、付款方式、期限、點交及其他條件，依個案與誠信原則判斷。陳立夫教授指出，此一標準亦適用於部分設定地上權或典權的情形（陳立夫，2024：85-86）。
+• 四、學者看法：同樣條件之適用有疑問 陳教授對上述見解提出重要質疑：出賣人與第三人既以整筆土地作為買賣標的，若優先購買權人僅買其中一部分，買賣標的已被改變，所成立的契約終究不同於原契約，是否仍符合「同樣條件」，並非沒有疑問。分割後土地的面積、形狀、臨路及利用條件也可能改變，價金未必能按面積機械拆算；第三人是否仍願購買剩餘土地，出賣人是否因此承受減價損失，也須一併考量（陳立夫，2024：85-87）。 陳教授並援引最高法院106年度台上字第1263號判決，指出「同樣條件」包括買賣標的；原契約既以整筆土地為標的，基地承租人即可能依相同標的優先購買全部，不以房屋坐落範圍為限。不過，陳教授的論述較接近對「部分承買說」的反思，尚不宜概括成只要整筆出售，地上權人一律有權承買全部（陳立夫，2024：86）。
+• 五、本專欄看法 此類案件不宜只以地籍上能否分割作為唯一標準。法院應依序查明：地上權登記及建物實際使用範圍、分割是否合法且是否仍能單獨使用，以及原交易的價金與附隨義務能否合理分離。若部分承買將使剩餘土地失去通常利用價值，或根本改變第三人所接受的交易組合，要求地上權人承買全部，較能維持「同樣條件」；反之，如土地及契約條件均可明確分離，將優先承買範圍限於地上權及建物使用所必要部分，則較符合土地法第104條促使基地與房屋權利合一、又避免先買權過度擴張的目的。
+參考文獻 陳立夫（2024），〈土地法第104條規定之基地優先購買權〉，《月旦實務選評》，第4卷第7期，頁82-90。 黃健彰（2024），〈基地承租人的先買權——以評析最高法院111年度台上字第2832號民事判決為主（一）〉，《新學林法學》，第6期，頁93-112。 司法院（1983），（72）廳民二字第0109號函。 司法院（2005），94年第4期民事業務研究會——強制執行專題第21則，《民事法律專題研究（二十）》，頁80-82。 臺灣高等法院（2006），95年法律座談會民執類提案第17號。 最高法院（2017），106年度台上字第1263號民事判決。 最高法院（2023），111年度台上字第2832號民事判決。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H964"/>
+  <dimension ref="A1:H965"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35330,6 +35330,50 @@
         </is>
       </c>
     </row>
+    <row r="965">
+      <c r="A965" t="n">
+        <v>916069</v>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>不動產自益信託與他益信託之稅負比較</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916069</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>2026-08-06 13:31:48</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>不動產自益信託、不動產他益信託</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>不動產信託分為自益信託與他益信託二種。兩者之稅負比較如下：
+• (一) 持有稅：不論自益信託或他益信託，地價稅及房屋稅之納稅義務人皆為受託人（即名義所有權人）。
+• (二) 移轉稅：
+1. 自益信託：不動產自益信託之移轉，分為信託行為成立時，辦理「信託登記」；及日後信託關係消滅時，辦理「塗銷信託登記」。前揭二個時點，皆不計徵贈與稅、不課徵土地增值稅及契稅。
+2. 他益信託：他益信託相當於贈與，按贈與稅課徵規定，對贈與人課徵贈與稅，對受贈人課徵土地增值稅及契稅。同理，不動產他益信託之移轉，分為信託行為成立時，辦理「信託登記」；及日後信託關係消滅時，辦理「信託歸屬登記」。前揭二個時點之課徵規定如下： (1)信託登記：向委託人（即贈與人）課徵贈與稅，但此時不課徵土地增值稅及契稅。 (2)信託歸屬登記：向歸屬權利人（即受贈人）課徵土地增值稅及契稅，但此時不課徵贈與稅。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H965"/>
+  <dimension ref="A1:H966"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35374,6 +35374,72 @@
         </is>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" t="n">
+        <v>916086</v>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>土地浮覆後，原所有權是否當然回復？—從臺灣高等法院114年度重上更一字第121號判決談土地法第12條</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916086</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>2026-08-11 12:42:15</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>土地浮覆、土地法第12條、請求國家塗銷登記、憲判20號</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[圖片1] 圖片來源：本專欄依據判決整理重點內容，並去識別化後，請ChatGPT生成圖片。
+• 一、案例事實甲為日據時期A番地之所有權人。A番地於民國21年4月12日因成為河川而削除登記。甲嗣於民國35年3月18日死亡，丙為甲之繼承人之一。
+其後，A番地因堤防施築後部分浮覆。臺北市政府於民國79年3月6日公告「防潮堤線加高工程堤線樁位」確定，地政機關並經清理測量，編具浮覆地面積計算清冊，記載A番地「流失前」與「浮覆後」之面積，並核對原圖簿資料。
+嗣後，地政機關於民國91年9月間辦理公布及公告程序，並於公告期滿後辦理土地標示部登記；A番地浮覆部分於民國91年10月8日編為B土地。B土地後於民國96年12月17日第一次登記為國有。
+丙主張，A番地因部分浮覆而編為B土地後，依土地法第12條第2項規定，原所有權人甲之所有權應當然回復；B土地應屬甲全體繼承人公同共有。B土地登記為國有，已妨害甲全體繼承人之所有權，故請求確認B土地為甲全體繼承人公同共有，並請求丁機關塗銷B土地之國有登記。
+丁機關則抗辯：B土地雖經公告浮覆，但尚未劃出河川區域，仍屬水道，與土地法第12條第2項所稱回復原狀要件不合；又B土地自民國79年3月6日浮覆後，始終供作防汛堤防使用，丁機關已因時效取得所有權，且丙於民國111年9月30日提起本件訴訟時，其回復請求權亦已罹於時效。
+試問：A番地因成為河川而削除登記，嗣後部分浮覆，經地政機關於民國91年編為B土地，並於民國96年第一次登記為國有，原所有權人甲之繼承人能否依土地法第12條第2項主張所有權當然回復，並請求確認B土地為甲全體繼承人公同共有及塗銷國有登記？
+• 二、相關法條 (一)土地法第12條第1項規定，私有土地，因天然變遷成為湖澤或可通運之水道時，其所有權視為消滅。 (二)土地法第12條第2項規定，前項土地，回復原狀時，經原所有權人證明為其原有者，仍回復其所有權。 (三)民法第767條第1項中段規定，所有人對於妨害其所有權者，得請求除去之。 (四)民法第828條第2項準用第821條規定，各公同共有人對於第三人，得就公同共有物之全部為本於所有權之請求。
+• 三、重要判決觀念(一)土地法第12條所稱所有權視為消滅，並非土地物理上滅失，所有權亦僅擬制消滅 土地法第12條第1項所謂私有土地因成為公共需要之湖澤或可通運之水道，其所有權視為消滅，並非土地物理上之滅失，所有權亦僅擬制消滅，當該土地回復原狀時，依同條第2項規定，原土地所有人之所有權當然回復，無待申請地政機關核准，亦不以其經公告劃出河川區域以外，及完成所有權第1次登記為要件。
+• (二) 私人土地經劃入河川區域內，僅是私權行使得受限制，對所有權歸屬並無影響 又私人所有土地經劃入河川區域內，僅其私權行使得基於公共利益以法律為必要之限制，就其所有權之歸屬並無影響。
+• (三) A番地已物理上浮現而部分浮覆，客觀上可具體計算面積、範圍，顯已回復原狀 B土地因堤防施築後浮覆，經臺北市政府依水利法第82條規定，於79年3月6日公告『防潮堤線加高工程堤線樁位』確定，並經清理測量編具『浮覆地面積計算清冊』記載『流失前』、『浮覆後』之面積，核對原圖簿資料無誤，於91年9月間辦理公布及公告程序，並於公告期滿辦理土地標示部之登記。 可見A番地已物理上浮現而部分浮覆，客觀上可具體計算面積、範圍與原地籍圖簿進行比對，並辦理土地標示部登記，顯已回復原狀，依上開說明，原所有權人甲之所有權當然回復，並無待地政機關核准，亦不以公告劃出河川區域以外為要件。
+• (四) 日治時期為人民所有，嗣登記為國有之土地，人民請求國家塗銷登記，無民法消滅時效規定之適用 日治時期為人民所有，嗣因逾土地總登記期限，未登記為人民所有，致登記為國有且持續至今之土地，在人民基於該土地所有人地位，請求國家塗銷登記時，無民法消滅時效規定之適用。因此，甲就B土地之所有權因浮覆而當然回復，並不因逾總登記期限而受影響。 B土地登記為國有，已構成對甲全體繼承人所有權之妨害，則丙先位訴請確認其與甲之其他繼承人因繼承而公同共有B土地，及依民法第767條第1項中段、第828條第2項準用第821條規定，請求丁機關塗銷系爭登記，為有理由，並無民法消滅時效規定之適用。
+• 四、本專欄說明 本件丙請求確認B土地為其與甲之其他繼承人公同共有，並請求丁機關塗銷B土地之國有登記，為有理由。
+本判決認為，土地法第12條第1項所稱私有土地因成為公共需要之湖澤或可通運之水道，其所有權視為消滅，並非土地物理上滅失，所有權亦僅為擬制消滅。當土地回復原狀時，依土地法第12條第2項規定，原土地所有人之所有權當然回復，無待申請地政機關核准，亦不以經公告劃出河川區域以外為要件。
+因此，B土地於民國96年12月17日第一次登記為國有，已構成對甲全體繼承人所有權之妨害。丙依民法第767條第1項中段、第828條第2項準用第821條規定，請求丁機關塗銷B土地之國有登記，為有理由，並無民法消滅時效規定之適用。
+至於丁機關所為消滅時效抗辯，本判決引用憲法法庭112年憲判字第20號判決主文及最高法院113年度台上字第969號判決要旨，認為日治時期為人民所有，嗣因逾土地總登記期限未登記為人民所有，致登記為國有且持續至今之土地，在人民基於該土地所有人地位請求國家塗銷登記時，無民法消滅時效規定之適用。
+值得注意的是，法務部法律字第11403512980號函，已就「浮覆地所有權回復請求權之消滅時效爭議」整理近期學說及司法實務發展：
+該函先指出，最高法院110年度台上大字第1153號大法庭裁定曾認為，日據時期已登記之土地，因成為河道、水道經塗銷登記，臺灣光復後土地浮覆，原所有人如未依我國法令辦理土地總登記，該土地仍屬未登記之不動產，原所有人依民法第767條第1項規定行使物上請求權時，有民法消滅時效規定之適用。
+惟憲法法庭112年憲判字第20號判決作成後，近期學說及司法實務見解就浮覆地所有權回復請求權之消滅時效爭議，多認為應依該憲法判決意旨處理。法務部函並整理學說見解指出，河川土地私有權之返還爭議，與憲判20號具有同質性，所不同者僅土地曾因自然變遷成為公共需用之湖澤或可通運之水道，然此項差異並不構成對浮覆地案件進行差別待遇之理由，而應與憲判20號作相同處理。
+法務部函另整理司法實務見解指出，近年司法實務見解多援引憲判20號意旨，針對國家基於公權力主體地位行使統治高權，將人民私有未辦理登記之土地逕行登記為國有之情形，採取「國家不得為時效完成抗辯」之基礎，就人民基於浮覆之私有土地所有人地位，請求國家塗銷登記時，無民法消滅時效規定之適用。
+因此，本件判決引用憲判20號處理消滅時效問題，是與近年浮覆地案件之實務趨勢相符。不過仍應注意，憲判20號原因案件與本案浮覆地之事實結構並非完全相同（可參憲判20號不同意見書及相關學者文章）；本判決係先依土地法第12條判斷B土地已回復原狀、原所有權人甲之所有權當然回復，再於丁機關抗辯消滅時效時，引用憲判20號及相關最高法院見解，認為人民基於土地所有人地位請求國家塗銷國有登記，無民法消滅時效規定之適用。
+資料來源：
+1. 臺灣高等法院114年度重上更一字第121號民事判決。
+2. 法務部法律字第11403512980號函。
+## 文章圖片
+![圖片1](./images/916086_862dcdd3.png)
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H966"/>
+  <dimension ref="A1:H967"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35440,6 +35440,65 @@
         </is>
       </c>
     </row>
+    <row r="967">
+      <c r="A967" t="n">
+        <v>916089</v>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>簡介「青安3.0方案」</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916089</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:42:54</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>青安3.0</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>政府於2010年12月推出「青年安心成家購屋優惠貸款」（青安1.0方案），嗣於2023年8月1日～2026年7月31日推出「青安2.0方案」，再於2026年8月1日～2029年7月31日推出「青安3.0方案」。
+• (一) 目的：
+1. 協助無自有住宅之青年購屋貸款。
+2. 將有限資源落實於真正需要協助之首購及自住族群。
+• (二) 特色：
+1. 增加年齡限制（排除高齡）：申貸人須未滿50歲，且申貸年齡加計核貸年限不得超過80。
+2. 增加所得限制（排除富有）：借款人個人年所得不得超過200萬元。
+3. 增加總價限制（排除高價）：購屋總價上限，台北市房屋總價3,500萬元，新北市及新竹市縣2,500萬元，其他縣（市）2,000萬元。
+4. 增加優惠利率期間限制（排除長期優惠）：青安3.0案優惠利率期間為6年，第7年起不再給予利率優惠。拉年輕人一把，而非拉他一輩子。讓政府有限資源，照顧更多的人。
+• (三) 貸款條件：
+1. 貸款年限：最長40年。
+2. 寬限期：最多5年。
+3. 貸款利率：前3年補貼2碼，第4年起逐年減少0.5碼，公股銀行0.5碼補貼至第6年。
+4. 貸款額度：最高貸款比例8成。一般首購最高貸款額度1,000萬元，結婚兩年內最高貸款額度1,200萬元，育有未成年家庭最高貸款額度1,500萬元。
+• (四) 青安3.0方案是否會造成房價上漲：2023年「青安2.0方案」上路，適逢房市熱潮，因此部分人士將房價高漲怪罪青安方案。至於2026年「青安3.0方案」上路應不致造成房價上漲。其理由如下：
+1. 目前房市量縮價穩，部分地區甚至下跌。
+2. 中央銀行選擇性信用管制尚未鬆綁，房市回溫可能性低。
+3. 現行房市買盤由自住需求支撐，投機性需求已消聲匿跡。
+4. 目前銀行維持審慎授信，謹慎放款。
+5. 「青安3.0方案」新增年齡、所得、房價之限制，遏止假性需求，限制轉售圖利或出租牟利。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H967"/>
+  <dimension ref="A1:H968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35499,6 +35499,65 @@
         </is>
       </c>
     </row>
+    <row r="968">
+      <c r="A968" t="n">
+        <v>916115</v>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>買房後才知道簽約當天發生自殺事件，有關仲介之凶宅資訊揭露義務</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916115</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>2026-08-18 12:22:56</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>凶宅、不動產經紀業管理條例</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[圖片1] 圖片來源：本專欄依據判決整理重點內容，並去識別化後，請ChatGPT生成圖片。
+• 一、案例事實 甲於民國109年6月間，經由乙仲介公司居間，得知丙欲出售其所有之A屋及其基地持分，並於民國109年8月6日簽訂不動產買賣契約，買賣價格為665萬元。
+嗣後，甲於民國113年1月19日委託其他仲介公司銷售A屋，經該仲介公司進行屋況調查後，發現A屋於民國109年8月6日晚上10時38分，有租客於屋內上吊自縊之情事，現場勘查時間為同日晚上11時25分。
+甲主張，A屋買賣契約所附之房地產標的現況說明書，對於持有期間是否曾發生非自然死亡情形，或本標的是否曾發生非自然死亡情形，均未記載。於簽約後至繳清尾款、完稅，甚至辦妥移轉登記交屋前，丙、乙仲介公司及其經紀人員丁，亦均未就此一情形如實說明。甲若知悉此重大瑕疵，絕無意願購買A屋。
+丙則抗辯，其出售A屋時完全不知有租客上吊自縊之事；縱有甲所述之事，甲於交屋後正常使用A屋經營安親班、補習班已近四年之久，期間一切如常，並無物之瑕疵，亦未影響通常效用。
+乙仲介公司及丁則抗辯，甲於6月至7月間看屋多次，至8月6日與前屋主見面議價敲定成交價格；其等至收受法院通知時才知道此事，並無知情未告知之情形。
+試問：A屋於簽約當日發生租客上吊自縊事件，買受人於數年後出售時才查知，得否向出賣人請求減少價金？仲介公司及經紀人員是否應負違反調查、據實告知義務之損害賠償責任？
+• 二、相關法條 (一)民法第567條：「居間人關於訂約事項，應就其所知，據實報告於各當事人。對於顯無履行能力之人，或知其無訂立該約能力之人，不得為其媒介。以居間為營業者，關於訂約事項及當事人之履行能力或訂立該約之能力，有調查之義務。」 (二)不動產經紀業管理條例第4條第5款：「仲介業務，係指從事不動產買賣、互易、租賃之居間或代理業務。」 (三)不動產經紀業管理條例第24條之2第3款、第4款：「經營仲介業務者經買賣或租賃雙方當事人之書面同意，得同時接受雙方之委託，並依下列規定辦理：一、公平提供雙方當事人類似不動產之交易價格。二、公平提供雙方當事人有關契約內容規範之說明。三、提供買受人或承租人關於不動產必要之資訊。四、告知買受人或承租人依仲介專業應查知之不動產之瑕疵。五、協助買受人或承租人對不動產進行必要之檢查。六、其他經中央主管機關為保護買賣或租賃當事人所為之規定。」 (四)不動產經紀業管理條例第26條第2項：「經紀業因經紀人員執行仲介或代銷業務之故意或過失致交易當事人受損害者，該經紀業應與經紀人員負連帶賠償責任。」
+• 三、重要判決觀念 (一)凶宅雖無法律上定義，但依交易慣例係指曾發生凶殺或自殺致死之房屋 非自然身故情事之房屋即一般所稱之凶宅，雖無法律上之定義，然依一般不動產買賣之交易慣例，係指曾發生凶殺或自殺致死之情事之房屋。
+• (二) 非自然身故情事雖未造成物理性損傷，仍會影響購買意願及購買價格，造成經濟性價值減損，應認屬物之瑕疵 此一因素，雖或未對此類房屋造成直接物理性之損傷，惟就一般社會大眾言，仍屬於心理層面嫌惡狀況，對居住於其內之住戶而言，除對居住品質會發生疑慮外，在心理層面止亦會造成相當大之負面影響。…因此，在房地產交易市場及實務經驗中，具有非自然身故情事之房屋，會嚴重影響購買意願及購買價格，亦造成該等房屋之市場接受程度及價格之低落情事。…非自然身故之情事，將對不動產之個別條件產生負面影響，造成經濟性之價值減損，進而影響其市場價格，應認屬物之瑕疵。
+• (三) 仲介業者收取佣金，應負善盡預見危險及調查之義務 仲介業之業務，涉及房地買賣之專業知識，一般之消費者委由仲介業者處理買賣事宜。而仲介業者針對其所為之仲介行為，既向消費者收取高額之佣金，應就其所從事之業務負善盡預見危險及調查之義務。…因此，丁、乙仲介公司對於買賣A屋之必要資訊負有調查及誠實告知買受人即甲之義務。經查，A屋於109年8月6日發生租客上吊自縊之情形，已如前述，A屋於109年9月25日始交屋，丁、乙仲介公司自應有據實查證之義務，丁收受報酬，自應有詳實查證之義務，卻疏於查證，自難以不知情為由。
+• (四) 仲介人員違反據實告知及調查義務，仲介公司應連帶負損害賠償責任 經紀人丁自有違反據實告知之義務，違反民法第567條居間人應據實告知及調查義務，並違反不動產經紀業管理條例第24之2條第3款提供買受人必要之資訊，自係違反保護他人之法律，甲依據民法第184條第2項規定，請求丁應負損害賠償責任；依不動產經紀業管理條例第26條第2項規定，請求丁、乙仲介公司應負連帶損害賠償責任，應屬有據。
+• (五) 出賣人與仲介業者對買受凶宅之損害，性質上屬不真正連帶債務 丙、丁、乙仲介公司分別基於請求減少價金、違反居間義務之原因，就甲買受凶宅之損害各負全部給付義務，性質上屬不真正連帶債務，則丙及丁、乙仲介公司，如任一人為給付者，另一人於該給付範圍內免給付之責。
+• 四、結論 本件甲向丙購買A屋後，於數年後委託其他仲介銷售時，才發現A屋於簽約當日晚上發生租客上吊自縊事件。法院認為，具有非自然身故情事之房屋，雖未造成直接物理性損傷，但就一般社會大眾而言，仍屬心理層面嫌惡狀況，會嚴重影響購買意願、購買價格及市場接受程度，並造成經濟性價值減損，應認屬物之瑕疵。
+就仲介責任部分，法院認為，仲介業者涉及房地買賣專業知識，且向消費者收取高額佣金，應就其所從事之業務負善盡預見危險及調查之義務。A屋於民國109年8月6日發生租客上吊自縊，並於民國109年9月25日始交屋，丁及乙仲介公司自應有據實查證之義務。丁收受報酬，卻疏於查證，自難以不知情為由免責。
+因此，法院認為，丁違反民法第567條居間人據實告知及調查義務，並違反不動產經紀業管理條例第24條之2第3款提供買受人必要資訊之義務，甲得依民法第184條第2項請求丁負損害賠償責任，並依不動產經紀業管理條例第26條第2項，請求丁及乙仲介公司負連帶損害賠償責任。
+資料來源：臺灣新北地方法院113年度訴字第520號民事判決。
+## 文章圖片
+![圖片1](./images/916115_93173d60.png)
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H968"/>
+  <dimension ref="A1:H969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35558,6 +35558,54 @@
         </is>
       </c>
     </row>
+    <row r="969">
+      <c r="A969" t="n">
+        <v>916131</v>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>地價上漲帶動房價上漲，抑或房價上漲帶動地價上漲？</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916131</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:23:25</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>地價上漲、房價上漲</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>社會普遍認為地價上漲帶動房價上漲，但筆者認為房價上漲帶動地價上漲。茲分短期分析及長期分析說明如下：
+• (一) 短期分析：
+1. 房價是由房屋需求與房屋供給所決定，而非生產成本（包括土地成本、營建成本等）所決定。
+2. 民眾對於房屋需求增加，導致房價上漲。建設公司因房價上漲而投資興建房屋有利可圖，遂競相購買土地，造成土地需求增加，地價隨之上漲。因此，房價上漲帶動地價上漲。
+• (二) 長期分析：土地成本係房屋之生產成本之一。生產成本增加（即地價上漲），房價跟著上漲。因此，地價上漲帶動房價上漲。
+• (三) 結論：
+1. 就短期分析而言，房價上漲帶動地價上漲；就長期分析而言，地價上漲帶動房價上漲。然，所謂經濟分析，一般指短期分析或短期現象，而非指長期分析或長期現象。
+2. 房價上漲，立即帶動地價上漲。然，地價上漲，短期不會帶動房價上漲。此時，建設公司無利可圖或甚至虧損，因此建設公司遂減少推出新案，導致市場上房屋供給減少。經過數年後，房價才會因房屋供給減少而上漲。前揭所稱「數年後」，即長期分析。
+3. 「房價影響地價，而非地價影響房價。」此正是不動產估價之土地開發分析法（詳見不動產估價技術規則第70條及第81條）之精髓所在。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H969"/>
+  <dimension ref="A1:H970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35606,6 +35606,49 @@
         </is>
       </c>
     </row>
+    <row r="970">
+      <c r="A970" t="n">
+        <v>916162</v>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>土地徵收收回權及優先購買權之比較</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>2026/08/25</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916162</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:24:34</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>徵收土地、收回權、優先購買權</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>• 一、徵收收回權 被徵收之土地，除區段徵收及本條例或其他法律另有規定外，有下列情形之一者，原土地所有權人得於徵收公告之日起二十年內，向該管直轄市或縣（市）主管機關申請照原徵收補償價額收回其土地，不適用土地法第二百十九條之規定： 一、徵收補償費發給完竣屆滿三年，未依徵收計畫開始使用者。 二、未依核准徵收原定興辦事業使用者。 三、依原徵收計畫開始使用後未滿五年，不繼續依原徵收計畫使用者。 該管直轄市或縣（市）主管機關收受申請後，經查明合於前項規定時，應報原核准徵收機關核准後，通知原土地所有權人於六個月內繳還原受領之補償地價及地價加成補償，逾期視為放棄收回權。 第一項第一款之情形，係因不可歸責於需用土地人之事由者，不得申請收回土地。 第一項第一款所稱開始使用，指興辦事業之主體工程動工。但依其事業性質無需興建工程者，不在此限。
+• 二、優先購買權 私有土地經依徵收計畫使用後，依法變更原使用目的，土地管理機關標售該土地時，應公告一個月，被徵收之原土地所有權人或其繼承人有依同樣條件優先購買權。但優先購買權人未於決標後十日內表示優先購買者，其優先購買權視為放棄。 依第八條第一項規定一併徵收之土地，須與原徵收土地同時標售時，適用前項之規定。 前二項規定，於區段徵收不適用之。
+• 三、收回權與優先購買權之比較兩者差異茲整理如下表：
+• T. ABLE_PLACEHOLDER_1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H970"/>
+  <dimension ref="A1:H971"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35649,6 +35649,67 @@
         </is>
       </c>
     </row>
+    <row r="971">
+      <c r="A971" t="n">
+        <v>916172</v>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>土地徵收之目的</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916172</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:02:25</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>土地徵收</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• (一) 現行土地徵收之用途：
+1. 土地法之規定：
+• (1)土地法第208條規定：「國家因左列公共事業之需要，得依本法之規定徵收私有土地。……。九、其他由政府興辦以公共利益為目的之事業。」由此可知，依土地法第208條規定，土地徵收之目的原則僅限於公共用途。
+• (2)土地法第209條規定：「政府機關因實施國家經濟政策，得徵收私有土地，但應以法律規定者爲限。」由此可知，依土地法第209條規定，土地徵收之目的得為實施國家經濟政策，不限於公共用途，非公共用途亦得徵收私有土地。
+綜上，土地法規定之土地徵收目的為公共利益，包括公共用途及非公共用途。
+2. 土地徵收條例之規定： 土地徵收條例第3條規定：「國家因公益需要，興辦下列各款事業，得徵收私有土地；……。一○、其他依法得徵收土地之事業。」由此可知，依土地徵收條例第3條規定，土地徵收之目的為公共利益，包括公共用途及非公共用途。
+總之，不論土地法或土地徵收條例，土地徵收之目的皆為公共利益，包括公共用途及非公共用途。
+• (二) 公共用途與非公共用途之區別： 公共利益包括公共用途及非公共用途。如圖所示。所稱公共用途，指供公眾使用，不限定特定人使用（稅減§4）。所稱非公共用途，指供特定人使用。
+[圖片1]
+1. 公共用途：例如，政府徵收私人土地，開闢成公園；公園即為公共用途。又例如，政府徵收私人土地，興建高速公路；高速公路即為公共用途。 土地徵收之目的應以公共用途為主。亦即犧牲私人財產權，最後成就眾人之公共利益。
+2. 非公共用途：例如，政府徵收私人土地，興建國民住宅，再將國民住宅出售給中低收入家庭；中低收入家庭（即私人）即為非公共用途。又例如，政府徵收私人土地，開發工業區，再將工業區土地出售給興辦工業人；興辦工業人（即私人）即為非公共用途。 土地徵收之目的如為非公共用途，並再出售給私人，恐造成犧牲某些私人之財產權，最後成就另一些私人之私人利益。換言之，政府以徵收手段，進行私人財富重分配。就民主國家而言，實不足取。
+• (三) 結論：
+1. 土地徵收是侵害私人財產權最激烈之手段。國家實施土地徵收應力求節制，避免浮濫，故應儘量以公共用途為限。至於非公共用途，政府機關為公用或公益之目的而以徵收方式剝奪人民財產權後，如續將原屬人民之財產移轉於第三人所有，易使徵收權力濫用及使人民產生圖利特定第三人之疑慮（司法院釋字第743號解釋理由書）。因此，政府徵收人民之土地，無論公共用途或非公共用途，均不宜再將其出售為私人所有。
+2. 土地徵收之用途可分為下列三種：
+• (1)公共用途，且未移轉於特定人。如高速公路。
+• (2)非公共用途，且未移轉於特定人。如開發工業區，再將工業區土地出租給興辦工業人。
+• (3)非公共用途，且移轉於特定人。如國民住宅。
+土地徵收之用途，嚴格而論，應侷限於上開第(1)種情形；寬鬆而論，頂多放寬加入第(2)種情形，但應謹慎且節制為之。至於第(3)種情形，將造成土地徵收之浮濫，應避免之。
+【註】 稅減：土地稅減免規則。
+## 文章圖片
+![圖片1](./images/916172_f8e2477e.png)
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H971"/>
+  <dimension ref="A1:H972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35710,6 +35710,48 @@
         </is>
       </c>
     </row>
+    <row r="972">
+      <c r="A972" t="n">
+        <v>916187</v>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>共有及基地優先購買權之要件比較</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916187</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:42:54</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>優先購買權</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>• 一、共有不動產出賣之優先購買權 共有人出賣其應有部分時，他共有人得以同一價格共同或單獨優先承購(土法§34-1 IV)。
+• 二、基地或房屋出賣之優先購買權 基地出賣時，地上權人、典權人或承租人有依同樣條件優先購買之權。房屋出賣時，基地所有權人有依同樣條件優先購買之權。其順序以登記之先後定之(土法§104 I)。 優先購買權人，於接到出賣通知後10日內不表示者，其優先權視為放棄。出賣人未通知優先購買權人而與第三人訂立買賣契約者，其契約不得對抗優先購買權人(土法§104 II)。此即為物權效力（性質）。
+• T. ABLE_PLACEHOLDER_1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H972"/>
+  <dimension ref="A1:H973"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35752,6 +35752,54 @@
         </is>
       </c>
     </row>
+    <row r="973">
+      <c r="A973" t="n">
+        <v>916189</v>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>結合土地法第12條及第57條之實例研習</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916189</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>2026-09-03 15:25:10</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>物上請求權、民法消滅時效</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>甲所有一筆土地，日治時期曾經登記為甲所有，因成為河川經塗銷登記，嗣於台灣光復後浮覆，然未於土地總登記辦理期間申請登記，致登記為國有迄今。試問該地所有權屬誰？甲行使物上請求權有無民法消滅時效規定之適用？
+【解答】
+• (一) 該地所有權屬於甲。理由如下：
+1. 該地浮覆，原所有權人甲之所有權當然回復，不待地政機關核准，不以公告劃出河川區域範圍以外，亦不以完成登記為要件。
+2. 土地總登記，僅係確認、整理及清查當時之地籍狀態與產權歸屬，並無使不動產物權發生變動。日治時期屬於人民私有之土地，雖經辦理土地總登記之程序而登記為國有，然該登記與物權之歸屬無關，並未影響人民自日治時期已取得之土地所有權，人民仍為該土地之真正所有人。
+• (二) 甲行使物上請求權無民法消滅時效規定之適用。理由如下：
+1. 國家為該地之登記名義人，甲為該地之真正權利人，致登記名義人與真正權利人不一致。此時，甲得行使物上請求權之除去妨害請求權，以回復所有權之圓滿狀態。
+2. 國家基於公權力主體地位行使統治高權，致與人民發生財產權爭執時，國家本非憲法第15條財產權保障之主體。因此，人民基於土地所有人地位，請求國家塗銷登記時，無民法消滅時效規定之適用。亦即，國家不得以時效完成為抗辯而拒絕返還。
+（本題解答依據憲法法庭112年憲判字第20號判決）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H973"/>
+  <dimension ref="A1:H974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35800,6 +35800,52 @@
         </is>
       </c>
     </row>
+    <row r="974">
+      <c r="A974" t="n">
+        <v>916217</v>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>照價收買與土地徵收之差異</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916217</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:34:57</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>照價收買、土地徵收</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>照價收買雖與土地徵收同屬政府以公權力強制取得人民土地之制度，但二者之發動原因、制度目的、程序、地價計算基準及法律效果，均不相同。土地徵收係基於公共利益或公益事業需要，由需用土地人依法申請，經中央主管機關核准後，由主管機關執行，並以市價補償為原則；照價收買則係針對人民違反土地政策之法定情形所採之強制取得措施，其收買地價並非按市價補償，而係依法律規定，分別以申報地價、申報土地移轉現值或收買當期公告土地現值計算。土地徵收具有公益實現之積極性與建設性；照價收買則較偏重防杜投機、矯正違規及促進土地合理利用，故屬制止性、矯正性較強之制度。
+又在法律效果上，土地徵收一般認為屬原始取得；至於照價收買究屬原始取得或繼受取得，學說上仍有不同見解，認較偏向繼受取得。另土地徵收取得之土地，原則上應供徵收計畫所定公益事業使用；照價收買取得之土地，則依土地性質不同，分別得予標售、讓售，農業用地並得出租與農民，必要時亦得優先讓售與需用土地人。至於稅負方面，被徵收土地依法免徵土地增值稅；照價收買則無此免稅規定，原則上仍屬土地增值稅課徵範圍。
+• T. ABLE_PLACEHOLDER_1
+補充：照價收買屬繼受取得之理由
+1. 目的：土地徵收為需用土地人創設新權利，使其取得供特定公益事業使用土地，而照價收買側重對土地所有權人權利之剝奪，後者涉及私益而非純屬公益，而宜解為繼受取得1。
+2. 保障：依平均地權條例第34條規定，照價收買之土地，地上建築改良物不屬土地所有權人所有者，不需一併收買。又平均地權條例施行細則第48條規定，照價收買之土地建有房屋時，得讓售與地上權人、土地承租人或房屋所有權人，故可解釋為權利繼續存續，而屬繼受取得。
+1陳明燦，2015，土地法學，一版，第724頁。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H974"/>
+  <dimension ref="A1:H975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35846,6 +35846,48 @@
         </is>
       </c>
     </row>
+    <row r="975">
+      <c r="A975" t="n">
+        <v>916243</v>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>使用借貸之優先購買權</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>2026/09/10</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916243</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:24:48</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>使用借貸、優先購買權</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>使用借貸，當事人一方以物交付他方，而約定他方於無償使用後返還其物之契約（民§464）。使用借貸與租賃皆屬於債權。前者為無償行為，後者為有償行為。
+• (一) 使用借貸不得適用土地法第104條之優先購買權：土地法第104條優先購買權限於建物與其基地之間存在地上權、典權或租賃權，不包括使用借貸。 例如：甲將其土地出借於乙建屋居住使用，不久乙即建屋使用。之後，甲將其土地出售於第三人丙，則借用人乙無優先購買權。
+• (二) 使用借貸得適用土地法第73條之1之優先購買權：未辦繼承土地，經財政部國有財產署公開標售時，繼承人、合法使用人或其他共有人就其使用範圍依序有優先購買權。 例如：甲將其土地出借於乙建屋居住使用，不久乙即建屋使用。之後，甲死亡，一直未辦理繼承登記，經財政部國有財產署公開標售，並由丙得標。此際，借用人乙為合法使用人，得就其使用範圍部分，主張優先購買。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
